--- a/NBFC-MF/CashFlow.xlsx
+++ b/NBFC-MF/CashFlow.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="226">
   <si>
     <t>Transaction Description</t>
   </si>
@@ -679,6 +679,33 @@
   <si>
     <t>223ChongthamGr</t>
   </si>
+  <si>
+    <t>bikram phiroi transfer to chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interest payment </t>
+  </si>
+  <si>
+    <t>kongba marup</t>
+  </si>
+  <si>
+    <t>162bijenti</t>
+  </si>
+  <si>
+    <t>224Kamala</t>
+  </si>
+  <si>
+    <t>wangkhei marup</t>
+  </si>
+  <si>
+    <t>197samila</t>
+  </si>
+  <si>
+    <t>225Samila</t>
+  </si>
+  <si>
+    <t>226Sandhyarani</t>
+  </si>
 </sst>
 </file>
 
@@ -3201,10 +3228,16 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" s="17"/>
+      <c r="A93" s="17">
+        <v>46277</v>
+      </c>
       <c r="B93" s="14"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="14"/>
+      <c r="C93" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
       <c r="G93" s="14">
@@ -3213,826 +3246,1513 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="16"/>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
+      <c r="A94" s="16">
+        <v>46277</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" s="13">
+        <v>300</v>
+      </c>
       <c r="F94" s="13"/>
       <c r="G94" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>75526</v>
       </c>
       <c r="I94" s="21"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="17"/>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
+      <c r="A95" s="17">
+        <v>46278</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="14">
+        <v>300</v>
+      </c>
       <c r="F95" s="14"/>
       <c r="G95" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>75826</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="16"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
+      <c r="A96" s="16">
+        <v>46278</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" s="13">
+        <v>300</v>
+      </c>
       <c r="F96" s="13"/>
       <c r="G96" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>76126</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="17"/>
-      <c r="B97" s="14"/>
-      <c r="C97" s="14"/>
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
+      <c r="A97" s="17">
+        <v>46278</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" s="14">
+        <v>150</v>
+      </c>
       <c r="F97" s="14"/>
       <c r="G97" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>76276</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="16"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
+      <c r="A98" s="16">
+        <v>46278</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="13">
+        <v>200</v>
+      </c>
       <c r="F98" s="13"/>
       <c r="G98" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>76476</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="17"/>
-      <c r="B99" s="14"/>
-      <c r="C99" s="14"/>
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
+      <c r="A99" s="17">
+        <v>46278</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" s="14">
+        <v>2100</v>
+      </c>
       <c r="F99" s="14"/>
       <c r="G99" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>78576</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="16"/>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
+      <c r="A100" s="16">
+        <v>46279</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" s="13">
+        <v>300</v>
+      </c>
       <c r="F100" s="13"/>
       <c r="G100" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>78876</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="17"/>
-      <c r="B101" s="14"/>
-      <c r="C101" s="14"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="14"/>
+      <c r="A101" s="17">
+        <v>46279</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="14">
+        <v>7000</v>
+      </c>
       <c r="F101" s="14"/>
       <c r="G101" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>85876</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="16"/>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
+      <c r="A102" s="16">
+        <v>46279</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" s="13">
+        <v>7000</v>
+      </c>
       <c r="F102" s="13"/>
       <c r="G102" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>92876</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="17"/>
-      <c r="B103" s="14"/>
-      <c r="C103" s="14"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="14"/>
+      <c r="A103" s="17">
+        <v>46279</v>
+      </c>
+      <c r="B103" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" s="14">
+        <v>200</v>
+      </c>
       <c r="F103" s="14"/>
       <c r="G103" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>93076</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="16"/>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
+      <c r="A104" s="16">
+        <v>46279</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" s="13">
+        <v>200</v>
+      </c>
       <c r="F104" s="13"/>
       <c r="G104" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>93276</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="17"/>
-      <c r="B105" s="14"/>
-      <c r="C105" s="14"/>
-      <c r="D105" s="14"/>
-      <c r="E105" s="14"/>
+      <c r="A105" s="17">
+        <v>46279</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" s="14">
+        <v>1400</v>
+      </c>
       <c r="F105" s="14"/>
       <c r="G105" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>94676</v>
       </c>
       <c r="H105" s="21"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="16"/>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
+      <c r="A106" s="16">
+        <v>46279</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" s="13">
+        <v>1400</v>
+      </c>
       <c r="F106" s="13"/>
       <c r="G106" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>96076</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="17"/>
-      <c r="B107" s="14"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
+      <c r="A107" s="17">
+        <v>46279</v>
+      </c>
+      <c r="B107" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" s="14">
+        <v>1400</v>
+      </c>
       <c r="F107" s="14"/>
       <c r="G107" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>97476</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="16"/>
-      <c r="B108" s="13"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
+      <c r="A108" s="16">
+        <v>46279</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" s="13">
+        <v>1400</v>
+      </c>
       <c r="F108" s="13"/>
       <c r="G108" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>98876</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="17"/>
-      <c r="B109" s="14"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
+      <c r="A109" s="17">
+        <v>46280</v>
+      </c>
+      <c r="B109" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="14">
+        <v>300</v>
+      </c>
       <c r="F109" s="14"/>
       <c r="G109" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>99176</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="16"/>
-      <c r="B110" s="13"/>
-      <c r="C110" s="13"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
+      <c r="A110" s="16">
+        <v>46280</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" s="13">
+        <v>200</v>
+      </c>
       <c r="F110" s="13"/>
       <c r="G110" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>99376</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="17"/>
-      <c r="B111" s="14"/>
-      <c r="C111" s="14"/>
-      <c r="D111" s="14"/>
-      <c r="E111" s="14"/>
+      <c r="A111" s="17">
+        <v>46280</v>
+      </c>
+      <c r="B111" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" s="14">
+        <v>200</v>
+      </c>
       <c r="F111" s="14"/>
       <c r="G111" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>99576</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="16"/>
-      <c r="B112" s="13"/>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
+      <c r="A112" s="16">
+        <v>46280</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E112" s="13">
+        <v>2400</v>
+      </c>
       <c r="F112" s="13"/>
       <c r="G112" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>101976</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="17"/>
-      <c r="B113" s="14"/>
-      <c r="C113" s="14"/>
-      <c r="D113" s="14"/>
-      <c r="E113" s="14"/>
+      <c r="A113" s="17">
+        <v>46280</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C113" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D113" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E113" s="14">
+        <v>600</v>
+      </c>
       <c r="F113" s="14"/>
       <c r="G113" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>102576</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="16"/>
-      <c r="B114" s="13"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
+      <c r="A114" s="16">
+        <v>46280</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E114" s="13">
+        <v>300</v>
+      </c>
       <c r="F114" s="13"/>
       <c r="G114" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="17"/>
-      <c r="B115" s="14"/>
-      <c r="C115" s="14"/>
-      <c r="D115" s="14"/>
+        <v>102876</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A115" s="17">
+        <v>46280</v>
+      </c>
+      <c r="B115" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C115" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E115" s="14"/>
-      <c r="F115" s="14"/>
+      <c r="F115" s="14">
+        <v>2000</v>
+      </c>
       <c r="G115" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>100876</v>
       </c>
       <c r="H115" s="21"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="16"/>
-      <c r="B116" s="13"/>
-      <c r="C116" s="13"/>
-      <c r="D116" s="13"/>
+      <c r="A116" s="16">
+        <v>46280</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
+      <c r="F116" s="13">
+        <v>6500</v>
+      </c>
       <c r="G116" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="17"/>
-      <c r="B117" s="14"/>
-      <c r="C117" s="14"/>
-      <c r="D117" s="14"/>
+        <v>94376</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A117" s="17">
+        <v>46280</v>
+      </c>
+      <c r="B117" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C117" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E117" s="14"/>
-      <c r="F117" s="14"/>
+      <c r="F117" s="14">
+        <v>5000</v>
+      </c>
       <c r="G117" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>89376</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="16"/>
-      <c r="B118" s="13"/>
-      <c r="C118" s="13"/>
-      <c r="D118" s="13"/>
+      <c r="A118" s="16">
+        <v>46280</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
+      <c r="F118" s="13">
+        <v>3000</v>
+      </c>
       <c r="G118" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>86376</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="17"/>
-      <c r="B119" s="14"/>
-      <c r="C119" s="14"/>
-      <c r="D119" s="14"/>
-      <c r="E119" s="14"/>
+      <c r="A119" s="17">
+        <v>46281</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C119" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D119" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E119" s="14">
+        <v>300</v>
+      </c>
       <c r="F119" s="14"/>
       <c r="G119" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>86676</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="16"/>
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
+      <c r="A120" s="16">
+        <v>46281</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E120" s="13">
+        <v>200</v>
+      </c>
       <c r="F120" s="13"/>
       <c r="G120" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>86876</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="17"/>
-      <c r="B121" s="14"/>
-      <c r="C121" s="14"/>
-      <c r="D121" s="14"/>
-      <c r="E121" s="14"/>
+      <c r="A121" s="17">
+        <v>46281</v>
+      </c>
+      <c r="B121" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C121" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D121" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E121" s="14">
+        <v>500</v>
+      </c>
       <c r="F121" s="14"/>
       <c r="G121" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="16"/>
-      <c r="B122" s="13"/>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
+        <v>87376</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A122" s="16">
+        <v>46281</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E122" s="13">
+        <v>4200</v>
+      </c>
       <c r="F122" s="13"/>
       <c r="G122" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>91576</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="17"/>
-      <c r="B123" s="14"/>
-      <c r="C123" s="14"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="14"/>
+      <c r="A123" s="17">
+        <v>46281</v>
+      </c>
+      <c r="B123" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C123" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D123" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" s="14">
+        <v>4200</v>
+      </c>
       <c r="F123" s="14"/>
       <c r="G123" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>95776</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="16"/>
-      <c r="B124" s="13"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
+      <c r="A124" s="16">
+        <v>46281</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E124" s="13">
+        <v>2100</v>
+      </c>
       <c r="F124" s="13"/>
       <c r="G124" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>97876</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="17"/>
-      <c r="B125" s="14"/>
-      <c r="C125" s="14"/>
-      <c r="D125" s="14"/>
-      <c r="E125" s="13"/>
+      <c r="A125" s="17">
+        <v>46282</v>
+      </c>
+      <c r="B125" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C125" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E125" s="13">
+        <v>300</v>
+      </c>
       <c r="F125" s="14"/>
       <c r="G125" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>98176</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="16"/>
-      <c r="B126" s="13"/>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
+      <c r="A126" s="16">
+        <v>46282</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E126" s="13">
+        <v>3000</v>
+      </c>
       <c r="F126" s="13"/>
       <c r="G126" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>101176</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="17"/>
-      <c r="B127" s="14"/>
-      <c r="C127" s="14"/>
-      <c r="D127" s="14"/>
-      <c r="E127" s="14"/>
+      <c r="A127" s="17">
+        <v>46282</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C127" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E127" s="14">
+        <v>200</v>
+      </c>
       <c r="F127" s="14"/>
       <c r="G127" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>101376</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="16"/>
-      <c r="B128" s="13"/>
-      <c r="C128" s="13"/>
-      <c r="D128" s="13"/>
-      <c r="E128" s="13"/>
+      <c r="A128" s="16">
+        <v>46282</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E128" s="13">
+        <v>1500</v>
+      </c>
       <c r="F128" s="13"/>
       <c r="G128" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>102876</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" s="17"/>
-      <c r="B129" s="14"/>
-      <c r="C129" s="14"/>
-      <c r="D129" s="14"/>
-      <c r="E129" s="14"/>
+      <c r="A129" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B129" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D129" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E129" s="14">
+        <v>1400</v>
+      </c>
       <c r="F129" s="14"/>
       <c r="G129" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>104276</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="16"/>
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
+      <c r="A130" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E130" s="13">
+        <v>1400</v>
+      </c>
       <c r="F130" s="13"/>
       <c r="G130" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>105676</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A131" s="17"/>
-      <c r="B131" s="14"/>
-      <c r="C131" s="14"/>
-      <c r="D131" s="14"/>
-      <c r="E131" s="14"/>
+      <c r="A131" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C131" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D131" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E131" s="14">
+        <v>1400</v>
+      </c>
       <c r="F131" s="14"/>
       <c r="G131" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A132" s="16"/>
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
+        <v>107076</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A132" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E132" s="13">
+        <v>1400</v>
+      </c>
       <c r="F132" s="13"/>
       <c r="G132" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>108476</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A133" s="17"/>
-      <c r="B133" s="14"/>
-      <c r="C133" s="14"/>
-      <c r="D133" s="14"/>
-      <c r="E133" s="14"/>
+      <c r="A133" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C133" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D133" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E133" s="14">
+        <v>1400</v>
+      </c>
       <c r="F133" s="14"/>
       <c r="G133" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>109876</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A134" s="16"/>
-      <c r="B134" s="13"/>
-      <c r="C134" s="13"/>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
+      <c r="A134" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D134" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E134" s="13">
+        <v>200</v>
+      </c>
       <c r="F134" s="13"/>
       <c r="G134" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>110076</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A135" s="17"/>
-      <c r="B135" s="14"/>
-      <c r="C135" s="14"/>
-      <c r="D135" s="14"/>
-      <c r="E135" s="14"/>
+      <c r="A135" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C135" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D135" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E135" s="14">
+        <v>300</v>
+      </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>110376</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A136" s="16"/>
-      <c r="B136" s="13"/>
-      <c r="C136" s="13"/>
-      <c r="D136" s="13"/>
-      <c r="E136" s="13"/>
+      <c r="A136" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" s="13">
+        <v>12600</v>
+      </c>
       <c r="F136" s="13"/>
       <c r="G136" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>122976</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A137" s="17"/>
-      <c r="B137" s="14"/>
-      <c r="C137" s="14"/>
-      <c r="D137" s="14"/>
-      <c r="E137" s="14"/>
+      <c r="A137" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E137" s="14">
+        <v>1400</v>
+      </c>
       <c r="F137" s="14"/>
       <c r="G137" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>124376</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A138" s="16"/>
-      <c r="B138" s="13"/>
-      <c r="C138" s="13"/>
-      <c r="D138" s="13"/>
-      <c r="E138" s="13"/>
+      <c r="A138" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C138" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E138" s="13">
+        <v>3000</v>
+      </c>
       <c r="F138" s="13"/>
       <c r="G138" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>127376</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A139" s="17"/>
-      <c r="B139" s="14"/>
-      <c r="C139" s="14"/>
-      <c r="D139" s="14"/>
-      <c r="E139" s="14"/>
+      <c r="A139" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B139" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C139" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D139" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E139" s="14">
+        <v>2100</v>
+      </c>
       <c r="F139" s="14"/>
       <c r="G139" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
-      </c>
+        <v>129476</v>
+      </c>
+      <c r="H139" s="21"/>
       <c r="I139" s="21"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A140" s="16"/>
-      <c r="B140" s="13"/>
-      <c r="C140" s="13"/>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
+      <c r="A140" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" s="13">
+        <v>500</v>
+      </c>
       <c r="F140" s="13"/>
       <c r="G140" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
-      </c>
+        <v>129976</v>
+      </c>
+      <c r="H140" s="21"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A141" s="17"/>
-      <c r="B141" s="14"/>
-      <c r="C141" s="14"/>
-      <c r="D141" s="14"/>
-      <c r="E141" s="14"/>
+      <c r="A141" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B141" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="C141" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E141" s="14">
+        <f>400*29</f>
+        <v>11600</v>
+      </c>
       <c r="F141" s="14"/>
       <c r="G141" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>141576</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A142" s="16"/>
-      <c r="B142" s="13"/>
-      <c r="C142" s="13"/>
-      <c r="D142" s="13"/>
+      <c r="A142" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E142" s="13"/>
-      <c r="F142" s="13"/>
+      <c r="F142" s="13">
+        <v>50000</v>
+      </c>
       <c r="G142" s="13">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>91576</v>
       </c>
       <c r="H142" s="21"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A143" s="17"/>
-      <c r="B143" s="14"/>
-      <c r="C143" s="14"/>
-      <c r="D143" s="14"/>
-      <c r="E143" s="14"/>
+      <c r="A143" s="17">
+        <v>46284</v>
+      </c>
+      <c r="B143" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C143" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D143" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E143" s="14">
+        <v>300</v>
+      </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14">
         <f t="shared" si="3"/>
-        <v>75226</v>
+        <v>91876</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A144" s="16"/>
-      <c r="B144" s="13"/>
-      <c r="C144" s="13"/>
-      <c r="D144" s="13"/>
-      <c r="E144" s="13"/>
+      <c r="A144" s="16">
+        <v>46284</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D144" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E144" s="13">
+        <v>200</v>
+      </c>
       <c r="F144" s="13"/>
       <c r="G144" s="13">
         <f t="shared" ref="G144:G207" si="4">G143+E144-F144</f>
-        <v>75226</v>
+        <v>92076</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A145" s="17"/>
-      <c r="B145" s="14"/>
-      <c r="C145" s="14"/>
-      <c r="D145" s="14"/>
-      <c r="E145" s="14"/>
+      <c r="A145" s="17">
+        <v>46285</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D145" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E145" s="14">
+        <v>300</v>
+      </c>
       <c r="F145" s="14"/>
       <c r="G145" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>92376</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A146" s="17"/>
-      <c r="B146" s="14"/>
-      <c r="C146" s="14"/>
-      <c r="D146" s="14"/>
-      <c r="E146" s="14"/>
+      <c r="A146" s="17">
+        <v>46285</v>
+      </c>
+      <c r="B146" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D146" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E146" s="14">
+        <v>200</v>
+      </c>
       <c r="F146" s="14"/>
       <c r="G146" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>92576</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A147" s="16"/>
-      <c r="B147" s="13"/>
-      <c r="C147" s="13"/>
-      <c r="D147" s="13"/>
-      <c r="E147" s="13"/>
+      <c r="A147" s="16">
+        <v>46285</v>
+      </c>
+      <c r="B147" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E147" s="13">
+        <v>2100</v>
+      </c>
       <c r="F147" s="13"/>
       <c r="G147" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>94676</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A148" s="17"/>
-      <c r="B148" s="14"/>
-      <c r="C148" s="14"/>
-      <c r="D148" s="14"/>
-      <c r="E148" s="14"/>
+      <c r="A148" s="17">
+        <v>46285</v>
+      </c>
+      <c r="B148" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D148" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E148" s="14">
+        <v>1400</v>
+      </c>
       <c r="F148" s="14"/>
       <c r="G148" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>96076</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A149" s="16"/>
-      <c r="B149" s="13"/>
-      <c r="C149" s="13"/>
-      <c r="D149" s="13"/>
-      <c r="E149" s="13"/>
+      <c r="A149" s="16">
+        <v>46285</v>
+      </c>
+      <c r="B149" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E149" s="13">
+        <v>1200</v>
+      </c>
       <c r="F149" s="13"/>
       <c r="G149" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>97276</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A150" s="17"/>
-      <c r="B150" s="14"/>
-      <c r="C150" s="14"/>
-      <c r="D150" s="14"/>
-      <c r="E150" s="14"/>
+      <c r="A150" s="17">
+        <v>46285</v>
+      </c>
+      <c r="B150" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C150" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D150" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E150" s="14">
+        <v>300</v>
+      </c>
       <c r="F150" s="14"/>
       <c r="G150" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A151" s="16"/>
-      <c r="B151" s="13"/>
-      <c r="C151" s="13"/>
-      <c r="D151" s="13"/>
+        <v>97576</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A151" s="16">
+        <v>46285</v>
+      </c>
+      <c r="B151" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C151" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E151" s="13"/>
-      <c r="F151" s="13"/>
+      <c r="F151" s="13">
+        <v>12000</v>
+      </c>
       <c r="G151" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>85576</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A152" s="17"/>
-      <c r="B152" s="14"/>
-      <c r="C152" s="14"/>
-      <c r="D152" s="14"/>
-      <c r="E152" s="14"/>
+      <c r="A152" s="17">
+        <v>46286</v>
+      </c>
+      <c r="B152" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C152" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D152" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E152" s="14">
+        <v>300</v>
+      </c>
       <c r="F152" s="14"/>
       <c r="G152" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>85876</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A153" s="16"/>
-      <c r="B153" s="13"/>
-      <c r="C153" s="13"/>
-      <c r="D153" s="13"/>
-      <c r="E153" s="13"/>
+      <c r="A153" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B153" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C153" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E153" s="13">
+        <v>7000</v>
+      </c>
       <c r="F153" s="13"/>
       <c r="G153" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>92876</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A154" s="17"/>
-      <c r="B154" s="14"/>
-      <c r="C154" s="14"/>
-      <c r="D154" s="14"/>
-      <c r="E154" s="14"/>
+      <c r="A154" s="17">
+        <v>46286</v>
+      </c>
+      <c r="B154" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C154" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D154" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E154" s="14">
+        <v>7000</v>
+      </c>
       <c r="F154" s="14"/>
       <c r="G154" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>99876</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A155" s="16"/>
-      <c r="B155" s="13"/>
-      <c r="C155" s="13"/>
-      <c r="D155" s="13"/>
-      <c r="E155" s="13"/>
+      <c r="A155" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B155" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C155" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E155" s="13">
+        <v>700</v>
+      </c>
       <c r="F155" s="13"/>
       <c r="G155" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>100576</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A156" s="17"/>
-      <c r="B156" s="14"/>
-      <c r="C156" s="14"/>
-      <c r="D156" s="14"/>
-      <c r="E156" s="14"/>
+      <c r="A156" s="17">
+        <v>46286</v>
+      </c>
+      <c r="B156" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C156" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D156" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E156" s="14">
+        <v>2100</v>
+      </c>
       <c r="F156" s="14"/>
       <c r="G156" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>102676</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A157" s="16"/>
-      <c r="B157" s="13"/>
-      <c r="C157" s="13"/>
-      <c r="D157" s="13"/>
-      <c r="E157" s="13"/>
+      <c r="A157" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B157" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C157" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E157" s="13">
+        <v>700</v>
+      </c>
       <c r="F157" s="13"/>
       <c r="G157" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A158" s="17"/>
-      <c r="B158" s="14"/>
-      <c r="C158" s="14"/>
-      <c r="D158" s="14"/>
-      <c r="E158" s="14"/>
+        <v>103376</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A158" s="17">
+        <v>46286</v>
+      </c>
+      <c r="B158" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D158" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" s="14">
+        <f>5*1400</f>
+        <v>7000</v>
+      </c>
       <c r="F158" s="14"/>
       <c r="G158" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>110376</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A159" s="16"/>
-      <c r="B159" s="13"/>
-      <c r="C159" s="13"/>
-      <c r="D159" s="13"/>
-      <c r="E159" s="13"/>
+      <c r="A159" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B159" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D159" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" s="13">
+        <f>6*1400</f>
+        <v>8400</v>
+      </c>
       <c r="F159" s="13"/>
       <c r="G159" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
-      </c>
+        <v>118776</v>
+      </c>
+      <c r="I159" s="21"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A160" s="17"/>
-      <c r="B160" s="14"/>
-      <c r="C160" s="14"/>
-      <c r="D160" s="14"/>
+      <c r="A160" s="17">
+        <v>46286</v>
+      </c>
+      <c r="B160" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C160" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D160" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E160" s="14"/>
-      <c r="F160" s="14"/>
+      <c r="F160" s="14">
+        <v>20000</v>
+      </c>
       <c r="G160" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>98776</v>
       </c>
       <c r="I160" s="21"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A161" s="16"/>
-      <c r="B161" s="13"/>
-      <c r="C161" s="13"/>
-      <c r="D161" s="13"/>
+    <row r="161" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A161" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E161" s="13"/>
-      <c r="F161" s="13"/>
+      <c r="F161" s="13">
+        <v>25000</v>
+      </c>
       <c r="G161" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
-      </c>
+        <v>73776</v>
+      </c>
+      <c r="I161" s="21"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="17"/>
@@ -4043,7 +4763,7 @@
       <c r="F162" s="14"/>
       <c r="G162" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
@@ -4055,7 +4775,7 @@
       <c r="F163" s="13"/>
       <c r="G163" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -4067,7 +4787,7 @@
       <c r="F164" s="14"/>
       <c r="G164" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
@@ -4079,7 +4799,7 @@
       <c r="F165" s="13"/>
       <c r="G165" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
@@ -4091,7 +4811,7 @@
       <c r="F166" s="14"/>
       <c r="G166" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -4103,7 +4823,7 @@
       <c r="F167" s="13"/>
       <c r="G167" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
@@ -4115,7 +4835,7 @@
       <c r="F168" s="14"/>
       <c r="G168" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
@@ -4127,7 +4847,7 @@
       <c r="F169" s="13"/>
       <c r="G169" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
@@ -4139,7 +4859,7 @@
       <c r="F170" s="14"/>
       <c r="G170" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
@@ -4151,7 +4871,7 @@
       <c r="F171" s="13"/>
       <c r="G171" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
@@ -4163,7 +4883,7 @@
       <c r="F172" s="14"/>
       <c r="G172" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I172" s="21"/>
     </row>
@@ -4176,7 +4896,7 @@
       <c r="F173" s="13"/>
       <c r="G173" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
@@ -4188,7 +4908,7 @@
       <c r="F174" s="14"/>
       <c r="G174" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
@@ -4200,7 +4920,7 @@
       <c r="F175" s="13"/>
       <c r="G175" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
@@ -4212,7 +4932,7 @@
       <c r="F176" s="14"/>
       <c r="G176" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
@@ -4224,7 +4944,7 @@
       <c r="F177" s="13"/>
       <c r="G177" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -4236,7 +4956,7 @@
       <c r="F178" s="14"/>
       <c r="G178" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
@@ -4248,7 +4968,7 @@
       <c r="F179" s="13"/>
       <c r="G179" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -4260,7 +4980,7 @@
       <c r="F180" s="14"/>
       <c r="G180" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I180" s="21"/>
     </row>
@@ -4273,7 +4993,7 @@
       <c r="F181" s="13"/>
       <c r="G181" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
@@ -4285,7 +5005,7 @@
       <c r="F182" s="14"/>
       <c r="G182" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -4297,7 +5017,7 @@
       <c r="F183" s="13"/>
       <c r="G183" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
@@ -4309,7 +5029,7 @@
       <c r="F184" s="14"/>
       <c r="G184" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
@@ -4321,7 +5041,7 @@
       <c r="F185" s="13"/>
       <c r="G185" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
@@ -4333,7 +5053,7 @@
       <c r="F186" s="14"/>
       <c r="G186" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
@@ -4345,7 +5065,7 @@
       <c r="F187" s="13"/>
       <c r="G187" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -4357,7 +5077,7 @@
       <c r="F188" s="14"/>
       <c r="G188" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
@@ -4369,7 +5089,7 @@
       <c r="F189" s="13"/>
       <c r="G189" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
@@ -4381,7 +5101,7 @@
       <c r="F190" s="14"/>
       <c r="G190" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
@@ -4393,7 +5113,7 @@
       <c r="F191" s="13"/>
       <c r="G191" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
@@ -4405,7 +5125,7 @@
       <c r="F192" s="14"/>
       <c r="G192" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
@@ -4417,7 +5137,7 @@
       <c r="F193" s="13"/>
       <c r="G193" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
@@ -4429,7 +5149,7 @@
       <c r="F194" s="13"/>
       <c r="G194" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -4441,7 +5161,7 @@
       <c r="F195" s="14"/>
       <c r="G195" s="14">
         <f>G194+E195-F195</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
@@ -4453,7 +5173,7 @@
       <c r="F196" s="13"/>
       <c r="G196" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
@@ -4465,7 +5185,7 @@
       <c r="F197" s="14"/>
       <c r="G197" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
@@ -4477,7 +5197,7 @@
       <c r="F198" s="13"/>
       <c r="G198" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
@@ -4489,7 +5209,7 @@
       <c r="F199" s="14"/>
       <c r="G199" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -4501,7 +5221,7 @@
       <c r="F200" s="13"/>
       <c r="G200" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
@@ -4513,7 +5233,7 @@
       <c r="F201" s="14"/>
       <c r="G201" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I201" s="21"/>
     </row>
@@ -4526,7 +5246,7 @@
       <c r="F202" s="13"/>
       <c r="G202" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
@@ -4538,7 +5258,7 @@
       <c r="F203" s="14"/>
       <c r="G203" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -4550,7 +5270,7 @@
       <c r="F204" s="13"/>
       <c r="G204" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
@@ -4562,7 +5282,7 @@
       <c r="F205" s="14"/>
       <c r="G205" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
@@ -4574,7 +5294,7 @@
       <c r="F206" s="13"/>
       <c r="G206" s="13">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
@@ -4586,7 +5306,7 @@
       <c r="F207" s="14"/>
       <c r="G207" s="14">
         <f t="shared" si="4"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
@@ -4598,7 +5318,7 @@
       <c r="F208" s="13"/>
       <c r="G208" s="13">
         <f t="shared" ref="G208:G271" si="5">G207+E208-F208</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
@@ -4610,7 +5330,7 @@
       <c r="F209" s="14"/>
       <c r="G209" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -4622,7 +5342,7 @@
       <c r="F210" s="13"/>
       <c r="G210" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
@@ -4634,7 +5354,7 @@
       <c r="F211" s="14"/>
       <c r="G211" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
@@ -4646,7 +5366,7 @@
       <c r="F212" s="13"/>
       <c r="G212" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
@@ -4658,7 +5378,7 @@
       <c r="F213" s="13"/>
       <c r="G213" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
@@ -4670,7 +5390,7 @@
       <c r="F214" s="13"/>
       <c r="G214" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
@@ -4682,7 +5402,7 @@
       <c r="F215" s="14"/>
       <c r="G215" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -4694,7 +5414,7 @@
       <c r="F216" s="13"/>
       <c r="G216" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -4706,7 +5426,7 @@
       <c r="F217" s="14"/>
       <c r="G217" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
@@ -4718,7 +5438,7 @@
       <c r="F218" s="13"/>
       <c r="G218" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -4730,7 +5450,7 @@
       <c r="F219" s="14"/>
       <c r="G219" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -4742,7 +5462,7 @@
       <c r="F220" s="13"/>
       <c r="G220" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -4754,7 +5474,7 @@
       <c r="F221" s="14"/>
       <c r="G221" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -4766,7 +5486,7 @@
       <c r="F222" s="13"/>
       <c r="G222" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -4778,7 +5498,7 @@
       <c r="F223" s="14"/>
       <c r="G223" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -4790,7 +5510,7 @@
       <c r="F224" s="13"/>
       <c r="G224" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -4802,7 +5522,7 @@
       <c r="F225" s="14"/>
       <c r="G225" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -4814,7 +5534,7 @@
       <c r="F226" s="13"/>
       <c r="G226" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -4826,7 +5546,7 @@
       <c r="F227" s="14"/>
       <c r="G227" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -4838,7 +5558,7 @@
       <c r="F228" s="13"/>
       <c r="G228" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -4850,7 +5570,7 @@
       <c r="F229" s="14"/>
       <c r="G229" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -4862,7 +5582,7 @@
       <c r="F230" s="13"/>
       <c r="G230" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -4874,7 +5594,7 @@
       <c r="F231" s="14"/>
       <c r="G231" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -4886,7 +5606,7 @@
       <c r="F232" s="13"/>
       <c r="G232" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -4898,7 +5618,7 @@
       <c r="F233" s="14"/>
       <c r="G233" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -4910,7 +5630,7 @@
       <c r="F234" s="13"/>
       <c r="G234" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -4922,7 +5642,7 @@
       <c r="F235" s="14"/>
       <c r="G235" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -4934,7 +5654,7 @@
       <c r="F236" s="13"/>
       <c r="G236" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -4946,7 +5666,7 @@
       <c r="F237" s="14"/>
       <c r="G237" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -4958,7 +5678,7 @@
       <c r="F238" s="13"/>
       <c r="G238" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -4970,7 +5690,7 @@
       <c r="F239" s="14"/>
       <c r="G239" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -4982,7 +5702,7 @@
       <c r="F240" s="13"/>
       <c r="G240" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -4994,7 +5714,7 @@
       <c r="F241" s="14"/>
       <c r="G241" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -5006,7 +5726,7 @@
       <c r="F242" s="13"/>
       <c r="G242" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -5018,7 +5738,7 @@
       <c r="F243" s="14"/>
       <c r="G243" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -5030,7 +5750,7 @@
       <c r="F244" s="13"/>
       <c r="G244" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -5042,7 +5762,7 @@
       <c r="F245" s="14"/>
       <c r="G245" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -5054,7 +5774,7 @@
       <c r="F246" s="13"/>
       <c r="G246" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -5066,7 +5786,7 @@
       <c r="F247" s="14"/>
       <c r="G247" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -5078,7 +5798,7 @@
       <c r="F248" s="13"/>
       <c r="G248" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -5090,7 +5810,7 @@
       <c r="F249" s="14"/>
       <c r="G249" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -5102,7 +5822,7 @@
       <c r="F250" s="13"/>
       <c r="G250" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -5114,7 +5834,7 @@
       <c r="F251" s="14"/>
       <c r="G251" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -5126,7 +5846,7 @@
       <c r="F252" s="13"/>
       <c r="G252" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -5138,7 +5858,7 @@
       <c r="F253" s="14"/>
       <c r="G253" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -5150,7 +5870,7 @@
       <c r="F254" s="13"/>
       <c r="G254" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -5162,7 +5882,7 @@
       <c r="F255" s="14"/>
       <c r="G255" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -5174,7 +5894,7 @@
       <c r="F256" s="13"/>
       <c r="G256" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -5186,7 +5906,7 @@
       <c r="F257" s="14"/>
       <c r="G257" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -5198,7 +5918,7 @@
       <c r="F258" s="13"/>
       <c r="G258" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -5210,7 +5930,7 @@
       <c r="F259" s="14"/>
       <c r="G259" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -5222,7 +5942,7 @@
       <c r="F260" s="13"/>
       <c r="G260" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -5234,7 +5954,7 @@
       <c r="F261" s="14"/>
       <c r="G261" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -5246,7 +5966,7 @@
       <c r="F262" s="13"/>
       <c r="G262" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -5258,7 +5978,7 @@
       <c r="F263" s="14"/>
       <c r="G263" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -5270,7 +5990,7 @@
       <c r="F264" s="13"/>
       <c r="G264" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -5282,7 +6002,7 @@
       <c r="F265" s="14"/>
       <c r="G265" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -5294,7 +6014,7 @@
       <c r="F266" s="13"/>
       <c r="G266" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -5306,7 +6026,7 @@
       <c r="F267" s="14"/>
       <c r="G267" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -5318,7 +6038,7 @@
       <c r="F268" s="13"/>
       <c r="G268" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -5330,7 +6050,7 @@
       <c r="F269" s="14"/>
       <c r="G269" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -5342,7 +6062,7 @@
       <c r="F270" s="13"/>
       <c r="G270" s="13">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -5354,7 +6074,7 @@
       <c r="F271" s="14"/>
       <c r="G271" s="14">
         <f t="shared" si="5"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -5366,7 +6086,7 @@
       <c r="F272" s="13"/>
       <c r="G272" s="13">
         <f t="shared" ref="G272:G335" si="6">G271+E272-F272</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
@@ -5378,7 +6098,7 @@
       <c r="F273" s="14"/>
       <c r="G273" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
@@ -5390,7 +6110,7 @@
       <c r="F274" s="13"/>
       <c r="G274" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
@@ -5402,7 +6122,7 @@
       <c r="F275" s="14"/>
       <c r="G275" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I275" s="21"/>
     </row>
@@ -5415,7 +6135,7 @@
       <c r="F276" s="13"/>
       <c r="G276" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
@@ -5427,7 +6147,7 @@
       <c r="F277" s="14"/>
       <c r="G277" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I277" s="21"/>
     </row>
@@ -5440,7 +6160,7 @@
       <c r="F278" s="13"/>
       <c r="G278" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
@@ -5452,7 +6172,7 @@
       <c r="F279" s="14"/>
       <c r="G279" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
@@ -5464,7 +6184,7 @@
       <c r="F280" s="13"/>
       <c r="G280" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
@@ -5476,7 +6196,7 @@
       <c r="F281" s="14"/>
       <c r="G281" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
@@ -5488,7 +6208,7 @@
       <c r="F282" s="13"/>
       <c r="G282" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
@@ -5500,7 +6220,7 @@
       <c r="F283" s="14"/>
       <c r="G283" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
@@ -5512,7 +6232,7 @@
       <c r="F284" s="13"/>
       <c r="G284" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
@@ -5524,7 +6244,7 @@
       <c r="F285" s="14"/>
       <c r="G285" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
@@ -5536,7 +6256,7 @@
       <c r="F286" s="13"/>
       <c r="G286" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
@@ -5548,7 +6268,7 @@
       <c r="F287" s="14"/>
       <c r="G287" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
@@ -5560,7 +6280,7 @@
       <c r="F288" s="13"/>
       <c r="G288" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I288" s="21"/>
     </row>
@@ -5573,7 +6293,7 @@
       <c r="F289" s="14"/>
       <c r="G289" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -5585,7 +6305,7 @@
       <c r="F290" s="13"/>
       <c r="G290" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -5597,7 +6317,7 @@
       <c r="F291" s="14"/>
       <c r="G291" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -5609,7 +6329,7 @@
       <c r="F292" s="13"/>
       <c r="G292" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -5621,7 +6341,7 @@
       <c r="F293" s="14"/>
       <c r="G293" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -5633,7 +6353,7 @@
       <c r="F294" s="13"/>
       <c r="G294" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -5645,7 +6365,7 @@
       <c r="F295" s="14"/>
       <c r="G295" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -5657,7 +6377,7 @@
       <c r="F296" s="13"/>
       <c r="G296" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -5669,7 +6389,7 @@
       <c r="F297" s="14"/>
       <c r="G297" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -5681,7 +6401,7 @@
       <c r="F298" s="13"/>
       <c r="G298" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -5693,7 +6413,7 @@
       <c r="F299" s="14"/>
       <c r="G299" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -5705,7 +6425,7 @@
       <c r="F300" s="13"/>
       <c r="G300" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -5717,7 +6437,7 @@
       <c r="F301" s="14"/>
       <c r="G301" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -5729,7 +6449,7 @@
       <c r="F302" s="13"/>
       <c r="G302" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -5741,7 +6461,7 @@
       <c r="F303" s="14"/>
       <c r="G303" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -5753,7 +6473,7 @@
       <c r="F304" s="13"/>
       <c r="G304" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -5765,7 +6485,7 @@
       <c r="F305" s="14"/>
       <c r="G305" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -5777,7 +6497,7 @@
       <c r="F306" s="13"/>
       <c r="G306" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -5789,7 +6509,7 @@
       <c r="F307" s="14"/>
       <c r="G307" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -5801,7 +6521,7 @@
       <c r="F308" s="13"/>
       <c r="G308" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -5813,7 +6533,7 @@
       <c r="F309" s="14"/>
       <c r="G309" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -5825,7 +6545,7 @@
       <c r="F310" s="13"/>
       <c r="G310" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -5837,7 +6557,7 @@
       <c r="F311" s="14"/>
       <c r="G311" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -5849,7 +6569,7 @@
       <c r="F312" s="13"/>
       <c r="G312" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -5861,7 +6581,7 @@
       <c r="F313" s="14"/>
       <c r="G313" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -5873,7 +6593,7 @@
       <c r="F314" s="13"/>
       <c r="G314" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -5885,7 +6605,7 @@
       <c r="F315" s="14"/>
       <c r="G315" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -5897,7 +6617,7 @@
       <c r="F316" s="13"/>
       <c r="G316" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -5909,7 +6629,7 @@
       <c r="F317" s="14"/>
       <c r="G317" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -5921,7 +6641,7 @@
       <c r="F318" s="13"/>
       <c r="G318" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -5933,7 +6653,7 @@
       <c r="F319" s="14"/>
       <c r="G319" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -5945,7 +6665,7 @@
       <c r="F320" s="13"/>
       <c r="G320" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
@@ -5957,7 +6677,7 @@
       <c r="F321" s="14"/>
       <c r="G321" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
@@ -5969,7 +6689,7 @@
       <c r="F322" s="13"/>
       <c r="G322" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
@@ -5981,7 +6701,7 @@
       <c r="F323" s="14"/>
       <c r="G323" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
@@ -5993,7 +6713,7 @@
       <c r="F324" s="13"/>
       <c r="G324" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
@@ -6005,7 +6725,7 @@
       <c r="F325" s="14"/>
       <c r="G325" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
@@ -6017,7 +6737,7 @@
       <c r="F326" s="13"/>
       <c r="G326" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
@@ -6029,7 +6749,7 @@
       <c r="F327" s="14"/>
       <c r="G327" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
@@ -6041,7 +6761,7 @@
       <c r="F328" s="13"/>
       <c r="G328" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
@@ -6053,7 +6773,7 @@
       <c r="F329" s="14"/>
       <c r="G329" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
@@ -6065,7 +6785,7 @@
       <c r="F330" s="13"/>
       <c r="G330" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
@@ -6077,7 +6797,7 @@
       <c r="F331" s="14"/>
       <c r="G331" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -6089,7 +6809,7 @@
       <c r="F332" s="13"/>
       <c r="G332" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
@@ -6101,7 +6821,7 @@
       <c r="F333" s="14"/>
       <c r="G333" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I333" s="21"/>
     </row>
@@ -6114,7 +6834,7 @@
       <c r="F334" s="13"/>
       <c r="G334" s="13">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
@@ -6126,7 +6846,7 @@
       <c r="F335" s="14"/>
       <c r="G335" s="14">
         <f t="shared" si="6"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
@@ -6138,7 +6858,7 @@
       <c r="F336" s="13"/>
       <c r="G336" s="13">
         <f t="shared" ref="G336:G399" si="7">G335+E336-F336</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
@@ -6150,7 +6870,7 @@
       <c r="F337" s="14"/>
       <c r="G337" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
@@ -6162,7 +6882,7 @@
       <c r="F338" s="13"/>
       <c r="G338" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
@@ -6174,7 +6894,7 @@
       <c r="F339" s="14"/>
       <c r="G339" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
@@ -6186,7 +6906,7 @@
       <c r="F340" s="13"/>
       <c r="G340" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="J340" s="21"/>
     </row>
@@ -6199,7 +6919,7 @@
       <c r="F341" s="14"/>
       <c r="G341" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
@@ -6211,7 +6931,7 @@
       <c r="F342" s="13"/>
       <c r="G342" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
@@ -6223,7 +6943,7 @@
       <c r="F343" s="14"/>
       <c r="G343" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
@@ -6235,7 +6955,7 @@
       <c r="F344" s="13"/>
       <c r="G344" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
@@ -6247,7 +6967,7 @@
       <c r="F345" s="14"/>
       <c r="G345" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
@@ -6259,7 +6979,7 @@
       <c r="F346" s="13"/>
       <c r="G346" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
@@ -6271,7 +6991,7 @@
       <c r="F347" s="14"/>
       <c r="G347" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
@@ -6283,7 +7003,7 @@
       <c r="F348" s="13"/>
       <c r="G348" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
@@ -6295,7 +7015,7 @@
       <c r="F349" s="14"/>
       <c r="G349" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
@@ -6307,7 +7027,7 @@
       <c r="F350" s="13"/>
       <c r="G350" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
@@ -6319,7 +7039,7 @@
       <c r="F351" s="14"/>
       <c r="G351" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
@@ -6331,7 +7051,7 @@
       <c r="F352" s="13"/>
       <c r="G352" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
@@ -6343,7 +7063,7 @@
       <c r="F353" s="14"/>
       <c r="G353" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
@@ -6355,7 +7075,7 @@
       <c r="F354" s="13"/>
       <c r="G354" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="J354" s="21"/>
     </row>
@@ -6368,7 +7088,7 @@
       <c r="F355" s="14"/>
       <c r="G355" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
@@ -6380,7 +7100,7 @@
       <c r="F356" s="13"/>
       <c r="G356" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
@@ -6392,7 +7112,7 @@
       <c r="F357" s="14"/>
       <c r="G357" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
@@ -6404,7 +7124,7 @@
       <c r="F358" s="13"/>
       <c r="G358" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
@@ -6416,7 +7136,7 @@
       <c r="F359" s="14"/>
       <c r="G359" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
@@ -6428,7 +7148,7 @@
       <c r="F360" s="13"/>
       <c r="G360" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
@@ -6440,7 +7160,7 @@
       <c r="F361" s="14"/>
       <c r="G361" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
@@ -6452,7 +7172,7 @@
       <c r="F362" s="13"/>
       <c r="G362" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
@@ -6464,7 +7184,7 @@
       <c r="F363" s="14"/>
       <c r="G363" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
@@ -6476,7 +7196,7 @@
       <c r="F364" s="13"/>
       <c r="G364" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
@@ -6488,7 +7208,7 @@
       <c r="F365" s="14"/>
       <c r="G365" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
@@ -6500,7 +7220,7 @@
       <c r="F366" s="13"/>
       <c r="G366" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
@@ -6512,7 +7232,7 @@
       <c r="F367" s="14"/>
       <c r="G367" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
@@ -6524,7 +7244,7 @@
       <c r="F368" s="13"/>
       <c r="G368" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
@@ -6536,7 +7256,7 @@
       <c r="F369" s="14"/>
       <c r="G369" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
@@ -6548,7 +7268,7 @@
       <c r="F370" s="13"/>
       <c r="G370" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
@@ -6560,7 +7280,7 @@
       <c r="F371" s="14"/>
       <c r="G371" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
@@ -6572,7 +7292,7 @@
       <c r="F372" s="13"/>
       <c r="G372" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
@@ -6584,7 +7304,7 @@
       <c r="F373" s="14"/>
       <c r="G373" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
@@ -6596,7 +7316,7 @@
       <c r="F374" s="13"/>
       <c r="G374" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
@@ -6608,7 +7328,7 @@
       <c r="F375" s="14"/>
       <c r="G375" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
@@ -6620,7 +7340,7 @@
       <c r="F376" s="13"/>
       <c r="G376" s="13">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
@@ -6632,7 +7352,7 @@
       <c r="F377" s="14"/>
       <c r="G377" s="14">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
@@ -6644,7 +7364,7 @@
       <c r="F378" s="18"/>
       <c r="G378" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
@@ -6656,7 +7376,7 @@
       <c r="F379" s="19"/>
       <c r="G379" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
@@ -6668,7 +7388,7 @@
       <c r="F380" s="18"/>
       <c r="G380" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
@@ -6680,7 +7400,7 @@
       <c r="F381" s="19"/>
       <c r="G381" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
@@ -6692,7 +7412,7 @@
       <c r="F382" s="18"/>
       <c r="G382" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
@@ -6704,7 +7424,7 @@
       <c r="F383" s="19"/>
       <c r="G383" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
@@ -6716,7 +7436,7 @@
       <c r="F384" s="18"/>
       <c r="G384" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
@@ -6728,7 +7448,7 @@
       <c r="F385" s="19"/>
       <c r="G385" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
@@ -6740,7 +7460,7 @@
       <c r="F386" s="18"/>
       <c r="G386" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
@@ -6752,7 +7472,7 @@
       <c r="F387" s="19"/>
       <c r="G387" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
@@ -6764,7 +7484,7 @@
       <c r="F388" s="18"/>
       <c r="G388" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
@@ -6776,7 +7496,7 @@
       <c r="F389" s="19"/>
       <c r="G389" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
@@ -6788,7 +7508,7 @@
       <c r="F390" s="18"/>
       <c r="G390" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
@@ -6800,7 +7520,7 @@
       <c r="F391" s="19"/>
       <c r="G391" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
@@ -6812,7 +7532,7 @@
       <c r="F392" s="18"/>
       <c r="G392" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
@@ -6824,7 +7544,7 @@
       <c r="F393" s="19"/>
       <c r="G393" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
@@ -6836,7 +7556,7 @@
       <c r="F394" s="18"/>
       <c r="G394" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
@@ -6848,7 +7568,7 @@
       <c r="F395" s="19"/>
       <c r="G395" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
@@ -6860,7 +7580,7 @@
       <c r="F396" s="18"/>
       <c r="G396" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
@@ -6872,7 +7592,7 @@
       <c r="F397" s="19"/>
       <c r="G397" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
@@ -6884,7 +7604,7 @@
       <c r="F398" s="18"/>
       <c r="G398" s="18">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
@@ -6896,7 +7616,7 @@
       <c r="F399" s="19"/>
       <c r="G399" s="19">
         <f t="shared" si="7"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
@@ -6908,7 +7628,7 @@
       <c r="F400" s="18"/>
       <c r="G400" s="18">
         <f t="shared" ref="G400:G463" si="8">G399+E400-F400</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
@@ -6920,7 +7640,7 @@
       <c r="F401" s="19"/>
       <c r="G401" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -6932,7 +7652,7 @@
       <c r="F402" s="18"/>
       <c r="G402" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I402" s="21"/>
     </row>
@@ -6945,7 +7665,7 @@
       <c r="F403" s="19"/>
       <c r="G403" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I403" s="21"/>
     </row>
@@ -6958,7 +7678,7 @@
       <c r="F404" s="18"/>
       <c r="G404" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="I404" s="21"/>
     </row>
@@ -6971,7 +7691,7 @@
       <c r="F405" s="19"/>
       <c r="G405" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
@@ -6983,7 +7703,7 @@
       <c r="F406" s="18"/>
       <c r="G406" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.3">
@@ -6995,7 +7715,7 @@
       <c r="F407" s="19"/>
       <c r="G407" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
@@ -7007,7 +7727,7 @@
       <c r="F408" s="18"/>
       <c r="G408" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
@@ -7019,7 +7739,7 @@
       <c r="F409" s="19"/>
       <c r="G409" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
@@ -7031,7 +7751,7 @@
       <c r="F410" s="18"/>
       <c r="G410" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
@@ -7043,7 +7763,7 @@
       <c r="F411" s="19"/>
       <c r="G411" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
@@ -7055,7 +7775,7 @@
       <c r="F412" s="18"/>
       <c r="G412" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
@@ -7067,7 +7787,7 @@
       <c r="F413" s="19"/>
       <c r="G413" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
@@ -7079,7 +7799,7 @@
       <c r="F414" s="18"/>
       <c r="G414" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
@@ -7091,7 +7811,7 @@
       <c r="F415" s="19"/>
       <c r="G415" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
@@ -7103,7 +7823,7 @@
       <c r="F416" s="18"/>
       <c r="G416" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
@@ -7115,7 +7835,7 @@
       <c r="F417" s="19"/>
       <c r="G417" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
@@ -7127,7 +7847,7 @@
       <c r="F418" s="18"/>
       <c r="G418" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
@@ -7139,7 +7859,7 @@
       <c r="F419" s="19"/>
       <c r="G419" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
@@ -7151,7 +7871,7 @@
       <c r="F420" s="18"/>
       <c r="G420" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
@@ -7163,7 +7883,7 @@
       <c r="F421" s="19"/>
       <c r="G421" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
@@ -7175,7 +7895,7 @@
       <c r="F422" s="18"/>
       <c r="G422" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
@@ -7187,7 +7907,7 @@
       <c r="F423" s="19"/>
       <c r="G423" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
@@ -7199,7 +7919,7 @@
       <c r="F424" s="18"/>
       <c r="G424" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
@@ -7211,7 +7931,7 @@
       <c r="F425" s="19"/>
       <c r="G425" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
@@ -7223,7 +7943,7 @@
       <c r="F426" s="18"/>
       <c r="G426" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
@@ -7235,7 +7955,7 @@
       <c r="F427" s="19"/>
       <c r="G427" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
@@ -7247,7 +7967,7 @@
       <c r="F428" s="18"/>
       <c r="G428" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
@@ -7259,7 +7979,7 @@
       <c r="F429" s="19"/>
       <c r="G429" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
@@ -7271,7 +7991,7 @@
       <c r="F430" s="18"/>
       <c r="G430" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
@@ -7283,7 +8003,7 @@
       <c r="F431" s="19"/>
       <c r="G431" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
@@ -7295,7 +8015,7 @@
       <c r="F432" s="18"/>
       <c r="G432" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
@@ -7307,7 +8027,7 @@
       <c r="F433" s="19"/>
       <c r="G433" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
@@ -7319,7 +8039,7 @@
       <c r="F434" s="18"/>
       <c r="G434" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
@@ -7331,7 +8051,7 @@
       <c r="F435" s="19"/>
       <c r="G435" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
@@ -7343,7 +8063,7 @@
       <c r="F436" s="18"/>
       <c r="G436" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
@@ -7355,7 +8075,7 @@
       <c r="F437" s="19"/>
       <c r="G437" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
@@ -7367,7 +8087,7 @@
       <c r="F438" s="18"/>
       <c r="G438" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
@@ -7379,7 +8099,7 @@
       <c r="F439" s="19"/>
       <c r="G439" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
@@ -7391,7 +8111,7 @@
       <c r="F440" s="18"/>
       <c r="G440" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
@@ -7403,7 +8123,7 @@
       <c r="F441" s="19"/>
       <c r="G441" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
@@ -7415,7 +8135,7 @@
       <c r="F442" s="18"/>
       <c r="G442" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
@@ -7427,7 +8147,7 @@
       <c r="F443" s="19"/>
       <c r="G443" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
@@ -7439,7 +8159,7 @@
       <c r="F444" s="18"/>
       <c r="G444" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
@@ -7451,7 +8171,7 @@
       <c r="F445" s="19"/>
       <c r="G445" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
@@ -7463,7 +8183,7 @@
       <c r="F446" s="18"/>
       <c r="G446" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
@@ -7475,7 +8195,7 @@
       <c r="F447" s="19"/>
       <c r="G447" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
@@ -7487,7 +8207,7 @@
       <c r="F448" s="18"/>
       <c r="G448" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
@@ -7499,7 +8219,7 @@
       <c r="F449" s="19"/>
       <c r="G449" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
@@ -7511,7 +8231,7 @@
       <c r="F450" s="18"/>
       <c r="G450" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
@@ -7523,7 +8243,7 @@
       <c r="F451" s="19"/>
       <c r="G451" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
@@ -7535,7 +8255,7 @@
       <c r="F452" s="18"/>
       <c r="G452" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
@@ -7547,7 +8267,7 @@
       <c r="F453" s="19"/>
       <c r="G453" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
@@ -7559,7 +8279,7 @@
       <c r="F454" s="18"/>
       <c r="G454" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
@@ -7571,7 +8291,7 @@
       <c r="F455" s="19"/>
       <c r="G455" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
@@ -7583,7 +8303,7 @@
       <c r="F456" s="18"/>
       <c r="G456" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
@@ -7595,7 +8315,7 @@
       <c r="F457" s="19"/>
       <c r="G457" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
@@ -7607,7 +8327,7 @@
       <c r="F458" s="18"/>
       <c r="G458" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
@@ -7619,7 +8339,7 @@
       <c r="F459" s="19"/>
       <c r="G459" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
@@ -7631,7 +8351,7 @@
       <c r="F460" s="18"/>
       <c r="G460" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
@@ -7643,7 +8363,7 @@
       <c r="F461" s="19"/>
       <c r="G461" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
@@ -7655,7 +8375,7 @@
       <c r="F462" s="18"/>
       <c r="G462" s="18">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
@@ -7667,7 +8387,7 @@
       <c r="F463" s="19"/>
       <c r="G463" s="19">
         <f t="shared" si="8"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
@@ -7679,7 +8399,7 @@
       <c r="F464" s="18"/>
       <c r="G464" s="18">
         <f t="shared" ref="G464:G527" si="9">G463+E464-F464</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
@@ -7691,7 +8411,7 @@
       <c r="F465" s="19"/>
       <c r="G465" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
@@ -7703,7 +8423,7 @@
       <c r="F466" s="18"/>
       <c r="G466" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
@@ -7715,7 +8435,7 @@
       <c r="F467" s="19"/>
       <c r="G467" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
@@ -7727,7 +8447,7 @@
       <c r="F468" s="18"/>
       <c r="G468" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
@@ -7739,7 +8459,7 @@
       <c r="F469" s="19"/>
       <c r="G469" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.3">
@@ -7751,7 +8471,7 @@
       <c r="F470" s="18"/>
       <c r="G470" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
@@ -7763,7 +8483,7 @@
       <c r="F471" s="19"/>
       <c r="G471" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
@@ -7775,7 +8495,7 @@
       <c r="F472" s="18"/>
       <c r="G472" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
@@ -7787,7 +8507,7 @@
       <c r="F473" s="19"/>
       <c r="G473" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="J473" s="21"/>
     </row>
@@ -7800,7 +8520,7 @@
       <c r="F474" s="18"/>
       <c r="G474" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
@@ -7812,7 +8532,7 @@
       <c r="F475" s="19"/>
       <c r="G475" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
@@ -7824,7 +8544,7 @@
       <c r="F476" s="18"/>
       <c r="G476" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
@@ -7836,7 +8556,7 @@
       <c r="F477" s="19"/>
       <c r="G477" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
@@ -7848,7 +8568,7 @@
       <c r="F478" s="18"/>
       <c r="G478" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
@@ -7860,7 +8580,7 @@
       <c r="F479" s="19"/>
       <c r="G479" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
@@ -7872,7 +8592,7 @@
       <c r="F480" s="18"/>
       <c r="G480" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
@@ -7884,7 +8604,7 @@
       <c r="F481" s="19"/>
       <c r="G481" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
@@ -7896,7 +8616,7 @@
       <c r="F482" s="18"/>
       <c r="G482" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
@@ -7908,7 +8628,7 @@
       <c r="F483" s="19"/>
       <c r="G483" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
@@ -7920,7 +8640,7 @@
       <c r="F484" s="18"/>
       <c r="G484" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
@@ -7932,7 +8652,7 @@
       <c r="F485" s="19"/>
       <c r="G485" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
@@ -7944,7 +8664,7 @@
       <c r="F486" s="18"/>
       <c r="G486" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
@@ -7956,7 +8676,7 @@
       <c r="F487" s="19"/>
       <c r="G487" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.3">
@@ -7968,7 +8688,7 @@
       <c r="F488" s="18"/>
       <c r="G488" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
@@ -7980,7 +8700,7 @@
       <c r="F489" s="19"/>
       <c r="G489" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="J489" s="21"/>
     </row>
@@ -7993,7 +8713,7 @@
       <c r="F490" s="18"/>
       <c r="G490" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.3">
@@ -8005,7 +8725,7 @@
       <c r="F491" s="19"/>
       <c r="G491" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.3">
@@ -8017,7 +8737,7 @@
       <c r="F492" s="18"/>
       <c r="G492" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.3">
@@ -8029,7 +8749,7 @@
       <c r="F493" s="19"/>
       <c r="G493" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.3">
@@ -8041,7 +8761,7 @@
       <c r="F494" s="18"/>
       <c r="G494" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.3">
@@ -8053,7 +8773,7 @@
       <c r="F495" s="19"/>
       <c r="G495" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.3">
@@ -8065,7 +8785,7 @@
       <c r="F496" s="18"/>
       <c r="G496" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
@@ -8077,7 +8797,7 @@
       <c r="F497" s="19"/>
       <c r="G497" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
@@ -8089,7 +8809,7 @@
       <c r="F498" s="18"/>
       <c r="G498" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
@@ -8101,7 +8821,7 @@
       <c r="F499" s="19"/>
       <c r="G499" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
@@ -8113,7 +8833,7 @@
       <c r="F500" s="18"/>
       <c r="G500" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
@@ -8125,7 +8845,7 @@
       <c r="F501" s="19"/>
       <c r="G501" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
@@ -8137,7 +8857,7 @@
       <c r="F502" s="18"/>
       <c r="G502" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
@@ -8149,7 +8869,7 @@
       <c r="F503" s="19"/>
       <c r="G503" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
@@ -8161,7 +8881,7 @@
       <c r="F504" s="18"/>
       <c r="G504" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
@@ -8173,7 +8893,7 @@
       <c r="F505" s="19"/>
       <c r="G505" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
@@ -8185,7 +8905,7 @@
       <c r="F506" s="18"/>
       <c r="G506" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
@@ -8197,7 +8917,7 @@
       <c r="F507" s="19"/>
       <c r="G507" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
@@ -8209,7 +8929,7 @@
       <c r="F508" s="18"/>
       <c r="G508" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
@@ -8221,7 +8941,7 @@
       <c r="F509" s="19"/>
       <c r="G509" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
@@ -8233,7 +8953,7 @@
       <c r="F510" s="18"/>
       <c r="G510" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
@@ -8245,7 +8965,7 @@
       <c r="F511" s="19"/>
       <c r="G511" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
@@ -8257,7 +8977,7 @@
       <c r="F512" s="18"/>
       <c r="G512" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
@@ -8269,7 +8989,7 @@
       <c r="F513" s="19"/>
       <c r="G513" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
@@ -8281,7 +9001,7 @@
       <c r="F514" s="18"/>
       <c r="G514" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
@@ -8293,7 +9013,7 @@
       <c r="F515" s="19"/>
       <c r="G515" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
@@ -8305,7 +9025,7 @@
       <c r="F516" s="18"/>
       <c r="G516" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
@@ -8317,7 +9037,7 @@
       <c r="F517" s="19"/>
       <c r="G517" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
@@ -8329,7 +9049,7 @@
       <c r="F518" s="18"/>
       <c r="G518" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
@@ -8341,7 +9061,7 @@
       <c r="F519" s="19"/>
       <c r="G519" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
@@ -8353,7 +9073,7 @@
       <c r="F520" s="18"/>
       <c r="G520" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
@@ -8365,7 +9085,7 @@
       <c r="F521" s="19"/>
       <c r="G521" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
@@ -8377,7 +9097,7 @@
       <c r="F522" s="18"/>
       <c r="G522" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
@@ -8389,7 +9109,7 @@
       <c r="F523" s="19"/>
       <c r="G523" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
@@ -8401,7 +9121,7 @@
       <c r="F524" s="18"/>
       <c r="G524" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
@@ -8413,7 +9133,7 @@
       <c r="F525" s="19"/>
       <c r="G525" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
@@ -8425,7 +9145,7 @@
       <c r="F526" s="18"/>
       <c r="G526" s="18">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
@@ -8437,7 +9157,7 @@
       <c r="F527" s="19"/>
       <c r="G527" s="19">
         <f t="shared" si="9"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
@@ -8449,7 +9169,7 @@
       <c r="F528" s="18"/>
       <c r="G528" s="18">
         <f t="shared" ref="G528:G591" si="10">G527+E528-F528</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.3">
@@ -8461,7 +9181,7 @@
       <c r="F529" s="19"/>
       <c r="G529" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.3">
@@ -8473,7 +9193,7 @@
       <c r="F530" s="18"/>
       <c r="G530" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.3">
@@ -8485,7 +9205,7 @@
       <c r="F531" s="19"/>
       <c r="G531" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.3">
@@ -8497,7 +9217,7 @@
       <c r="F532" s="18"/>
       <c r="G532" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
       <c r="K532" s="21"/>
     </row>
@@ -8510,7 +9230,7 @@
       <c r="F533" s="19"/>
       <c r="G533" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.3">
@@ -8522,7 +9242,7 @@
       <c r="F534" s="18"/>
       <c r="G534" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.3">
@@ -8534,7 +9254,7 @@
       <c r="F535" s="19"/>
       <c r="G535" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.3">
@@ -8546,7 +9266,7 @@
       <c r="F536" s="18"/>
       <c r="G536" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.3">
@@ -8558,7 +9278,7 @@
       <c r="F537" s="19"/>
       <c r="G537" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.3">
@@ -8570,7 +9290,7 @@
       <c r="F538" s="18"/>
       <c r="G538" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.3">
@@ -8582,7 +9302,7 @@
       <c r="F539" s="19"/>
       <c r="G539" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.3">
@@ -8594,7 +9314,7 @@
       <c r="F540" s="18"/>
       <c r="G540" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.3">
@@ -8606,7 +9326,7 @@
       <c r="F541" s="19"/>
       <c r="G541" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.3">
@@ -8618,7 +9338,7 @@
       <c r="F542" s="18"/>
       <c r="G542" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.3">
@@ -8630,7 +9350,7 @@
       <c r="F543" s="19"/>
       <c r="G543" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.3">
@@ -8642,7 +9362,7 @@
       <c r="F544" s="18"/>
       <c r="G544" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
@@ -8654,7 +9374,7 @@
       <c r="F545" s="19"/>
       <c r="G545" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
@@ -8666,7 +9386,7 @@
       <c r="F546" s="18"/>
       <c r="G546" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -8678,7 +9398,7 @@
       <c r="F547" s="19"/>
       <c r="G547" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.3">
@@ -8690,7 +9410,7 @@
       <c r="F548" s="18"/>
       <c r="G548" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
@@ -8702,7 +9422,7 @@
       <c r="F549" s="19"/>
       <c r="G549" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.3">
@@ -8714,7 +9434,7 @@
       <c r="F550" s="18"/>
       <c r="G550" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.3">
@@ -8726,7 +9446,7 @@
       <c r="F551" s="19"/>
       <c r="G551" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
@@ -8738,7 +9458,7 @@
       <c r="F552" s="18"/>
       <c r="G552" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.3">
@@ -8750,7 +9470,7 @@
       <c r="F553" s="19"/>
       <c r="G553" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.3">
@@ -8762,7 +9482,7 @@
       <c r="F554" s="18"/>
       <c r="G554" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.3">
@@ -8774,7 +9494,7 @@
       <c r="F555" s="19"/>
       <c r="G555" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.3">
@@ -8786,7 +9506,7 @@
       <c r="F556" s="18"/>
       <c r="G556" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
@@ -8798,7 +9518,7 @@
       <c r="F557" s="19"/>
       <c r="G557" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
@@ -8810,7 +9530,7 @@
       <c r="F558" s="18"/>
       <c r="G558" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
@@ -8822,7 +9542,7 @@
       <c r="F559" s="19"/>
       <c r="G559" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.3">
@@ -8834,7 +9554,7 @@
       <c r="F560" s="18"/>
       <c r="G560" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
@@ -8846,7 +9566,7 @@
       <c r="F561" s="19"/>
       <c r="G561" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.3">
@@ -8858,7 +9578,7 @@
       <c r="F562" s="18"/>
       <c r="G562" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.3">
@@ -8870,7 +9590,7 @@
       <c r="F563" s="19"/>
       <c r="G563" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
@@ -8882,7 +9602,7 @@
       <c r="F564" s="18"/>
       <c r="G564" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.3">
@@ -8894,7 +9614,7 @@
       <c r="F565" s="19"/>
       <c r="G565" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.3">
@@ -8906,7 +9626,7 @@
       <c r="F566" s="18"/>
       <c r="G566" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
@@ -8918,7 +9638,7 @@
       <c r="F567" s="19"/>
       <c r="G567" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.3">
@@ -8930,7 +9650,7 @@
       <c r="F568" s="18"/>
       <c r="G568" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
@@ -8942,7 +9662,7 @@
       <c r="F569" s="19"/>
       <c r="G569" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
@@ -8954,7 +9674,7 @@
       <c r="F570" s="18"/>
       <c r="G570" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.3">
@@ -8966,7 +9686,7 @@
       <c r="F571" s="19"/>
       <c r="G571" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
@@ -8978,7 +9698,7 @@
       <c r="F572" s="18"/>
       <c r="G572" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
@@ -8990,7 +9710,7 @@
       <c r="F573" s="19"/>
       <c r="G573" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.3">
@@ -9002,7 +9722,7 @@
       <c r="F574" s="18"/>
       <c r="G574" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
@@ -9014,7 +9734,7 @@
       <c r="F575" s="19"/>
       <c r="G575" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
@@ -9026,7 +9746,7 @@
       <c r="F576" s="18"/>
       <c r="G576" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
@@ -9038,7 +9758,7 @@
       <c r="F577" s="19"/>
       <c r="G577" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.3">
@@ -9050,7 +9770,7 @@
       <c r="F578" s="18"/>
       <c r="G578" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
@@ -9062,7 +9782,7 @@
       <c r="F579" s="19"/>
       <c r="G579" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
@@ -9074,7 +9794,7 @@
       <c r="F580" s="18"/>
       <c r="G580" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
@@ -9086,7 +9806,7 @@
       <c r="F581" s="19"/>
       <c r="G581" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
@@ -9098,7 +9818,7 @@
       <c r="F582" s="18"/>
       <c r="G582" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
@@ -9110,7 +9830,7 @@
       <c r="F583" s="19"/>
       <c r="G583" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
@@ -9122,7 +9842,7 @@
       <c r="F584" s="18"/>
       <c r="G584" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
@@ -9134,7 +9854,7 @@
       <c r="F585" s="19"/>
       <c r="G585" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
@@ -9146,7 +9866,7 @@
       <c r="F586" s="18"/>
       <c r="G586" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
@@ -9158,7 +9878,7 @@
       <c r="F587" s="19"/>
       <c r="G587" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
@@ -9170,7 +9890,7 @@
       <c r="F588" s="18"/>
       <c r="G588" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
@@ -9182,7 +9902,7 @@
       <c r="F589" s="19"/>
       <c r="G589" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
@@ -9194,7 +9914,7 @@
       <c r="F590" s="18"/>
       <c r="G590" s="18">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
@@ -9206,7 +9926,7 @@
       <c r="F591" s="19"/>
       <c r="G591" s="19">
         <f t="shared" si="10"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
@@ -9218,7 +9938,7 @@
       <c r="F592" s="18"/>
       <c r="G592" s="18">
         <f t="shared" ref="G592:G655" si="11">G591+E592-F592</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
@@ -9230,7 +9950,7 @@
       <c r="F593" s="19"/>
       <c r="G593" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
@@ -9242,7 +9962,7 @@
       <c r="F594" s="18"/>
       <c r="G594" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
@@ -9254,7 +9974,7 @@
       <c r="F595" s="19"/>
       <c r="G595" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
@@ -9266,7 +9986,7 @@
       <c r="F596" s="18"/>
       <c r="G596" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
@@ -9278,7 +9998,7 @@
       <c r="F597" s="19"/>
       <c r="G597" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.3">
@@ -9290,7 +10010,7 @@
       <c r="F598" s="18"/>
       <c r="G598" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
@@ -9302,7 +10022,7 @@
       <c r="F599" s="19"/>
       <c r="G599" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.3">
@@ -9314,7 +10034,7 @@
       <c r="F600" s="18"/>
       <c r="G600" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
@@ -9326,7 +10046,7 @@
       <c r="F601" s="19"/>
       <c r="G601" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
@@ -9338,7 +10058,7 @@
       <c r="F602" s="18"/>
       <c r="G602" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
@@ -9350,7 +10070,7 @@
       <c r="F603" s="19"/>
       <c r="G603" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
@@ -9362,7 +10082,7 @@
       <c r="F604" s="18"/>
       <c r="G604" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
@@ -9374,7 +10094,7 @@
       <c r="F605" s="19"/>
       <c r="G605" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
@@ -9386,7 +10106,7 @@
       <c r="F606" s="18"/>
       <c r="G606" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.3">
@@ -9398,7 +10118,7 @@
       <c r="F607" s="19"/>
       <c r="G607" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
@@ -9410,7 +10130,7 @@
       <c r="F608" s="18"/>
       <c r="G608" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
@@ -9422,7 +10142,7 @@
       <c r="F609" s="19"/>
       <c r="G609" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
@@ -9434,7 +10154,7 @@
       <c r="F610" s="18"/>
       <c r="G610" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.3">
@@ -9446,7 +10166,7 @@
       <c r="F611" s="19"/>
       <c r="G611" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
@@ -9458,7 +10178,7 @@
       <c r="F612" s="18"/>
       <c r="G612" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
@@ -9470,7 +10190,7 @@
       <c r="F613" s="19"/>
       <c r="G613" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">
@@ -9482,7 +10202,7 @@
       <c r="F614" s="18"/>
       <c r="G614" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
@@ -9494,7 +10214,7 @@
       <c r="F615" s="19"/>
       <c r="G615" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.3">
@@ -9506,7 +10226,7 @@
       <c r="F616" s="18"/>
       <c r="G616" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.3">
@@ -9518,7 +10238,7 @@
       <c r="F617" s="19"/>
       <c r="G617" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.3">
@@ -9530,7 +10250,7 @@
       <c r="F618" s="18"/>
       <c r="G618" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.3">
@@ -9542,7 +10262,7 @@
       <c r="F619" s="19"/>
       <c r="G619" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.3">
@@ -9554,7 +10274,7 @@
       <c r="F620" s="18"/>
       <c r="G620" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.3">
@@ -9566,7 +10286,7 @@
       <c r="F621" s="19"/>
       <c r="G621" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.3">
@@ -9578,7 +10298,7 @@
       <c r="F622" s="18"/>
       <c r="G622" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.3">
@@ -9590,7 +10310,7 @@
       <c r="F623" s="19"/>
       <c r="G623" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
@@ -9602,7 +10322,7 @@
       <c r="F624" s="18"/>
       <c r="G624" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
@@ -9614,7 +10334,7 @@
       <c r="F625" s="19"/>
       <c r="G625" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.3">
@@ -9626,7 +10346,7 @@
       <c r="F626" s="18"/>
       <c r="G626" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.3">
@@ -9638,7 +10358,7 @@
       <c r="F627" s="19"/>
       <c r="G627" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
@@ -9650,7 +10370,7 @@
       <c r="F628" s="18"/>
       <c r="G628" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.3">
@@ -9662,7 +10382,7 @@
       <c r="F629" s="19"/>
       <c r="G629" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.3">
@@ -9674,7 +10394,7 @@
       <c r="F630" s="18"/>
       <c r="G630" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.3">
@@ -9686,7 +10406,7 @@
       <c r="F631" s="19"/>
       <c r="G631" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.3">
@@ -9698,7 +10418,7 @@
       <c r="F632" s="18"/>
       <c r="G632" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.3">
@@ -9710,7 +10430,7 @@
       <c r="F633" s="19"/>
       <c r="G633" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.3">
@@ -9722,7 +10442,7 @@
       <c r="F634" s="18"/>
       <c r="G634" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.3">
@@ -9734,7 +10454,7 @@
       <c r="F635" s="19"/>
       <c r="G635" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
@@ -9746,7 +10466,7 @@
       <c r="F636" s="18"/>
       <c r="G636" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.3">
@@ -9758,7 +10478,7 @@
       <c r="F637" s="19"/>
       <c r="G637" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.3">
@@ -9770,7 +10490,7 @@
       <c r="F638" s="18"/>
       <c r="G638" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
@@ -9782,7 +10502,7 @@
       <c r="F639" s="19"/>
       <c r="G639" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.3">
@@ -9794,7 +10514,7 @@
       <c r="F640" s="18"/>
       <c r="G640" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.3">
@@ -9806,7 +10526,7 @@
       <c r="F641" s="19"/>
       <c r="G641" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.3">
@@ -9818,7 +10538,7 @@
       <c r="F642" s="18"/>
       <c r="G642" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.3">
@@ -9830,7 +10550,7 @@
       <c r="F643" s="19"/>
       <c r="G643" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,7 +10562,7 @@
       <c r="F644" s="18"/>
       <c r="G644" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.3">
@@ -9854,7 +10574,7 @@
       <c r="F645" s="19"/>
       <c r="G645" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.3">
@@ -9866,7 +10586,7 @@
       <c r="F646" s="18"/>
       <c r="G646" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.3">
@@ -9878,7 +10598,7 @@
       <c r="F647" s="19"/>
       <c r="G647" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.3">
@@ -9890,7 +10610,7 @@
       <c r="F648" s="18"/>
       <c r="G648" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.3">
@@ -9902,7 +10622,7 @@
       <c r="F649" s="19"/>
       <c r="G649" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.3">
@@ -9914,7 +10634,7 @@
       <c r="F650" s="18"/>
       <c r="G650" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.3">
@@ -9926,7 +10646,7 @@
       <c r="F651" s="19"/>
       <c r="G651" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.3">
@@ -9938,7 +10658,7 @@
       <c r="F652" s="18"/>
       <c r="G652" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.3">
@@ -9950,7 +10670,7 @@
       <c r="F653" s="19"/>
       <c r="G653" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.3">
@@ -9962,7 +10682,7 @@
       <c r="F654" s="18"/>
       <c r="G654" s="18">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.3">
@@ -9974,7 +10694,7 @@
       <c r="F655" s="19"/>
       <c r="G655" s="19">
         <f t="shared" si="11"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.3">
@@ -9986,7 +10706,7 @@
       <c r="F656" s="18"/>
       <c r="G656" s="18">
         <f t="shared" ref="G656:G719" si="12">G655+E656-F656</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.3">
@@ -9998,7 +10718,7 @@
       <c r="F657" s="19"/>
       <c r="G657" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.3">
@@ -10010,7 +10730,7 @@
       <c r="F658" s="18"/>
       <c r="G658" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.3">
@@ -10022,7 +10742,7 @@
       <c r="F659" s="19"/>
       <c r="G659" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.3">
@@ -10034,7 +10754,7 @@
       <c r="F660" s="18"/>
       <c r="G660" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.3">
@@ -10046,7 +10766,7 @@
       <c r="F661" s="19"/>
       <c r="G661" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.3">
@@ -10058,7 +10778,7 @@
       <c r="F662" s="18"/>
       <c r="G662" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.3">
@@ -10070,7 +10790,7 @@
       <c r="F663" s="19"/>
       <c r="G663" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.3">
@@ -10082,7 +10802,7 @@
       <c r="F664" s="18"/>
       <c r="G664" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.3">
@@ -10094,7 +10814,7 @@
       <c r="F665" s="19"/>
       <c r="G665" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.3">
@@ -10106,7 +10826,7 @@
       <c r="F666" s="18"/>
       <c r="G666" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,7 +10838,7 @@
       <c r="F667" s="19"/>
       <c r="G667" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.3">
@@ -10130,7 +10850,7 @@
       <c r="F668" s="18"/>
       <c r="G668" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.3">
@@ -10142,7 +10862,7 @@
       <c r="F669" s="19"/>
       <c r="G669" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.3">
@@ -10154,7 +10874,7 @@
       <c r="F670" s="18"/>
       <c r="G670" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.3">
@@ -10166,7 +10886,7 @@
       <c r="F671" s="19"/>
       <c r="G671" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.3">
@@ -10178,7 +10898,7 @@
       <c r="F672" s="18"/>
       <c r="G672" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.3">
@@ -10190,7 +10910,7 @@
       <c r="F673" s="19"/>
       <c r="G673" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.3">
@@ -10202,7 +10922,7 @@
       <c r="F674" s="18"/>
       <c r="G674" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.3">
@@ -10214,7 +10934,7 @@
       <c r="F675" s="19"/>
       <c r="G675" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.3">
@@ -10226,7 +10946,7 @@
       <c r="F676" s="18"/>
       <c r="G676" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.3">
@@ -10238,7 +10958,7 @@
       <c r="F677" s="19"/>
       <c r="G677" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.3">
@@ -10250,7 +10970,7 @@
       <c r="F678" s="18"/>
       <c r="G678" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.3">
@@ -10262,7 +10982,7 @@
       <c r="F679" s="19"/>
       <c r="G679" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.3">
@@ -10274,7 +10994,7 @@
       <c r="F680" s="18"/>
       <c r="G680" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.3">
@@ -10286,7 +11006,7 @@
       <c r="F681" s="19"/>
       <c r="G681" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.3">
@@ -10298,7 +11018,7 @@
       <c r="F682" s="18"/>
       <c r="G682" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.3">
@@ -10310,7 +11030,7 @@
       <c r="F683" s="19"/>
       <c r="G683" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.3">
@@ -10322,7 +11042,7 @@
       <c r="F684" s="18"/>
       <c r="G684" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.3">
@@ -10334,7 +11054,7 @@
       <c r="F685" s="19"/>
       <c r="G685" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.3">
@@ -10346,7 +11066,7 @@
       <c r="F686" s="18"/>
       <c r="G686" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.3">
@@ -10358,7 +11078,7 @@
       <c r="F687" s="19"/>
       <c r="G687" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.3">
@@ -10370,7 +11090,7 @@
       <c r="F688" s="18"/>
       <c r="G688" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.3">
@@ -10382,7 +11102,7 @@
       <c r="F689" s="19"/>
       <c r="G689" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,7 +11114,7 @@
       <c r="F690" s="18"/>
       <c r="G690" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.3">
@@ -10406,7 +11126,7 @@
       <c r="F691" s="19"/>
       <c r="G691" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.3">
@@ -10418,7 +11138,7 @@
       <c r="F692" s="18"/>
       <c r="G692" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.3">
@@ -10430,7 +11150,7 @@
       <c r="F693" s="19"/>
       <c r="G693" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.3">
@@ -10442,7 +11162,7 @@
       <c r="F694" s="18"/>
       <c r="G694" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.3">
@@ -10454,7 +11174,7 @@
       <c r="F695" s="19"/>
       <c r="G695" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.3">
@@ -10466,7 +11186,7 @@
       <c r="F696" s="18"/>
       <c r="G696" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.3">
@@ -10478,7 +11198,7 @@
       <c r="F697" s="19"/>
       <c r="G697" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.3">
@@ -10490,7 +11210,7 @@
       <c r="F698" s="18"/>
       <c r="G698" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.3">
@@ -10502,7 +11222,7 @@
       <c r="F699" s="19"/>
       <c r="G699" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.3">
@@ -10514,7 +11234,7 @@
       <c r="F700" s="18"/>
       <c r="G700" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.3">
@@ -10526,7 +11246,7 @@
       <c r="F701" s="19"/>
       <c r="G701" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.3">
@@ -10538,7 +11258,7 @@
       <c r="F702" s="18"/>
       <c r="G702" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.3">
@@ -10550,7 +11270,7 @@
       <c r="F703" s="19"/>
       <c r="G703" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.3">
@@ -10562,7 +11282,7 @@
       <c r="F704" s="18"/>
       <c r="G704" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.3">
@@ -10574,7 +11294,7 @@
       <c r="F705" s="19"/>
       <c r="G705" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.3">
@@ -10586,7 +11306,7 @@
       <c r="F706" s="18"/>
       <c r="G706" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.3">
@@ -10598,7 +11318,7 @@
       <c r="F707" s="19"/>
       <c r="G707" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.3">
@@ -10610,7 +11330,7 @@
       <c r="F708" s="18"/>
       <c r="G708" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.3">
@@ -10622,7 +11342,7 @@
       <c r="F709" s="19"/>
       <c r="G709" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.3">
@@ -10634,7 +11354,7 @@
       <c r="F710" s="18"/>
       <c r="G710" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.3">
@@ -10646,7 +11366,7 @@
       <c r="F711" s="19"/>
       <c r="G711" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.3">
@@ -10658,7 +11378,7 @@
       <c r="F712" s="18"/>
       <c r="G712" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,7 +11390,7 @@
       <c r="F713" s="19"/>
       <c r="G713" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.3">
@@ -10682,7 +11402,7 @@
       <c r="F714" s="18"/>
       <c r="G714" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.3">
@@ -10694,7 +11414,7 @@
       <c r="F715" s="19"/>
       <c r="G715" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.3">
@@ -10706,7 +11426,7 @@
       <c r="F716" s="18"/>
       <c r="G716" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.3">
@@ -10718,7 +11438,7 @@
       <c r="F717" s="19"/>
       <c r="G717" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.3">
@@ -10730,7 +11450,7 @@
       <c r="F718" s="18"/>
       <c r="G718" s="18">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.3">
@@ -10742,7 +11462,7 @@
       <c r="F719" s="19"/>
       <c r="G719" s="19">
         <f t="shared" si="12"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
@@ -10754,7 +11474,7 @@
       <c r="F720" s="18"/>
       <c r="G720" s="18">
         <f t="shared" ref="G720:G735" si="13">G719+E720-F720</f>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.3">
@@ -10766,7 +11486,7 @@
       <c r="F721" s="19"/>
       <c r="G721" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.3">
@@ -10778,7 +11498,7 @@
       <c r="F722" s="18"/>
       <c r="G722" s="18">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.3">
@@ -10790,7 +11510,7 @@
       <c r="F723" s="19"/>
       <c r="G723" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.3">
@@ -10802,7 +11522,7 @@
       <c r="F724" s="18"/>
       <c r="G724" s="18">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.3">
@@ -10814,7 +11534,7 @@
       <c r="F725" s="19"/>
       <c r="G725" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.3">
@@ -10826,7 +11546,7 @@
       <c r="F726" s="18"/>
       <c r="G726" s="18">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.3">
@@ -10838,7 +11558,7 @@
       <c r="F727" s="19"/>
       <c r="G727" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.3">
@@ -10850,7 +11570,7 @@
       <c r="F728" s="18"/>
       <c r="G728" s="18">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.3">
@@ -10862,7 +11582,7 @@
       <c r="F729" s="19"/>
       <c r="G729" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.3">
@@ -10874,7 +11594,7 @@
       <c r="F730" s="18"/>
       <c r="G730" s="18">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.3">
@@ -10886,7 +11606,7 @@
       <c r="F731" s="19"/>
       <c r="G731" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.3">
@@ -10898,7 +11618,7 @@
       <c r="F732" s="18"/>
       <c r="G732" s="18">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.3">
@@ -10910,7 +11630,7 @@
       <c r="F733" s="19"/>
       <c r="G733" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.3">
@@ -10922,7 +11642,7 @@
       <c r="F734" s="18"/>
       <c r="G734" s="18">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.3">
@@ -10934,7 +11654,7 @@
       <c r="F735" s="19"/>
       <c r="G735" s="19">
         <f t="shared" si="13"/>
-        <v>75226</v>
+        <v>73776</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.3">

--- a/NBFC-MF/CashFlow.xlsx
+++ b/NBFC-MF/CashFlow.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="232">
   <si>
     <t>Transaction Description</t>
   </si>
@@ -706,6 +706,24 @@
   <si>
     <t>226Sandhyarani</t>
   </si>
+  <si>
+    <t>190bidyarani</t>
+  </si>
+  <si>
+    <t>227Tina</t>
+  </si>
+  <si>
+    <t>228Gomti</t>
+  </si>
+  <si>
+    <t>snacks +paper</t>
+  </si>
+  <si>
+    <t>chahi din</t>
+  </si>
+  <si>
+    <t>228Ichal</t>
+  </si>
 </sst>
 </file>
 
@@ -4755,10 +4773,16 @@
       <c r="I161" s="21"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A162" s="17"/>
+      <c r="A162" s="17">
+        <v>46287</v>
+      </c>
       <c r="B162" s="14"/>
-      <c r="C162" s="14"/>
-      <c r="D162" s="14"/>
+      <c r="C162" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D162" s="14" t="s">
+        <v>19</v>
+      </c>
       <c r="E162" s="14"/>
       <c r="F162" s="14"/>
       <c r="G162" s="14">
@@ -4767,801 +4791,1466 @@
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A163" s="16"/>
-      <c r="B163" s="13"/>
-      <c r="C163" s="13"/>
-      <c r="D163" s="13"/>
-      <c r="E163" s="13"/>
+      <c r="A163" s="16">
+        <v>46287</v>
+      </c>
+      <c r="B163" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C163" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D163" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E163" s="13">
+        <v>300</v>
+      </c>
       <c r="F163" s="13"/>
       <c r="G163" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>74076</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A164" s="17"/>
-      <c r="B164" s="14"/>
-      <c r="C164" s="14"/>
-      <c r="D164" s="14"/>
-      <c r="E164" s="14"/>
+      <c r="A164" s="17">
+        <v>46287</v>
+      </c>
+      <c r="B164" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C164" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D164" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E164" s="14">
+        <v>200</v>
+      </c>
       <c r="F164" s="14"/>
       <c r="G164" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A165" s="16"/>
-      <c r="B165" s="13"/>
-      <c r="C165" s="13"/>
-      <c r="D165" s="13"/>
-      <c r="E165" s="13"/>
+        <v>74276</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A165" s="16">
+        <v>46287</v>
+      </c>
+      <c r="B165" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C165" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D165" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E165" s="13">
+        <v>1750</v>
+      </c>
       <c r="F165" s="13"/>
       <c r="G165" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>76026</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A166" s="17"/>
-      <c r="B166" s="14"/>
-      <c r="C166" s="14"/>
-      <c r="D166" s="14"/>
-      <c r="E166" s="14"/>
+      <c r="A166" s="17">
+        <v>46288</v>
+      </c>
+      <c r="B166" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C166" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D166" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E166" s="14">
+        <v>600</v>
+      </c>
       <c r="F166" s="14"/>
       <c r="G166" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>76626</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A167" s="16"/>
-      <c r="B167" s="13"/>
-      <c r="C167" s="13"/>
-      <c r="D167" s="13"/>
-      <c r="E167" s="13"/>
+      <c r="A167" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B167" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C167" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D167" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E167" s="13">
+        <v>2100</v>
+      </c>
       <c r="F167" s="13"/>
       <c r="G167" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A168" s="17"/>
-      <c r="B168" s="14"/>
-      <c r="C168" s="14"/>
-      <c r="D168" s="14"/>
-      <c r="E168" s="14"/>
+        <v>78726</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A168" s="17">
+        <v>46288</v>
+      </c>
+      <c r="B168" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="C168" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D168" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E168" s="14">
+        <v>4200</v>
+      </c>
       <c r="F168" s="14"/>
       <c r="G168" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>82926</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A169" s="16"/>
-      <c r="B169" s="13"/>
-      <c r="C169" s="13"/>
-      <c r="D169" s="13"/>
-      <c r="E169" s="13"/>
+      <c r="A169" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C169" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E169" s="13">
+        <v>4200</v>
+      </c>
       <c r="F169" s="13"/>
       <c r="G169" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>87126</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A170" s="17"/>
-      <c r="B170" s="14"/>
-      <c r="C170" s="14"/>
-      <c r="D170" s="14"/>
-      <c r="E170" s="14"/>
+      <c r="A170" s="17">
+        <v>46288</v>
+      </c>
+      <c r="B170" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C170" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D170" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E170" s="14">
+        <v>1400</v>
+      </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>88526</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A171" s="16"/>
-      <c r="B171" s="13"/>
-      <c r="C171" s="13"/>
-      <c r="D171" s="13"/>
-      <c r="E171" s="13"/>
+      <c r="A171" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B171" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C171" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E171" s="13">
+        <v>1400</v>
+      </c>
       <c r="F171" s="13"/>
       <c r="G171" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>89926</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A172" s="17"/>
-      <c r="B172" s="14"/>
-      <c r="C172" s="14"/>
-      <c r="D172" s="14"/>
-      <c r="E172" s="14"/>
+      <c r="A172" s="17">
+        <v>46288</v>
+      </c>
+      <c r="B172" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C172" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D172" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E172" s="14">
+        <v>1400</v>
+      </c>
       <c r="F172" s="14"/>
       <c r="G172" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>91326</v>
       </c>
       <c r="I172" s="21"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A173" s="16"/>
-      <c r="B173" s="13"/>
-      <c r="C173" s="13"/>
-      <c r="D173" s="13"/>
-      <c r="E173" s="13"/>
+      <c r="A173" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B173" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C173" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E173" s="13">
+        <v>1400</v>
+      </c>
       <c r="F173" s="13"/>
       <c r="G173" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>92726</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A174" s="17"/>
-      <c r="B174" s="14"/>
-      <c r="C174" s="14"/>
-      <c r="D174" s="14"/>
-      <c r="E174" s="14"/>
+      <c r="A174" s="17">
+        <v>46288</v>
+      </c>
+      <c r="B174" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C174" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D174" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E174" s="14">
+        <v>200</v>
+      </c>
       <c r="F174" s="14"/>
       <c r="G174" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>92926</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A175" s="16"/>
-      <c r="B175" s="13"/>
-      <c r="C175" s="13"/>
-      <c r="D175" s="13"/>
-      <c r="E175" s="13"/>
+      <c r="A175" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B175" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C175" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E175" s="13">
+        <v>300</v>
+      </c>
       <c r="F175" s="13"/>
       <c r="G175" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>93226</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A176" s="17"/>
-      <c r="B176" s="14"/>
-      <c r="C176" s="14"/>
-      <c r="D176" s="14"/>
-      <c r="E176" s="14"/>
+      <c r="A176" s="17">
+        <v>46288</v>
+      </c>
+      <c r="B176" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E176" s="14">
+        <v>2500</v>
+      </c>
       <c r="F176" s="14"/>
       <c r="G176" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>95726</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A177" s="16"/>
-      <c r="B177" s="13"/>
-      <c r="C177" s="13"/>
-      <c r="D177" s="13"/>
-      <c r="E177" s="13"/>
+      <c r="A177" s="16">
+        <v>46289</v>
+      </c>
+      <c r="B177" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C177" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E177" s="13">
+        <v>200</v>
+      </c>
       <c r="F177" s="13"/>
       <c r="G177" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>95926</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A178" s="17"/>
-      <c r="B178" s="14"/>
-      <c r="C178" s="14"/>
-      <c r="D178" s="14"/>
-      <c r="E178" s="14"/>
+      <c r="A178" s="17">
+        <v>46289</v>
+      </c>
+      <c r="B178" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C178" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D178" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E178" s="14">
+        <v>3000</v>
+      </c>
       <c r="F178" s="14"/>
       <c r="G178" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>98926</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A179" s="16"/>
-      <c r="B179" s="13"/>
-      <c r="C179" s="13"/>
-      <c r="D179" s="13"/>
-      <c r="E179" s="13"/>
+      <c r="A179" s="16">
+        <v>46289</v>
+      </c>
+      <c r="B179" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C179" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D179" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E179" s="13">
+        <v>700</v>
+      </c>
       <c r="F179" s="13"/>
       <c r="G179" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>99626</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A180" s="17"/>
-      <c r="B180" s="14"/>
-      <c r="C180" s="14"/>
-      <c r="D180" s="14"/>
-      <c r="E180" s="14"/>
+      <c r="A180" s="17">
+        <v>46289</v>
+      </c>
+      <c r="B180" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C180" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D180" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E180" s="14">
+        <v>300</v>
+      </c>
       <c r="F180" s="14"/>
       <c r="G180" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>99926</v>
       </c>
       <c r="I180" s="21"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A181" s="16"/>
-      <c r="B181" s="13"/>
-      <c r="C181" s="13"/>
-      <c r="D181" s="13"/>
-      <c r="E181" s="13"/>
+      <c r="A181" s="16">
+        <v>46289</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C181" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D181" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E181" s="13">
+        <v>500</v>
+      </c>
       <c r="F181" s="13"/>
       <c r="G181" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>100426</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A182" s="17"/>
-      <c r="B182" s="14"/>
-      <c r="C182" s="14"/>
-      <c r="D182" s="14"/>
-      <c r="E182" s="14"/>
+      <c r="A182" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B182" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C182" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D182" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E182" s="14">
+        <v>1200</v>
+      </c>
       <c r="F182" s="14"/>
       <c r="G182" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>101626</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A183" s="16"/>
-      <c r="B183" s="13"/>
-      <c r="C183" s="13"/>
-      <c r="D183" s="13"/>
-      <c r="E183" s="13"/>
+      <c r="A183" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C183" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D183" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E183" s="13">
+        <v>12600</v>
+      </c>
       <c r="F183" s="13"/>
       <c r="G183" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A184" s="17"/>
-      <c r="B184" s="14"/>
-      <c r="C184" s="14"/>
-      <c r="D184" s="14"/>
-      <c r="E184" s="14"/>
+      <c r="A184" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B184" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C184" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D184" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E184" s="14">
+        <v>200</v>
+      </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>114426</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A185" s="16"/>
-      <c r="B185" s="13"/>
-      <c r="C185" s="13"/>
-      <c r="D185" s="13"/>
-      <c r="E185" s="13"/>
+      <c r="A185" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B185" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C185" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D185" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E185" s="13">
+        <v>300</v>
+      </c>
       <c r="F185" s="13"/>
       <c r="G185" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>114726</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A186" s="17"/>
-      <c r="B186" s="14"/>
-      <c r="C186" s="14"/>
-      <c r="D186" s="14"/>
-      <c r="E186" s="14"/>
+      <c r="A186" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B186" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C186" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D186" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E186" s="14">
+        <v>2100</v>
+      </c>
       <c r="F186" s="14"/>
       <c r="G186" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>116826</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A187" s="16"/>
-      <c r="B187" s="13"/>
-      <c r="C187" s="13"/>
-      <c r="D187" s="13"/>
-      <c r="E187" s="13"/>
+      <c r="A187" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B187" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C187" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E187" s="13">
+        <v>1400</v>
+      </c>
       <c r="F187" s="13"/>
       <c r="G187" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>118226</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A188" s="17"/>
-      <c r="B188" s="14"/>
-      <c r="C188" s="14"/>
-      <c r="D188" s="14"/>
-      <c r="E188" s="14"/>
+      <c r="A188" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B188" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C188" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D188" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E188" s="14">
+        <v>700</v>
+      </c>
       <c r="F188" s="14"/>
       <c r="G188" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>118926</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A189" s="16"/>
-      <c r="B189" s="13"/>
-      <c r="C189" s="13"/>
-      <c r="D189" s="13"/>
-      <c r="E189" s="13"/>
+      <c r="A189" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B189" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C189" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D189" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E189" s="13">
+        <v>1400</v>
+      </c>
       <c r="F189" s="13"/>
       <c r="G189" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>120326</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A190" s="17"/>
-      <c r="B190" s="14"/>
-      <c r="C190" s="14"/>
-      <c r="D190" s="14"/>
-      <c r="E190" s="14"/>
+      <c r="A190" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B190" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C190" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D190" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E190" s="14">
+        <v>500</v>
+      </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>120826</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A191" s="16"/>
-      <c r="B191" s="13"/>
-      <c r="C191" s="13"/>
-      <c r="D191" s="13"/>
-      <c r="E191" s="13"/>
+      <c r="A191" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B191" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C191" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D191" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E191" s="13">
+        <v>700</v>
+      </c>
       <c r="F191" s="13"/>
       <c r="G191" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>121526</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A192" s="17"/>
-      <c r="B192" s="14"/>
-      <c r="C192" s="14"/>
-      <c r="D192" s="14"/>
-      <c r="E192" s="14"/>
+      <c r="A192" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B192" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C192" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D192" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E192" s="14">
+        <v>2100</v>
+      </c>
       <c r="F192" s="14"/>
       <c r="G192" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A193" s="16"/>
-      <c r="B193" s="13"/>
-      <c r="C193" s="13"/>
-      <c r="D193" s="13"/>
-      <c r="E193" s="13"/>
+        <v>123626</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A193" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B193" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C193" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D193" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E193" s="13">
+        <v>700</v>
+      </c>
       <c r="F193" s="13"/>
       <c r="G193" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A194" s="16"/>
-      <c r="B194" s="13"/>
-      <c r="C194" s="13"/>
-      <c r="D194" s="13"/>
-      <c r="E194" s="13"/>
+        <v>124326</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A194" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C194" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E194" s="13">
+        <v>1400</v>
+      </c>
       <c r="F194" s="13"/>
       <c r="G194" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A195" s="17"/>
-      <c r="B195" s="14"/>
-      <c r="C195" s="14"/>
-      <c r="D195" s="14"/>
-      <c r="E195" s="14"/>
+        <v>125726</v>
+      </c>
+      <c r="J194" s="21"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A195" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B195" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C195" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D195" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E195" s="14">
+        <v>1400</v>
+      </c>
       <c r="F195" s="14"/>
       <c r="G195" s="14">
         <f>G194+E195-F195</f>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A196" s="16"/>
-      <c r="B196" s="13"/>
-      <c r="C196" s="13"/>
-      <c r="D196" s="13"/>
-      <c r="E196" s="13"/>
+        <v>127126</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A196" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B196" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C196" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D196" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E196" s="13">
+        <v>2800</v>
+      </c>
       <c r="F196" s="13"/>
       <c r="G196" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A197" s="17"/>
-      <c r="B197" s="14"/>
-      <c r="C197" s="14"/>
-      <c r="D197" s="14"/>
-      <c r="E197" s="14"/>
+        <v>129926</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A197" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B197" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="C197" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D197" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E197" s="14">
+        <v>350</v>
+      </c>
       <c r="F197" s="14"/>
       <c r="G197" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A198" s="16"/>
-      <c r="B198" s="13"/>
-      <c r="C198" s="13"/>
-      <c r="D198" s="13"/>
-      <c r="E198" s="13"/>
+        <v>130276</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A198" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C198" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E198" s="13">
+        <v>1400</v>
+      </c>
       <c r="F198" s="13"/>
       <c r="G198" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A199" s="17"/>
-      <c r="B199" s="14"/>
-      <c r="C199" s="14"/>
-      <c r="D199" s="14"/>
+        <v>131676</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A199" s="17">
+        <v>46290</v>
+      </c>
+      <c r="B199" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C199" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E199" s="14"/>
-      <c r="F199" s="14"/>
+      <c r="F199" s="14">
+        <v>10000</v>
+      </c>
       <c r="G199" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A200" s="16"/>
-      <c r="B200" s="13"/>
-      <c r="C200" s="13"/>
-      <c r="D200" s="13"/>
+        <v>121676</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A200" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B200" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C200" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D200" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E200" s="13"/>
-      <c r="F200" s="13"/>
+      <c r="F200" s="13">
+        <v>30000</v>
+      </c>
       <c r="G200" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A201" s="17"/>
-      <c r="B201" s="14"/>
-      <c r="C201" s="14"/>
-      <c r="D201" s="14"/>
-      <c r="E201" s="14"/>
+        <v>91676</v>
+      </c>
+      <c r="J200" s="21"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A201" s="17">
+        <v>46291</v>
+      </c>
+      <c r="B201" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C201" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D201" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E201" s="14">
+        <v>600</v>
+      </c>
       <c r="F201" s="14"/>
       <c r="G201" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
+        <v>92276</v>
       </c>
       <c r="I201" s="21"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A202" s="16"/>
-      <c r="B202" s="13"/>
-      <c r="C202" s="13"/>
-      <c r="D202" s="13"/>
-      <c r="E202" s="13"/>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A202" s="16">
+        <v>46291</v>
+      </c>
+      <c r="B202" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C202" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D202" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E202" s="13">
+        <v>200</v>
+      </c>
       <c r="F202" s="13"/>
       <c r="G202" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A203" s="17"/>
-      <c r="B203" s="14"/>
-      <c r="C203" s="14"/>
-      <c r="D203" s="14"/>
-      <c r="E203" s="14"/>
+        <v>92476</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A203" s="17">
+        <v>46291</v>
+      </c>
+      <c r="B203" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C203" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D203" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E203" s="14">
+        <v>100</v>
+      </c>
       <c r="F203" s="14"/>
       <c r="G203" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A204" s="16"/>
-      <c r="B204" s="13"/>
-      <c r="C204" s="13"/>
-      <c r="D204" s="13"/>
-      <c r="E204" s="13"/>
+        <v>92576</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A204" s="16">
+        <v>46291</v>
+      </c>
+      <c r="B204" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C204" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D204" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E204" s="13">
+        <v>1200</v>
+      </c>
       <c r="F204" s="13"/>
       <c r="G204" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A205" s="17"/>
-      <c r="B205" s="14"/>
-      <c r="C205" s="14"/>
-      <c r="D205" s="14"/>
+        <v>93776</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A205" s="17">
+        <v>46291</v>
+      </c>
+      <c r="B205" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C205" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E205" s="14"/>
-      <c r="F205" s="14"/>
+      <c r="F205" s="14">
+        <f>700+350</f>
+        <v>1050</v>
+      </c>
       <c r="G205" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A206" s="16"/>
-      <c r="B206" s="13"/>
-      <c r="C206" s="13"/>
-      <c r="D206" s="13"/>
-      <c r="E206" s="13"/>
+        <v>92726</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A206" s="16">
+        <v>46292</v>
+      </c>
+      <c r="B206" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C206" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D206" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E206" s="13">
+        <v>200</v>
+      </c>
       <c r="F206" s="13"/>
       <c r="G206" s="13">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A207" s="17"/>
-      <c r="B207" s="14"/>
-      <c r="C207" s="14"/>
-      <c r="D207" s="14"/>
-      <c r="E207" s="14"/>
+        <v>92926</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A207" s="17">
+        <v>46292</v>
+      </c>
+      <c r="B207" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C207" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D207" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E207" s="14">
+        <v>300</v>
+      </c>
       <c r="F207" s="14"/>
       <c r="G207" s="14">
         <f t="shared" si="4"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A208" s="16"/>
-      <c r="B208" s="13"/>
-      <c r="C208" s="13"/>
-      <c r="D208" s="13"/>
-      <c r="E208" s="13"/>
+        <v>93226</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A208" s="16">
+        <v>46292</v>
+      </c>
+      <c r="B208" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C208" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D208" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E208" s="13">
+        <v>100</v>
+      </c>
       <c r="F208" s="13"/>
       <c r="G208" s="13">
         <f t="shared" ref="G208:G271" si="5">G207+E208-F208</f>
-        <v>73776</v>
+        <v>93326</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" s="17"/>
-      <c r="B209" s="14"/>
-      <c r="C209" s="14"/>
-      <c r="D209" s="14"/>
-      <c r="E209" s="14"/>
+      <c r="A209" s="17">
+        <v>46292</v>
+      </c>
+      <c r="B209" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C209" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D209" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E209" s="14">
+        <v>2100</v>
+      </c>
       <c r="F209" s="14"/>
       <c r="G209" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>95426</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A210" s="16"/>
-      <c r="B210" s="13"/>
-      <c r="C210" s="13"/>
-      <c r="D210" s="13"/>
-      <c r="E210" s="13"/>
+      <c r="A210" s="16">
+        <v>46292</v>
+      </c>
+      <c r="B210" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C210" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D210" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E210" s="13">
+        <v>450</v>
+      </c>
       <c r="F210" s="13"/>
       <c r="G210" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>95876</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" s="17"/>
-      <c r="B211" s="14"/>
-      <c r="C211" s="14"/>
-      <c r="D211" s="14"/>
-      <c r="E211" s="14"/>
+      <c r="A211" s="17">
+        <v>46293</v>
+      </c>
+      <c r="B211" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C211" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D211" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E211" s="14">
+        <v>200</v>
+      </c>
       <c r="F211" s="14"/>
       <c r="G211" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>96076</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" s="16"/>
-      <c r="B212" s="13"/>
-      <c r="C212" s="13"/>
-      <c r="D212" s="13"/>
-      <c r="E212" s="13"/>
+      <c r="A212" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C212" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D212" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E212" s="13">
+        <v>300</v>
+      </c>
       <c r="F212" s="13"/>
       <c r="G212" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>96376</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A213" s="17"/>
-      <c r="B213" s="14"/>
-      <c r="C213" s="14"/>
-      <c r="D213" s="14"/>
-      <c r="E213" s="14"/>
+      <c r="A213" s="17">
+        <v>46293</v>
+      </c>
+      <c r="B213" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C213" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D213" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E213" s="14">
+        <v>100</v>
+      </c>
       <c r="F213" s="13"/>
       <c r="G213" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>96476</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A214" s="16"/>
-      <c r="B214" s="13"/>
-      <c r="C214" s="13"/>
-      <c r="D214" s="13"/>
-      <c r="E214" s="13"/>
+      <c r="A214" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B214" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C214" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D214" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E214" s="13">
+        <v>300</v>
+      </c>
       <c r="F214" s="13"/>
       <c r="G214" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>96776</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" s="17"/>
-      <c r="B215" s="14"/>
-      <c r="C215" s="14"/>
-      <c r="D215" s="14"/>
-      <c r="E215" s="14"/>
+      <c r="A215" s="17">
+        <v>46293</v>
+      </c>
+      <c r="B215" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C215" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D215" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E215" s="14">
+        <v>7000</v>
+      </c>
       <c r="F215" s="14"/>
       <c r="G215" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>103776</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" s="16"/>
-      <c r="B216" s="13"/>
-      <c r="C216" s="13"/>
-      <c r="D216" s="13"/>
-      <c r="E216" s="13"/>
+      <c r="A216" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B216" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C216" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D216" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E216" s="13">
+        <v>7000</v>
+      </c>
       <c r="F216" s="13"/>
       <c r="G216" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>110776</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" s="17"/>
-      <c r="B217" s="14"/>
-      <c r="C217" s="14"/>
-      <c r="D217" s="14"/>
-      <c r="E217" s="14"/>
+      <c r="A217" s="17">
+        <v>46293</v>
+      </c>
+      <c r="B217" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C217" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D217" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E217" s="14">
+        <v>1400</v>
+      </c>
       <c r="F217" s="14"/>
       <c r="G217" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>112176</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" s="16"/>
-      <c r="B218" s="13"/>
-      <c r="C218" s="13"/>
-      <c r="D218" s="13"/>
-      <c r="E218" s="13"/>
+      <c r="A218" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B218" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C218" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D218" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E218" s="13">
+        <v>1400</v>
+      </c>
       <c r="F218" s="13"/>
       <c r="G218" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>113576</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A219" s="17"/>
-      <c r="B219" s="14"/>
-      <c r="C219" s="14"/>
-      <c r="D219" s="14"/>
-      <c r="E219" s="14"/>
+      <c r="A219" s="17">
+        <v>46293</v>
+      </c>
+      <c r="B219" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C219" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D219" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E219" s="14">
+        <v>1400</v>
+      </c>
       <c r="F219" s="14"/>
       <c r="G219" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>114976</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A220" s="16"/>
-      <c r="B220" s="13"/>
-      <c r="C220" s="13"/>
-      <c r="D220" s="13"/>
-      <c r="E220" s="13"/>
+      <c r="A220" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B220" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C220" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D220" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E220" s="13">
+        <v>5600</v>
+      </c>
       <c r="F220" s="13"/>
       <c r="G220" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>120576</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A221" s="17"/>
-      <c r="B221" s="14"/>
-      <c r="C221" s="14"/>
-      <c r="D221" s="14"/>
-      <c r="E221" s="14"/>
+      <c r="A221" s="17">
+        <v>46293</v>
+      </c>
+      <c r="B221" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C221" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D221" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E221" s="14">
+        <v>200</v>
+      </c>
       <c r="F221" s="14"/>
       <c r="G221" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>120776</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A222" s="16"/>
-      <c r="B222" s="13"/>
-      <c r="C222" s="13"/>
-      <c r="D222" s="13"/>
+      <c r="A222" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C222" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D222" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E222" s="13"/>
-      <c r="F222" s="13"/>
+      <c r="F222" s="13">
+        <v>2450</v>
+      </c>
       <c r="G222" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>118326</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A223" s="17"/>
-      <c r="B223" s="14"/>
-      <c r="C223" s="14"/>
-      <c r="D223" s="14"/>
+      <c r="A223" s="17">
+        <v>46293</v>
+      </c>
+      <c r="B223" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C223" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D223" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E223" s="14"/>
-      <c r="F223" s="14"/>
+      <c r="F223" s="14">
+        <v>30000</v>
+      </c>
       <c r="G223" s="14">
-        <f t="shared" si="5"/>
-        <v>73776</v>
+        <f>G222+E223-F223</f>
+        <v>88326</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A224" s="16"/>
-      <c r="B224" s="13"/>
-      <c r="C224" s="13"/>
-      <c r="D224" s="13"/>
-      <c r="E224" s="13"/>
+      <c r="A224" s="16">
+        <v>46294</v>
+      </c>
+      <c r="B224" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C224" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D224" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E224" s="13">
+        <v>200</v>
+      </c>
       <c r="F224" s="13"/>
       <c r="G224" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A225" s="17"/>
-      <c r="B225" s="14"/>
-      <c r="C225" s="14"/>
-      <c r="D225" s="14"/>
-      <c r="E225" s="14"/>
+        <v>88526</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" s="17">
+        <v>46294</v>
+      </c>
+      <c r="B225" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C225" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D225" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E225" s="14">
+        <v>300</v>
+      </c>
       <c r="F225" s="14"/>
       <c r="G225" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A226" s="16"/>
-      <c r="B226" s="13"/>
-      <c r="C226" s="13"/>
-      <c r="D226" s="13"/>
-      <c r="E226" s="13"/>
+        <v>88826</v>
+      </c>
+      <c r="J225" s="21"/>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" s="16">
+        <v>46294</v>
+      </c>
+      <c r="B226" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C226" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D226" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E226" s="13">
+        <v>500</v>
+      </c>
       <c r="F226" s="13"/>
       <c r="G226" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A227" s="17"/>
-      <c r="B227" s="14"/>
-      <c r="C227" s="14"/>
-      <c r="D227" s="14"/>
-      <c r="E227" s="14"/>
+        <v>89326</v>
+      </c>
+      <c r="J226" s="21"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A227" s="17">
+        <v>46294</v>
+      </c>
+      <c r="B227" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C227" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D227" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E227" s="14">
+        <v>100</v>
+      </c>
       <c r="F227" s="14"/>
       <c r="G227" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A228" s="16"/>
-      <c r="B228" s="13"/>
-      <c r="C228" s="13"/>
-      <c r="D228" s="13"/>
-      <c r="E228" s="13"/>
+        <v>89426</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" s="16">
+        <v>46294</v>
+      </c>
+      <c r="B228" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C228" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D228" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E228" s="13">
+        <v>300</v>
+      </c>
       <c r="F228" s="13"/>
       <c r="G228" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="17"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -5570,10 +6259,11 @@
       <c r="F229" s="14"/>
       <c r="G229" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+      <c r="J229" s="21"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="16"/>
       <c r="B230" s="13"/>
       <c r="C230" s="13"/>
@@ -5582,10 +6272,10 @@
       <c r="F230" s="13"/>
       <c r="G230" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="17"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -5594,10 +6284,10 @@
       <c r="F231" s="14"/>
       <c r="G231" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="16"/>
       <c r="B232" s="13"/>
       <c r="C232" s="13"/>
@@ -5606,10 +6296,10 @@
       <c r="F232" s="13"/>
       <c r="G232" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="17"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -5618,10 +6308,10 @@
       <c r="F233" s="14"/>
       <c r="G233" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="16"/>
       <c r="B234" s="13"/>
       <c r="C234" s="13"/>
@@ -5630,10 +6320,10 @@
       <c r="F234" s="13"/>
       <c r="G234" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="17"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -5642,10 +6332,10 @@
       <c r="F235" s="14"/>
       <c r="G235" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="16"/>
       <c r="B236" s="13"/>
       <c r="C236" s="13"/>
@@ -5654,10 +6344,10 @@
       <c r="F236" s="13"/>
       <c r="G236" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="17"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -5666,10 +6356,10 @@
       <c r="F237" s="14"/>
       <c r="G237" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="16"/>
       <c r="B238" s="13"/>
       <c r="C238" s="13"/>
@@ -5678,10 +6368,10 @@
       <c r="F238" s="13"/>
       <c r="G238" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="17"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -5690,10 +6380,10 @@
       <c r="F239" s="14"/>
       <c r="G239" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89726</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="16"/>
       <c r="B240" s="13"/>
       <c r="C240" s="13"/>
@@ -5702,7 +6392,7 @@
       <c r="F240" s="13"/>
       <c r="G240" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -5714,7 +6404,7 @@
       <c r="F241" s="14"/>
       <c r="G241" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -5726,7 +6416,7 @@
       <c r="F242" s="13"/>
       <c r="G242" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -5738,7 +6428,7 @@
       <c r="F243" s="14"/>
       <c r="G243" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -5750,7 +6440,7 @@
       <c r="F244" s="13"/>
       <c r="G244" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -5762,7 +6452,7 @@
       <c r="F245" s="14"/>
       <c r="G245" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -5774,7 +6464,7 @@
       <c r="F246" s="13"/>
       <c r="G246" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -5786,7 +6476,7 @@
       <c r="F247" s="14"/>
       <c r="G247" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -5798,7 +6488,7 @@
       <c r="F248" s="13"/>
       <c r="G248" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -5810,7 +6500,7 @@
       <c r="F249" s="14"/>
       <c r="G249" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -5822,7 +6512,7 @@
       <c r="F250" s="13"/>
       <c r="G250" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -5834,7 +6524,7 @@
       <c r="F251" s="14"/>
       <c r="G251" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -5846,7 +6536,7 @@
       <c r="F252" s="13"/>
       <c r="G252" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -5858,7 +6548,7 @@
       <c r="F253" s="14"/>
       <c r="G253" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -5870,7 +6560,7 @@
       <c r="F254" s="13"/>
       <c r="G254" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -5882,7 +6572,7 @@
       <c r="F255" s="14"/>
       <c r="G255" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -5894,7 +6584,7 @@
       <c r="F256" s="13"/>
       <c r="G256" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -5906,7 +6596,7 @@
       <c r="F257" s="14"/>
       <c r="G257" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -5918,7 +6608,7 @@
       <c r="F258" s="13"/>
       <c r="G258" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -5930,7 +6620,7 @@
       <c r="F259" s="14"/>
       <c r="G259" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -5942,7 +6632,7 @@
       <c r="F260" s="13"/>
       <c r="G260" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -5954,7 +6644,7 @@
       <c r="F261" s="14"/>
       <c r="G261" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -5966,7 +6656,7 @@
       <c r="F262" s="13"/>
       <c r="G262" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -5978,7 +6668,7 @@
       <c r="F263" s="14"/>
       <c r="G263" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -5990,7 +6680,7 @@
       <c r="F264" s="13"/>
       <c r="G264" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -6002,7 +6692,7 @@
       <c r="F265" s="14"/>
       <c r="G265" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -6014,7 +6704,7 @@
       <c r="F266" s="13"/>
       <c r="G266" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -6026,7 +6716,7 @@
       <c r="F267" s="14"/>
       <c r="G267" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -6038,7 +6728,7 @@
       <c r="F268" s="13"/>
       <c r="G268" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -6050,7 +6740,7 @@
       <c r="F269" s="14"/>
       <c r="G269" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -6062,7 +6752,7 @@
       <c r="F270" s="13"/>
       <c r="G270" s="13">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -6074,7 +6764,7 @@
       <c r="F271" s="14"/>
       <c r="G271" s="14">
         <f t="shared" si="5"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -6086,7 +6776,7 @@
       <c r="F272" s="13"/>
       <c r="G272" s="13">
         <f t="shared" ref="G272:G335" si="6">G271+E272-F272</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
@@ -6098,7 +6788,7 @@
       <c r="F273" s="14"/>
       <c r="G273" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
@@ -6110,7 +6800,7 @@
       <c r="F274" s="13"/>
       <c r="G274" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
@@ -6122,7 +6812,7 @@
       <c r="F275" s="14"/>
       <c r="G275" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="I275" s="21"/>
     </row>
@@ -6135,7 +6825,7 @@
       <c r="F276" s="13"/>
       <c r="G276" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
@@ -6147,7 +6837,7 @@
       <c r="F277" s="14"/>
       <c r="G277" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="I277" s="21"/>
     </row>
@@ -6160,7 +6850,7 @@
       <c r="F278" s="13"/>
       <c r="G278" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
@@ -6172,7 +6862,7 @@
       <c r="F279" s="14"/>
       <c r="G279" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
@@ -6184,7 +6874,7 @@
       <c r="F280" s="13"/>
       <c r="G280" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
@@ -6196,7 +6886,7 @@
       <c r="F281" s="14"/>
       <c r="G281" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
@@ -6208,7 +6898,7 @@
       <c r="F282" s="13"/>
       <c r="G282" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
@@ -6220,7 +6910,7 @@
       <c r="F283" s="14"/>
       <c r="G283" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
@@ -6232,7 +6922,7 @@
       <c r="F284" s="13"/>
       <c r="G284" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
@@ -6244,7 +6934,7 @@
       <c r="F285" s="14"/>
       <c r="G285" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
@@ -6256,7 +6946,7 @@
       <c r="F286" s="13"/>
       <c r="G286" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
@@ -6268,7 +6958,7 @@
       <c r="F287" s="14"/>
       <c r="G287" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
@@ -6280,7 +6970,7 @@
       <c r="F288" s="13"/>
       <c r="G288" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="I288" s="21"/>
     </row>
@@ -6293,7 +6983,7 @@
       <c r="F289" s="14"/>
       <c r="G289" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -6305,7 +6995,7 @@
       <c r="F290" s="13"/>
       <c r="G290" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -6317,7 +7007,7 @@
       <c r="F291" s="14"/>
       <c r="G291" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -6329,7 +7019,7 @@
       <c r="F292" s="13"/>
       <c r="G292" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -6341,7 +7031,7 @@
       <c r="F293" s="14"/>
       <c r="G293" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -6353,7 +7043,7 @@
       <c r="F294" s="13"/>
       <c r="G294" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -6365,7 +7055,7 @@
       <c r="F295" s="14"/>
       <c r="G295" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -6377,7 +7067,7 @@
       <c r="F296" s="13"/>
       <c r="G296" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -6389,7 +7079,7 @@
       <c r="F297" s="14"/>
       <c r="G297" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -6401,7 +7091,7 @@
       <c r="F298" s="13"/>
       <c r="G298" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -6413,7 +7103,7 @@
       <c r="F299" s="14"/>
       <c r="G299" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -6425,7 +7115,7 @@
       <c r="F300" s="13"/>
       <c r="G300" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -6437,7 +7127,7 @@
       <c r="F301" s="14"/>
       <c r="G301" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -6449,7 +7139,7 @@
       <c r="F302" s="13"/>
       <c r="G302" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -6461,7 +7151,7 @@
       <c r="F303" s="14"/>
       <c r="G303" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -6473,7 +7163,7 @@
       <c r="F304" s="13"/>
       <c r="G304" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -6485,7 +7175,7 @@
       <c r="F305" s="14"/>
       <c r="G305" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -6497,7 +7187,7 @@
       <c r="F306" s="13"/>
       <c r="G306" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -6509,7 +7199,7 @@
       <c r="F307" s="14"/>
       <c r="G307" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -6521,7 +7211,7 @@
       <c r="F308" s="13"/>
       <c r="G308" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -6533,7 +7223,7 @@
       <c r="F309" s="14"/>
       <c r="G309" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -6545,7 +7235,7 @@
       <c r="F310" s="13"/>
       <c r="G310" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -6557,7 +7247,7 @@
       <c r="F311" s="14"/>
       <c r="G311" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -6569,7 +7259,7 @@
       <c r="F312" s="13"/>
       <c r="G312" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -6581,7 +7271,7 @@
       <c r="F313" s="14"/>
       <c r="G313" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -6593,7 +7283,7 @@
       <c r="F314" s="13"/>
       <c r="G314" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -6605,7 +7295,7 @@
       <c r="F315" s="14"/>
       <c r="G315" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -6617,7 +7307,7 @@
       <c r="F316" s="13"/>
       <c r="G316" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -6629,7 +7319,7 @@
       <c r="F317" s="14"/>
       <c r="G317" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -6641,7 +7331,7 @@
       <c r="F318" s="13"/>
       <c r="G318" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -6653,7 +7343,7 @@
       <c r="F319" s="14"/>
       <c r="G319" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -6665,7 +7355,7 @@
       <c r="F320" s="13"/>
       <c r="G320" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
@@ -6677,7 +7367,7 @@
       <c r="F321" s="14"/>
       <c r="G321" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
@@ -6689,7 +7379,7 @@
       <c r="F322" s="13"/>
       <c r="G322" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
@@ -6701,7 +7391,7 @@
       <c r="F323" s="14"/>
       <c r="G323" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
@@ -6713,7 +7403,7 @@
       <c r="F324" s="13"/>
       <c r="G324" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
@@ -6725,7 +7415,7 @@
       <c r="F325" s="14"/>
       <c r="G325" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
@@ -6737,7 +7427,7 @@
       <c r="F326" s="13"/>
       <c r="G326" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
@@ -6749,7 +7439,7 @@
       <c r="F327" s="14"/>
       <c r="G327" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
@@ -6761,7 +7451,7 @@
       <c r="F328" s="13"/>
       <c r="G328" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
@@ -6773,7 +7463,7 @@
       <c r="F329" s="14"/>
       <c r="G329" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
@@ -6785,7 +7475,7 @@
       <c r="F330" s="13"/>
       <c r="G330" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
@@ -6797,7 +7487,7 @@
       <c r="F331" s="14"/>
       <c r="G331" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
@@ -6809,7 +7499,7 @@
       <c r="F332" s="13"/>
       <c r="G332" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
@@ -6821,7 +7511,7 @@
       <c r="F333" s="14"/>
       <c r="G333" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="I333" s="21"/>
     </row>
@@ -6834,7 +7524,7 @@
       <c r="F334" s="13"/>
       <c r="G334" s="13">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
@@ -6846,7 +7536,7 @@
       <c r="F335" s="14"/>
       <c r="G335" s="14">
         <f t="shared" si="6"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
@@ -6858,7 +7548,7 @@
       <c r="F336" s="13"/>
       <c r="G336" s="13">
         <f t="shared" ref="G336:G399" si="7">G335+E336-F336</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
@@ -6870,7 +7560,7 @@
       <c r="F337" s="14"/>
       <c r="G337" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
@@ -6882,7 +7572,7 @@
       <c r="F338" s="13"/>
       <c r="G338" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
@@ -6894,7 +7584,7 @@
       <c r="F339" s="14"/>
       <c r="G339" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
@@ -6906,7 +7596,7 @@
       <c r="F340" s="13"/>
       <c r="G340" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="J340" s="21"/>
     </row>
@@ -6919,7 +7609,7 @@
       <c r="F341" s="14"/>
       <c r="G341" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
@@ -6931,7 +7621,7 @@
       <c r="F342" s="13"/>
       <c r="G342" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
@@ -6943,7 +7633,7 @@
       <c r="F343" s="14"/>
       <c r="G343" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
@@ -6955,7 +7645,7 @@
       <c r="F344" s="13"/>
       <c r="G344" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
@@ -6967,7 +7657,7 @@
       <c r="F345" s="14"/>
       <c r="G345" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
@@ -6979,7 +7669,7 @@
       <c r="F346" s="13"/>
       <c r="G346" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
@@ -6991,7 +7681,7 @@
       <c r="F347" s="14"/>
       <c r="G347" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
@@ -7003,7 +7693,7 @@
       <c r="F348" s="13"/>
       <c r="G348" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
@@ -7015,7 +7705,7 @@
       <c r="F349" s="14"/>
       <c r="G349" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
@@ -7027,7 +7717,7 @@
       <c r="F350" s="13"/>
       <c r="G350" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
@@ -7039,7 +7729,7 @@
       <c r="F351" s="14"/>
       <c r="G351" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
@@ -7051,7 +7741,7 @@
       <c r="F352" s="13"/>
       <c r="G352" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
@@ -7063,7 +7753,7 @@
       <c r="F353" s="14"/>
       <c r="G353" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
@@ -7075,7 +7765,7 @@
       <c r="F354" s="13"/>
       <c r="G354" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="J354" s="21"/>
     </row>
@@ -7088,7 +7778,7 @@
       <c r="F355" s="14"/>
       <c r="G355" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
@@ -7100,7 +7790,7 @@
       <c r="F356" s="13"/>
       <c r="G356" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
@@ -7112,7 +7802,7 @@
       <c r="F357" s="14"/>
       <c r="G357" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
@@ -7124,7 +7814,7 @@
       <c r="F358" s="13"/>
       <c r="G358" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
@@ -7136,7 +7826,7 @@
       <c r="F359" s="14"/>
       <c r="G359" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
@@ -7148,7 +7838,7 @@
       <c r="F360" s="13"/>
       <c r="G360" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
@@ -7160,7 +7850,7 @@
       <c r="F361" s="14"/>
       <c r="G361" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
@@ -7172,7 +7862,7 @@
       <c r="F362" s="13"/>
       <c r="G362" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
@@ -7184,7 +7874,7 @@
       <c r="F363" s="14"/>
       <c r="G363" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
@@ -7196,7 +7886,7 @@
       <c r="F364" s="13"/>
       <c r="G364" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
@@ -7208,7 +7898,7 @@
       <c r="F365" s="14"/>
       <c r="G365" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
@@ -7220,7 +7910,7 @@
       <c r="F366" s="13"/>
       <c r="G366" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
@@ -7232,7 +7922,7 @@
       <c r="F367" s="14"/>
       <c r="G367" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
@@ -7244,7 +7934,7 @@
       <c r="F368" s="13"/>
       <c r="G368" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
@@ -7256,7 +7946,7 @@
       <c r="F369" s="14"/>
       <c r="G369" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
@@ -7268,7 +7958,7 @@
       <c r="F370" s="13"/>
       <c r="G370" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
@@ -7280,7 +7970,7 @@
       <c r="F371" s="14"/>
       <c r="G371" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
@@ -7292,7 +7982,7 @@
       <c r="F372" s="13"/>
       <c r="G372" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
@@ -7304,7 +7994,7 @@
       <c r="F373" s="14"/>
       <c r="G373" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
@@ -7316,7 +8006,7 @@
       <c r="F374" s="13"/>
       <c r="G374" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
@@ -7328,7 +8018,7 @@
       <c r="F375" s="14"/>
       <c r="G375" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
@@ -7340,7 +8030,7 @@
       <c r="F376" s="13"/>
       <c r="G376" s="13">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
@@ -7352,7 +8042,7 @@
       <c r="F377" s="14"/>
       <c r="G377" s="14">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
@@ -7364,7 +8054,7 @@
       <c r="F378" s="18"/>
       <c r="G378" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
@@ -7376,7 +8066,7 @@
       <c r="F379" s="19"/>
       <c r="G379" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
@@ -7388,7 +8078,7 @@
       <c r="F380" s="18"/>
       <c r="G380" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
@@ -7400,7 +8090,7 @@
       <c r="F381" s="19"/>
       <c r="G381" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
@@ -7412,7 +8102,7 @@
       <c r="F382" s="18"/>
       <c r="G382" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
@@ -7424,7 +8114,7 @@
       <c r="F383" s="19"/>
       <c r="G383" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
@@ -7436,7 +8126,7 @@
       <c r="F384" s="18"/>
       <c r="G384" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
@@ -7448,7 +8138,7 @@
       <c r="F385" s="19"/>
       <c r="G385" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
@@ -7460,7 +8150,7 @@
       <c r="F386" s="18"/>
       <c r="G386" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
@@ -7472,7 +8162,7 @@
       <c r="F387" s="19"/>
       <c r="G387" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
@@ -7484,7 +8174,7 @@
       <c r="F388" s="18"/>
       <c r="G388" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
@@ -7496,7 +8186,7 @@
       <c r="F389" s="19"/>
       <c r="G389" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
@@ -7508,7 +8198,7 @@
       <c r="F390" s="18"/>
       <c r="G390" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
@@ -7520,7 +8210,7 @@
       <c r="F391" s="19"/>
       <c r="G391" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
@@ -7532,7 +8222,7 @@
       <c r="F392" s="18"/>
       <c r="G392" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
@@ -7544,7 +8234,7 @@
       <c r="F393" s="19"/>
       <c r="G393" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
@@ -7556,7 +8246,7 @@
       <c r="F394" s="18"/>
       <c r="G394" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
@@ -7568,7 +8258,7 @@
       <c r="F395" s="19"/>
       <c r="G395" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
@@ -7580,7 +8270,7 @@
       <c r="F396" s="18"/>
       <c r="G396" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
@@ -7592,7 +8282,7 @@
       <c r="F397" s="19"/>
       <c r="G397" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
@@ -7604,7 +8294,7 @@
       <c r="F398" s="18"/>
       <c r="G398" s="18">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
@@ -7616,7 +8306,7 @@
       <c r="F399" s="19"/>
       <c r="G399" s="19">
         <f t="shared" si="7"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
@@ -7628,7 +8318,7 @@
       <c r="F400" s="18"/>
       <c r="G400" s="18">
         <f t="shared" ref="G400:G463" si="8">G399+E400-F400</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
@@ -7640,7 +8330,7 @@
       <c r="F401" s="19"/>
       <c r="G401" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -7652,7 +8342,7 @@
       <c r="F402" s="18"/>
       <c r="G402" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="I402" s="21"/>
     </row>
@@ -7665,7 +8355,7 @@
       <c r="F403" s="19"/>
       <c r="G403" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="I403" s="21"/>
     </row>
@@ -7678,7 +8368,7 @@
       <c r="F404" s="18"/>
       <c r="G404" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="I404" s="21"/>
     </row>
@@ -7691,7 +8381,7 @@
       <c r="F405" s="19"/>
       <c r="G405" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
@@ -7703,7 +8393,7 @@
       <c r="F406" s="18"/>
       <c r="G406" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.3">
@@ -7715,7 +8405,7 @@
       <c r="F407" s="19"/>
       <c r="G407" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
@@ -7727,7 +8417,7 @@
       <c r="F408" s="18"/>
       <c r="G408" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
@@ -7739,7 +8429,7 @@
       <c r="F409" s="19"/>
       <c r="G409" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
@@ -7751,7 +8441,7 @@
       <c r="F410" s="18"/>
       <c r="G410" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
@@ -7763,7 +8453,7 @@
       <c r="F411" s="19"/>
       <c r="G411" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
@@ -7775,7 +8465,7 @@
       <c r="F412" s="18"/>
       <c r="G412" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
@@ -7787,7 +8477,7 @@
       <c r="F413" s="19"/>
       <c r="G413" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
@@ -7799,7 +8489,7 @@
       <c r="F414" s="18"/>
       <c r="G414" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
@@ -7811,7 +8501,7 @@
       <c r="F415" s="19"/>
       <c r="G415" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
@@ -7823,7 +8513,7 @@
       <c r="F416" s="18"/>
       <c r="G416" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
@@ -7835,7 +8525,7 @@
       <c r="F417" s="19"/>
       <c r="G417" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
@@ -7847,7 +8537,7 @@
       <c r="F418" s="18"/>
       <c r="G418" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
@@ -7859,7 +8549,7 @@
       <c r="F419" s="19"/>
       <c r="G419" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
@@ -7871,7 +8561,7 @@
       <c r="F420" s="18"/>
       <c r="G420" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
@@ -7883,7 +8573,7 @@
       <c r="F421" s="19"/>
       <c r="G421" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
@@ -7895,7 +8585,7 @@
       <c r="F422" s="18"/>
       <c r="G422" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
@@ -7907,7 +8597,7 @@
       <c r="F423" s="19"/>
       <c r="G423" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
@@ -7919,7 +8609,7 @@
       <c r="F424" s="18"/>
       <c r="G424" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
@@ -7931,7 +8621,7 @@
       <c r="F425" s="19"/>
       <c r="G425" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
@@ -7943,7 +8633,7 @@
       <c r="F426" s="18"/>
       <c r="G426" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
@@ -7955,7 +8645,7 @@
       <c r="F427" s="19"/>
       <c r="G427" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
@@ -7967,7 +8657,7 @@
       <c r="F428" s="18"/>
       <c r="G428" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
@@ -7979,7 +8669,7 @@
       <c r="F429" s="19"/>
       <c r="G429" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
@@ -7991,7 +8681,7 @@
       <c r="F430" s="18"/>
       <c r="G430" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
@@ -8003,7 +8693,7 @@
       <c r="F431" s="19"/>
       <c r="G431" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
@@ -8015,7 +8705,7 @@
       <c r="F432" s="18"/>
       <c r="G432" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
@@ -8027,7 +8717,7 @@
       <c r="F433" s="19"/>
       <c r="G433" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
@@ -8039,7 +8729,7 @@
       <c r="F434" s="18"/>
       <c r="G434" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
@@ -8051,7 +8741,7 @@
       <c r="F435" s="19"/>
       <c r="G435" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
@@ -8063,7 +8753,7 @@
       <c r="F436" s="18"/>
       <c r="G436" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
@@ -8075,7 +8765,7 @@
       <c r="F437" s="19"/>
       <c r="G437" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
@@ -8087,7 +8777,7 @@
       <c r="F438" s="18"/>
       <c r="G438" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
@@ -8099,7 +8789,7 @@
       <c r="F439" s="19"/>
       <c r="G439" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
@@ -8111,7 +8801,7 @@
       <c r="F440" s="18"/>
       <c r="G440" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
@@ -8123,7 +8813,7 @@
       <c r="F441" s="19"/>
       <c r="G441" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
@@ -8135,7 +8825,7 @@
       <c r="F442" s="18"/>
       <c r="G442" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
@@ -8147,7 +8837,7 @@
       <c r="F443" s="19"/>
       <c r="G443" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
@@ -8159,7 +8849,7 @@
       <c r="F444" s="18"/>
       <c r="G444" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
@@ -8171,7 +8861,7 @@
       <c r="F445" s="19"/>
       <c r="G445" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
@@ -8183,7 +8873,7 @@
       <c r="F446" s="18"/>
       <c r="G446" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
@@ -8195,7 +8885,7 @@
       <c r="F447" s="19"/>
       <c r="G447" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
@@ -8207,7 +8897,7 @@
       <c r="F448" s="18"/>
       <c r="G448" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
@@ -8219,7 +8909,7 @@
       <c r="F449" s="19"/>
       <c r="G449" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
@@ -8231,7 +8921,7 @@
       <c r="F450" s="18"/>
       <c r="G450" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
@@ -8243,7 +8933,7 @@
       <c r="F451" s="19"/>
       <c r="G451" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
@@ -8255,7 +8945,7 @@
       <c r="F452" s="18"/>
       <c r="G452" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
@@ -8267,7 +8957,7 @@
       <c r="F453" s="19"/>
       <c r="G453" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
@@ -8279,7 +8969,7 @@
       <c r="F454" s="18"/>
       <c r="G454" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
@@ -8291,7 +8981,7 @@
       <c r="F455" s="19"/>
       <c r="G455" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
@@ -8303,7 +8993,7 @@
       <c r="F456" s="18"/>
       <c r="G456" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
@@ -8315,7 +9005,7 @@
       <c r="F457" s="19"/>
       <c r="G457" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
@@ -8327,7 +9017,7 @@
       <c r="F458" s="18"/>
       <c r="G458" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
@@ -8339,7 +9029,7 @@
       <c r="F459" s="19"/>
       <c r="G459" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
@@ -8351,7 +9041,7 @@
       <c r="F460" s="18"/>
       <c r="G460" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
@@ -8363,7 +9053,7 @@
       <c r="F461" s="19"/>
       <c r="G461" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
@@ -8375,7 +9065,7 @@
       <c r="F462" s="18"/>
       <c r="G462" s="18">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
@@ -8387,7 +9077,7 @@
       <c r="F463" s="19"/>
       <c r="G463" s="19">
         <f t="shared" si="8"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
@@ -8399,7 +9089,7 @@
       <c r="F464" s="18"/>
       <c r="G464" s="18">
         <f t="shared" ref="G464:G527" si="9">G463+E464-F464</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
@@ -8411,7 +9101,7 @@
       <c r="F465" s="19"/>
       <c r="G465" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
@@ -8423,7 +9113,7 @@
       <c r="F466" s="18"/>
       <c r="G466" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
@@ -8435,7 +9125,7 @@
       <c r="F467" s="19"/>
       <c r="G467" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
@@ -8447,7 +9137,7 @@
       <c r="F468" s="18"/>
       <c r="G468" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
@@ -8459,7 +9149,7 @@
       <c r="F469" s="19"/>
       <c r="G469" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.3">
@@ -8471,7 +9161,7 @@
       <c r="F470" s="18"/>
       <c r="G470" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
@@ -8483,7 +9173,7 @@
       <c r="F471" s="19"/>
       <c r="G471" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
@@ -8495,7 +9185,7 @@
       <c r="F472" s="18"/>
       <c r="G472" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
@@ -8507,7 +9197,7 @@
       <c r="F473" s="19"/>
       <c r="G473" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="J473" s="21"/>
     </row>
@@ -8520,7 +9210,7 @@
       <c r="F474" s="18"/>
       <c r="G474" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
@@ -8532,7 +9222,7 @@
       <c r="F475" s="19"/>
       <c r="G475" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
@@ -8544,7 +9234,7 @@
       <c r="F476" s="18"/>
       <c r="G476" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
@@ -8556,7 +9246,7 @@
       <c r="F477" s="19"/>
       <c r="G477" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
@@ -8568,7 +9258,7 @@
       <c r="F478" s="18"/>
       <c r="G478" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
@@ -8580,7 +9270,7 @@
       <c r="F479" s="19"/>
       <c r="G479" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
@@ -8592,7 +9282,7 @@
       <c r="F480" s="18"/>
       <c r="G480" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
@@ -8604,7 +9294,7 @@
       <c r="F481" s="19"/>
       <c r="G481" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
@@ -8616,7 +9306,7 @@
       <c r="F482" s="18"/>
       <c r="G482" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
@@ -8628,7 +9318,7 @@
       <c r="F483" s="19"/>
       <c r="G483" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
@@ -8640,7 +9330,7 @@
       <c r="F484" s="18"/>
       <c r="G484" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
@@ -8652,7 +9342,7 @@
       <c r="F485" s="19"/>
       <c r="G485" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
@@ -8664,7 +9354,7 @@
       <c r="F486" s="18"/>
       <c r="G486" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
@@ -8676,7 +9366,7 @@
       <c r="F487" s="19"/>
       <c r="G487" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.3">
@@ -8688,7 +9378,7 @@
       <c r="F488" s="18"/>
       <c r="G488" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
@@ -8700,7 +9390,7 @@
       <c r="F489" s="19"/>
       <c r="G489" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="J489" s="21"/>
     </row>
@@ -8713,7 +9403,7 @@
       <c r="F490" s="18"/>
       <c r="G490" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.3">
@@ -8725,7 +9415,7 @@
       <c r="F491" s="19"/>
       <c r="G491" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.3">
@@ -8737,7 +9427,7 @@
       <c r="F492" s="18"/>
       <c r="G492" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.3">
@@ -8749,7 +9439,7 @@
       <c r="F493" s="19"/>
       <c r="G493" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.3">
@@ -8761,7 +9451,7 @@
       <c r="F494" s="18"/>
       <c r="G494" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.3">
@@ -8773,7 +9463,7 @@
       <c r="F495" s="19"/>
       <c r="G495" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.3">
@@ -8785,7 +9475,7 @@
       <c r="F496" s="18"/>
       <c r="G496" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
@@ -8797,7 +9487,7 @@
       <c r="F497" s="19"/>
       <c r="G497" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
@@ -8809,7 +9499,7 @@
       <c r="F498" s="18"/>
       <c r="G498" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
@@ -8821,7 +9511,7 @@
       <c r="F499" s="19"/>
       <c r="G499" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
@@ -8833,7 +9523,7 @@
       <c r="F500" s="18"/>
       <c r="G500" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
@@ -8845,7 +9535,7 @@
       <c r="F501" s="19"/>
       <c r="G501" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
@@ -8857,7 +9547,7 @@
       <c r="F502" s="18"/>
       <c r="G502" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
@@ -8869,7 +9559,7 @@
       <c r="F503" s="19"/>
       <c r="G503" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
@@ -8881,7 +9571,7 @@
       <c r="F504" s="18"/>
       <c r="G504" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
@@ -8893,7 +9583,7 @@
       <c r="F505" s="19"/>
       <c r="G505" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
@@ -8905,7 +9595,7 @@
       <c r="F506" s="18"/>
       <c r="G506" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
@@ -8917,7 +9607,7 @@
       <c r="F507" s="19"/>
       <c r="G507" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
@@ -8929,7 +9619,7 @@
       <c r="F508" s="18"/>
       <c r="G508" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
@@ -8941,7 +9631,7 @@
       <c r="F509" s="19"/>
       <c r="G509" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
@@ -8953,7 +9643,7 @@
       <c r="F510" s="18"/>
       <c r="G510" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
@@ -8965,7 +9655,7 @@
       <c r="F511" s="19"/>
       <c r="G511" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
@@ -8977,7 +9667,7 @@
       <c r="F512" s="18"/>
       <c r="G512" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
@@ -8989,7 +9679,7 @@
       <c r="F513" s="19"/>
       <c r="G513" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
@@ -9001,7 +9691,7 @@
       <c r="F514" s="18"/>
       <c r="G514" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
@@ -9013,7 +9703,7 @@
       <c r="F515" s="19"/>
       <c r="G515" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
@@ -9025,7 +9715,7 @@
       <c r="F516" s="18"/>
       <c r="G516" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
@@ -9037,7 +9727,7 @@
       <c r="F517" s="19"/>
       <c r="G517" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
@@ -9049,7 +9739,7 @@
       <c r="F518" s="18"/>
       <c r="G518" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
@@ -9061,7 +9751,7 @@
       <c r="F519" s="19"/>
       <c r="G519" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
@@ -9073,7 +9763,7 @@
       <c r="F520" s="18"/>
       <c r="G520" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
@@ -9085,7 +9775,7 @@
       <c r="F521" s="19"/>
       <c r="G521" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
@@ -9097,7 +9787,7 @@
       <c r="F522" s="18"/>
       <c r="G522" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
@@ -9109,7 +9799,7 @@
       <c r="F523" s="19"/>
       <c r="G523" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
@@ -9121,7 +9811,7 @@
       <c r="F524" s="18"/>
       <c r="G524" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
@@ -9133,7 +9823,7 @@
       <c r="F525" s="19"/>
       <c r="G525" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
@@ -9145,7 +9835,7 @@
       <c r="F526" s="18"/>
       <c r="G526" s="18">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
@@ -9157,7 +9847,7 @@
       <c r="F527" s="19"/>
       <c r="G527" s="19">
         <f t="shared" si="9"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
@@ -9169,7 +9859,7 @@
       <c r="F528" s="18"/>
       <c r="G528" s="18">
         <f t="shared" ref="G528:G591" si="10">G527+E528-F528</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.3">
@@ -9181,7 +9871,7 @@
       <c r="F529" s="19"/>
       <c r="G529" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.3">
@@ -9193,7 +9883,7 @@
       <c r="F530" s="18"/>
       <c r="G530" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.3">
@@ -9205,7 +9895,7 @@
       <c r="F531" s="19"/>
       <c r="G531" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.3">
@@ -9217,7 +9907,7 @@
       <c r="F532" s="18"/>
       <c r="G532" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
       <c r="K532" s="21"/>
     </row>
@@ -9230,7 +9920,7 @@
       <c r="F533" s="19"/>
       <c r="G533" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.3">
@@ -9242,7 +9932,7 @@
       <c r="F534" s="18"/>
       <c r="G534" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.3">
@@ -9254,7 +9944,7 @@
       <c r="F535" s="19"/>
       <c r="G535" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.3">
@@ -9266,7 +9956,7 @@
       <c r="F536" s="18"/>
       <c r="G536" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.3">
@@ -9278,7 +9968,7 @@
       <c r="F537" s="19"/>
       <c r="G537" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.3">
@@ -9290,7 +9980,7 @@
       <c r="F538" s="18"/>
       <c r="G538" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.3">
@@ -9302,7 +9992,7 @@
       <c r="F539" s="19"/>
       <c r="G539" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.3">
@@ -9314,7 +10004,7 @@
       <c r="F540" s="18"/>
       <c r="G540" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.3">
@@ -9326,7 +10016,7 @@
       <c r="F541" s="19"/>
       <c r="G541" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.3">
@@ -9338,7 +10028,7 @@
       <c r="F542" s="18"/>
       <c r="G542" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.3">
@@ -9350,7 +10040,7 @@
       <c r="F543" s="19"/>
       <c r="G543" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.3">
@@ -9362,7 +10052,7 @@
       <c r="F544" s="18"/>
       <c r="G544" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
@@ -9374,7 +10064,7 @@
       <c r="F545" s="19"/>
       <c r="G545" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
@@ -9386,7 +10076,7 @@
       <c r="F546" s="18"/>
       <c r="G546" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -9398,7 +10088,7 @@
       <c r="F547" s="19"/>
       <c r="G547" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.3">
@@ -9410,7 +10100,7 @@
       <c r="F548" s="18"/>
       <c r="G548" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
@@ -9422,7 +10112,7 @@
       <c r="F549" s="19"/>
       <c r="G549" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.3">
@@ -9434,7 +10124,7 @@
       <c r="F550" s="18"/>
       <c r="G550" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.3">
@@ -9446,7 +10136,7 @@
       <c r="F551" s="19"/>
       <c r="G551" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
@@ -9458,7 +10148,7 @@
       <c r="F552" s="18"/>
       <c r="G552" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.3">
@@ -9470,7 +10160,7 @@
       <c r="F553" s="19"/>
       <c r="G553" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.3">
@@ -9482,7 +10172,7 @@
       <c r="F554" s="18"/>
       <c r="G554" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.3">
@@ -9494,7 +10184,7 @@
       <c r="F555" s="19"/>
       <c r="G555" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.3">
@@ -9506,7 +10196,7 @@
       <c r="F556" s="18"/>
       <c r="G556" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
@@ -9518,7 +10208,7 @@
       <c r="F557" s="19"/>
       <c r="G557" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
@@ -9530,7 +10220,7 @@
       <c r="F558" s="18"/>
       <c r="G558" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
@@ -9542,7 +10232,7 @@
       <c r="F559" s="19"/>
       <c r="G559" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.3">
@@ -9554,7 +10244,7 @@
       <c r="F560" s="18"/>
       <c r="G560" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
@@ -9566,7 +10256,7 @@
       <c r="F561" s="19"/>
       <c r="G561" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.3">
@@ -9578,7 +10268,7 @@
       <c r="F562" s="18"/>
       <c r="G562" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.3">
@@ -9590,7 +10280,7 @@
       <c r="F563" s="19"/>
       <c r="G563" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
@@ -9602,7 +10292,7 @@
       <c r="F564" s="18"/>
       <c r="G564" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.3">
@@ -9614,7 +10304,7 @@
       <c r="F565" s="19"/>
       <c r="G565" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.3">
@@ -9626,7 +10316,7 @@
       <c r="F566" s="18"/>
       <c r="G566" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
@@ -9638,7 +10328,7 @@
       <c r="F567" s="19"/>
       <c r="G567" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.3">
@@ -9650,7 +10340,7 @@
       <c r="F568" s="18"/>
       <c r="G568" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
@@ -9662,7 +10352,7 @@
       <c r="F569" s="19"/>
       <c r="G569" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
@@ -9674,7 +10364,7 @@
       <c r="F570" s="18"/>
       <c r="G570" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.3">
@@ -9686,7 +10376,7 @@
       <c r="F571" s="19"/>
       <c r="G571" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
@@ -9698,7 +10388,7 @@
       <c r="F572" s="18"/>
       <c r="G572" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
@@ -9710,7 +10400,7 @@
       <c r="F573" s="19"/>
       <c r="G573" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.3">
@@ -9722,7 +10412,7 @@
       <c r="F574" s="18"/>
       <c r="G574" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
@@ -9734,7 +10424,7 @@
       <c r="F575" s="19"/>
       <c r="G575" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
@@ -9746,7 +10436,7 @@
       <c r="F576" s="18"/>
       <c r="G576" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
@@ -9758,7 +10448,7 @@
       <c r="F577" s="19"/>
       <c r="G577" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.3">
@@ -9770,7 +10460,7 @@
       <c r="F578" s="18"/>
       <c r="G578" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
@@ -9782,7 +10472,7 @@
       <c r="F579" s="19"/>
       <c r="G579" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
@@ -9794,7 +10484,7 @@
       <c r="F580" s="18"/>
       <c r="G580" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
@@ -9806,7 +10496,7 @@
       <c r="F581" s="19"/>
       <c r="G581" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
@@ -9818,7 +10508,7 @@
       <c r="F582" s="18"/>
       <c r="G582" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
@@ -9830,7 +10520,7 @@
       <c r="F583" s="19"/>
       <c r="G583" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,7 +10532,7 @@
       <c r="F584" s="18"/>
       <c r="G584" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
@@ -9854,7 +10544,7 @@
       <c r="F585" s="19"/>
       <c r="G585" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
@@ -9866,7 +10556,7 @@
       <c r="F586" s="18"/>
       <c r="G586" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
@@ -9878,7 +10568,7 @@
       <c r="F587" s="19"/>
       <c r="G587" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
@@ -9890,7 +10580,7 @@
       <c r="F588" s="18"/>
       <c r="G588" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
@@ -9902,7 +10592,7 @@
       <c r="F589" s="19"/>
       <c r="G589" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
@@ -9914,7 +10604,7 @@
       <c r="F590" s="18"/>
       <c r="G590" s="18">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
@@ -9926,7 +10616,7 @@
       <c r="F591" s="19"/>
       <c r="G591" s="19">
         <f t="shared" si="10"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
@@ -9938,7 +10628,7 @@
       <c r="F592" s="18"/>
       <c r="G592" s="18">
         <f t="shared" ref="G592:G655" si="11">G591+E592-F592</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
@@ -9950,7 +10640,7 @@
       <c r="F593" s="19"/>
       <c r="G593" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
@@ -9962,7 +10652,7 @@
       <c r="F594" s="18"/>
       <c r="G594" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
@@ -9974,7 +10664,7 @@
       <c r="F595" s="19"/>
       <c r="G595" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
@@ -9986,7 +10676,7 @@
       <c r="F596" s="18"/>
       <c r="G596" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
@@ -9998,7 +10688,7 @@
       <c r="F597" s="19"/>
       <c r="G597" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.3">
@@ -10010,7 +10700,7 @@
       <c r="F598" s="18"/>
       <c r="G598" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
@@ -10022,7 +10712,7 @@
       <c r="F599" s="19"/>
       <c r="G599" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.3">
@@ -10034,7 +10724,7 @@
       <c r="F600" s="18"/>
       <c r="G600" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
@@ -10046,7 +10736,7 @@
       <c r="F601" s="19"/>
       <c r="G601" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
@@ -10058,7 +10748,7 @@
       <c r="F602" s="18"/>
       <c r="G602" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
@@ -10070,7 +10760,7 @@
       <c r="F603" s="19"/>
       <c r="G603" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
@@ -10082,7 +10772,7 @@
       <c r="F604" s="18"/>
       <c r="G604" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
@@ -10094,7 +10784,7 @@
       <c r="F605" s="19"/>
       <c r="G605" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
@@ -10106,7 +10796,7 @@
       <c r="F606" s="18"/>
       <c r="G606" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,7 +10808,7 @@
       <c r="F607" s="19"/>
       <c r="G607" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
@@ -10130,7 +10820,7 @@
       <c r="F608" s="18"/>
       <c r="G608" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
@@ -10142,7 +10832,7 @@
       <c r="F609" s="19"/>
       <c r="G609" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
@@ -10154,7 +10844,7 @@
       <c r="F610" s="18"/>
       <c r="G610" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.3">
@@ -10166,7 +10856,7 @@
       <c r="F611" s="19"/>
       <c r="G611" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
@@ -10178,7 +10868,7 @@
       <c r="F612" s="18"/>
       <c r="G612" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
@@ -10190,7 +10880,7 @@
       <c r="F613" s="19"/>
       <c r="G613" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">
@@ -10202,7 +10892,7 @@
       <c r="F614" s="18"/>
       <c r="G614" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
@@ -10214,7 +10904,7 @@
       <c r="F615" s="19"/>
       <c r="G615" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.3">
@@ -10226,7 +10916,7 @@
       <c r="F616" s="18"/>
       <c r="G616" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.3">
@@ -10238,7 +10928,7 @@
       <c r="F617" s="19"/>
       <c r="G617" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.3">
@@ -10250,7 +10940,7 @@
       <c r="F618" s="18"/>
       <c r="G618" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.3">
@@ -10262,7 +10952,7 @@
       <c r="F619" s="19"/>
       <c r="G619" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.3">
@@ -10274,7 +10964,7 @@
       <c r="F620" s="18"/>
       <c r="G620" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.3">
@@ -10286,7 +10976,7 @@
       <c r="F621" s="19"/>
       <c r="G621" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.3">
@@ -10298,7 +10988,7 @@
       <c r="F622" s="18"/>
       <c r="G622" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.3">
@@ -10310,7 +11000,7 @@
       <c r="F623" s="19"/>
       <c r="G623" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
@@ -10322,7 +11012,7 @@
       <c r="F624" s="18"/>
       <c r="G624" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
@@ -10334,7 +11024,7 @@
       <c r="F625" s="19"/>
       <c r="G625" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.3">
@@ -10346,7 +11036,7 @@
       <c r="F626" s="18"/>
       <c r="G626" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.3">
@@ -10358,7 +11048,7 @@
       <c r="F627" s="19"/>
       <c r="G627" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
@@ -10370,7 +11060,7 @@
       <c r="F628" s="18"/>
       <c r="G628" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.3">
@@ -10382,7 +11072,7 @@
       <c r="F629" s="19"/>
       <c r="G629" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,7 +11084,7 @@
       <c r="F630" s="18"/>
       <c r="G630" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.3">
@@ -10406,7 +11096,7 @@
       <c r="F631" s="19"/>
       <c r="G631" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.3">
@@ -10418,7 +11108,7 @@
       <c r="F632" s="18"/>
       <c r="G632" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.3">
@@ -10430,7 +11120,7 @@
       <c r="F633" s="19"/>
       <c r="G633" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.3">
@@ -10442,7 +11132,7 @@
       <c r="F634" s="18"/>
       <c r="G634" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.3">
@@ -10454,7 +11144,7 @@
       <c r="F635" s="19"/>
       <c r="G635" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
@@ -10466,7 +11156,7 @@
       <c r="F636" s="18"/>
       <c r="G636" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.3">
@@ -10478,7 +11168,7 @@
       <c r="F637" s="19"/>
       <c r="G637" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.3">
@@ -10490,7 +11180,7 @@
       <c r="F638" s="18"/>
       <c r="G638" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
@@ -10502,7 +11192,7 @@
       <c r="F639" s="19"/>
       <c r="G639" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.3">
@@ -10514,7 +11204,7 @@
       <c r="F640" s="18"/>
       <c r="G640" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.3">
@@ -10526,7 +11216,7 @@
       <c r="F641" s="19"/>
       <c r="G641" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.3">
@@ -10538,7 +11228,7 @@
       <c r="F642" s="18"/>
       <c r="G642" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.3">
@@ -10550,7 +11240,7 @@
       <c r="F643" s="19"/>
       <c r="G643" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.3">
@@ -10562,7 +11252,7 @@
       <c r="F644" s="18"/>
       <c r="G644" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.3">
@@ -10574,7 +11264,7 @@
       <c r="F645" s="19"/>
       <c r="G645" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.3">
@@ -10586,7 +11276,7 @@
       <c r="F646" s="18"/>
       <c r="G646" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.3">
@@ -10598,7 +11288,7 @@
       <c r="F647" s="19"/>
       <c r="G647" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.3">
@@ -10610,7 +11300,7 @@
       <c r="F648" s="18"/>
       <c r="G648" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.3">
@@ -10622,7 +11312,7 @@
       <c r="F649" s="19"/>
       <c r="G649" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.3">
@@ -10634,7 +11324,7 @@
       <c r="F650" s="18"/>
       <c r="G650" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.3">
@@ -10646,7 +11336,7 @@
       <c r="F651" s="19"/>
       <c r="G651" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.3">
@@ -10658,7 +11348,7 @@
       <c r="F652" s="18"/>
       <c r="G652" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,7 +11360,7 @@
       <c r="F653" s="19"/>
       <c r="G653" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.3">
@@ -10682,7 +11372,7 @@
       <c r="F654" s="18"/>
       <c r="G654" s="18">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.3">
@@ -10694,7 +11384,7 @@
       <c r="F655" s="19"/>
       <c r="G655" s="19">
         <f t="shared" si="11"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.3">
@@ -10706,7 +11396,7 @@
       <c r="F656" s="18"/>
       <c r="G656" s="18">
         <f t="shared" ref="G656:G719" si="12">G655+E656-F656</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.3">
@@ -10718,7 +11408,7 @@
       <c r="F657" s="19"/>
       <c r="G657" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.3">
@@ -10730,7 +11420,7 @@
       <c r="F658" s="18"/>
       <c r="G658" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.3">
@@ -10742,7 +11432,7 @@
       <c r="F659" s="19"/>
       <c r="G659" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.3">
@@ -10754,7 +11444,7 @@
       <c r="F660" s="18"/>
       <c r="G660" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.3">
@@ -10766,7 +11456,7 @@
       <c r="F661" s="19"/>
       <c r="G661" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.3">
@@ -10778,7 +11468,7 @@
       <c r="F662" s="18"/>
       <c r="G662" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.3">
@@ -10790,7 +11480,7 @@
       <c r="F663" s="19"/>
       <c r="G663" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.3">
@@ -10802,7 +11492,7 @@
       <c r="F664" s="18"/>
       <c r="G664" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.3">
@@ -10814,7 +11504,7 @@
       <c r="F665" s="19"/>
       <c r="G665" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.3">
@@ -10826,7 +11516,7 @@
       <c r="F666" s="18"/>
       <c r="G666" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.3">
@@ -10838,7 +11528,7 @@
       <c r="F667" s="19"/>
       <c r="G667" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.3">
@@ -10850,7 +11540,7 @@
       <c r="F668" s="18"/>
       <c r="G668" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.3">
@@ -10862,7 +11552,7 @@
       <c r="F669" s="19"/>
       <c r="G669" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.3">
@@ -10874,7 +11564,7 @@
       <c r="F670" s="18"/>
       <c r="G670" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.3">
@@ -10886,7 +11576,7 @@
       <c r="F671" s="19"/>
       <c r="G671" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.3">
@@ -10898,7 +11588,7 @@
       <c r="F672" s="18"/>
       <c r="G672" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.3">
@@ -10910,7 +11600,7 @@
       <c r="F673" s="19"/>
       <c r="G673" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.3">
@@ -10922,7 +11612,7 @@
       <c r="F674" s="18"/>
       <c r="G674" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.3">
@@ -10934,7 +11624,7 @@
       <c r="F675" s="19"/>
       <c r="G675" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.3">
@@ -10946,7 +11636,7 @@
       <c r="F676" s="18"/>
       <c r="G676" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.3">
@@ -10958,7 +11648,7 @@
       <c r="F677" s="19"/>
       <c r="G677" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.3">
@@ -10970,7 +11660,7 @@
       <c r="F678" s="18"/>
       <c r="G678" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.3">
@@ -10982,7 +11672,7 @@
       <c r="F679" s="19"/>
       <c r="G679" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.3">
@@ -10994,7 +11684,7 @@
       <c r="F680" s="18"/>
       <c r="G680" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.3">
@@ -11006,7 +11696,7 @@
       <c r="F681" s="19"/>
       <c r="G681" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.3">
@@ -11018,7 +11708,7 @@
       <c r="F682" s="18"/>
       <c r="G682" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.3">
@@ -11030,7 +11720,7 @@
       <c r="F683" s="19"/>
       <c r="G683" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.3">
@@ -11042,7 +11732,7 @@
       <c r="F684" s="18"/>
       <c r="G684" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.3">
@@ -11054,7 +11744,7 @@
       <c r="F685" s="19"/>
       <c r="G685" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.3">
@@ -11066,7 +11756,7 @@
       <c r="F686" s="18"/>
       <c r="G686" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.3">
@@ -11078,7 +11768,7 @@
       <c r="F687" s="19"/>
       <c r="G687" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.3">
@@ -11090,7 +11780,7 @@
       <c r="F688" s="18"/>
       <c r="G688" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.3">
@@ -11102,7 +11792,7 @@
       <c r="F689" s="19"/>
       <c r="G689" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.3">
@@ -11114,7 +11804,7 @@
       <c r="F690" s="18"/>
       <c r="G690" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.3">
@@ -11126,7 +11816,7 @@
       <c r="F691" s="19"/>
       <c r="G691" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.3">
@@ -11138,7 +11828,7 @@
       <c r="F692" s="18"/>
       <c r="G692" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.3">
@@ -11150,7 +11840,7 @@
       <c r="F693" s="19"/>
       <c r="G693" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.3">
@@ -11162,7 +11852,7 @@
       <c r="F694" s="18"/>
       <c r="G694" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.3">
@@ -11174,7 +11864,7 @@
       <c r="F695" s="19"/>
       <c r="G695" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.3">
@@ -11186,7 +11876,7 @@
       <c r="F696" s="18"/>
       <c r="G696" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.3">
@@ -11198,7 +11888,7 @@
       <c r="F697" s="19"/>
       <c r="G697" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.3">
@@ -11210,7 +11900,7 @@
       <c r="F698" s="18"/>
       <c r="G698" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,7 +11912,7 @@
       <c r="F699" s="19"/>
       <c r="G699" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.3">
@@ -11234,7 +11924,7 @@
       <c r="F700" s="18"/>
       <c r="G700" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.3">
@@ -11246,7 +11936,7 @@
       <c r="F701" s="19"/>
       <c r="G701" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.3">
@@ -11258,7 +11948,7 @@
       <c r="F702" s="18"/>
       <c r="G702" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.3">
@@ -11270,7 +11960,7 @@
       <c r="F703" s="19"/>
       <c r="G703" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.3">
@@ -11282,7 +11972,7 @@
       <c r="F704" s="18"/>
       <c r="G704" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.3">
@@ -11294,7 +11984,7 @@
       <c r="F705" s="19"/>
       <c r="G705" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.3">
@@ -11306,7 +11996,7 @@
       <c r="F706" s="18"/>
       <c r="G706" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.3">
@@ -11318,7 +12008,7 @@
       <c r="F707" s="19"/>
       <c r="G707" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.3">
@@ -11330,7 +12020,7 @@
       <c r="F708" s="18"/>
       <c r="G708" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.3">
@@ -11342,7 +12032,7 @@
       <c r="F709" s="19"/>
       <c r="G709" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.3">
@@ -11354,7 +12044,7 @@
       <c r="F710" s="18"/>
       <c r="G710" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.3">
@@ -11366,7 +12056,7 @@
       <c r="F711" s="19"/>
       <c r="G711" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.3">
@@ -11378,7 +12068,7 @@
       <c r="F712" s="18"/>
       <c r="G712" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.3">
@@ -11390,7 +12080,7 @@
       <c r="F713" s="19"/>
       <c r="G713" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.3">
@@ -11402,7 +12092,7 @@
       <c r="F714" s="18"/>
       <c r="G714" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.3">
@@ -11414,7 +12104,7 @@
       <c r="F715" s="19"/>
       <c r="G715" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.3">
@@ -11426,7 +12116,7 @@
       <c r="F716" s="18"/>
       <c r="G716" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.3">
@@ -11438,7 +12128,7 @@
       <c r="F717" s="19"/>
       <c r="G717" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.3">
@@ -11450,7 +12140,7 @@
       <c r="F718" s="18"/>
       <c r="G718" s="18">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.3">
@@ -11462,7 +12152,7 @@
       <c r="F719" s="19"/>
       <c r="G719" s="19">
         <f t="shared" si="12"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
@@ -11474,7 +12164,7 @@
       <c r="F720" s="18"/>
       <c r="G720" s="18">
         <f t="shared" ref="G720:G735" si="13">G719+E720-F720</f>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.3">
@@ -11486,7 +12176,7 @@
       <c r="F721" s="19"/>
       <c r="G721" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.3">
@@ -11498,7 +12188,7 @@
       <c r="F722" s="18"/>
       <c r="G722" s="18">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.3">
@@ -11510,7 +12200,7 @@
       <c r="F723" s="19"/>
       <c r="G723" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.3">
@@ -11522,7 +12212,7 @@
       <c r="F724" s="18"/>
       <c r="G724" s="18">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.3">
@@ -11534,7 +12224,7 @@
       <c r="F725" s="19"/>
       <c r="G725" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.3">
@@ -11546,7 +12236,7 @@
       <c r="F726" s="18"/>
       <c r="G726" s="18">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.3">
@@ -11558,7 +12248,7 @@
       <c r="F727" s="19"/>
       <c r="G727" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.3">
@@ -11570,7 +12260,7 @@
       <c r="F728" s="18"/>
       <c r="G728" s="18">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.3">
@@ -11582,7 +12272,7 @@
       <c r="F729" s="19"/>
       <c r="G729" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.3">
@@ -11594,7 +12284,7 @@
       <c r="F730" s="18"/>
       <c r="G730" s="18">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.3">
@@ -11606,7 +12296,7 @@
       <c r="F731" s="19"/>
       <c r="G731" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.3">
@@ -11618,7 +12308,7 @@
       <c r="F732" s="18"/>
       <c r="G732" s="18">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.3">
@@ -11630,7 +12320,7 @@
       <c r="F733" s="19"/>
       <c r="G733" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.3">
@@ -11642,7 +12332,7 @@
       <c r="F734" s="18"/>
       <c r="G734" s="18">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.3">
@@ -11654,7 +12344,7 @@
       <c r="F735" s="19"/>
       <c r="G735" s="19">
         <f t="shared" si="13"/>
-        <v>73776</v>
+        <v>89726</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.3">

--- a/NBFC-MF/CashFlow.xlsx
+++ b/NBFC-MF/CashFlow.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="238">
   <si>
     <t>Transaction Description</t>
   </si>
@@ -724,6 +724,24 @@
   <si>
     <t>228Ichal</t>
   </si>
+  <si>
+    <t>229echal</t>
+  </si>
+  <si>
+    <t>230Moirangkhm</t>
+  </si>
+  <si>
+    <t>231Seema</t>
+  </si>
+  <si>
+    <t>chicken; veg fish</t>
+  </si>
+  <si>
+    <t>232Ranita</t>
+  </si>
+  <si>
+    <t>ngari</t>
+  </si>
 </sst>
 </file>
 
@@ -6251,10 +6269,16 @@
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A229" s="17"/>
+      <c r="A229" s="17">
+        <v>46295</v>
+      </c>
       <c r="B229" s="14"/>
-      <c r="C229" s="14"/>
-      <c r="D229" s="14"/>
+      <c r="C229" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D229" s="14" t="s">
+        <v>19</v>
+      </c>
       <c r="E229" s="14"/>
       <c r="F229" s="14"/>
       <c r="G229" s="14">
@@ -6264,1388 +6288,2538 @@
       <c r="J229" s="21"/>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A230" s="16"/>
-      <c r="B230" s="13"/>
-      <c r="C230" s="13"/>
-      <c r="D230" s="13"/>
-      <c r="E230" s="13"/>
+      <c r="A230" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B230" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C230" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D230" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E230" s="13">
+        <v>300</v>
+      </c>
       <c r="F230" s="13"/>
       <c r="G230" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>90026</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A231" s="17"/>
-      <c r="B231" s="14"/>
-      <c r="C231" s="14"/>
-      <c r="D231" s="14"/>
-      <c r="E231" s="14"/>
+      <c r="A231" s="17">
+        <v>46295</v>
+      </c>
+      <c r="B231" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C231" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D231" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E231" s="14">
+        <v>100</v>
+      </c>
       <c r="F231" s="14"/>
       <c r="G231" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>90126</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A232" s="16"/>
-      <c r="B232" s="13"/>
-      <c r="C232" s="13"/>
-      <c r="D232" s="13"/>
-      <c r="E232" s="13"/>
+      <c r="A232" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B232" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C232" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D232" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E232" s="13">
+        <v>2100</v>
+      </c>
       <c r="F232" s="13"/>
       <c r="G232" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>92226</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A233" s="17"/>
-      <c r="B233" s="14"/>
-      <c r="C233" s="14"/>
-      <c r="D233" s="14"/>
-      <c r="E233" s="14"/>
+      <c r="A233" s="17">
+        <v>46295</v>
+      </c>
+      <c r="B233" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C233" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D233" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E233" s="14">
+        <v>300</v>
+      </c>
       <c r="F233" s="14"/>
       <c r="G233" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>92526</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A234" s="16"/>
-      <c r="B234" s="13"/>
-      <c r="C234" s="13"/>
-      <c r="D234" s="13"/>
-      <c r="E234" s="13"/>
+      <c r="A234" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B234" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C234" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D234" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E234" s="13">
+        <v>200</v>
+      </c>
       <c r="F234" s="13"/>
       <c r="G234" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>92726</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A235" s="17"/>
-      <c r="B235" s="14"/>
-      <c r="C235" s="14"/>
-      <c r="D235" s="14"/>
-      <c r="E235" s="14"/>
+      <c r="A235" s="17">
+        <v>46295</v>
+      </c>
+      <c r="B235" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C235" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D235" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E235" s="14">
+        <v>1400</v>
+      </c>
       <c r="F235" s="14"/>
       <c r="G235" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A236" s="16"/>
-      <c r="B236" s="13"/>
-      <c r="C236" s="13"/>
-      <c r="D236" s="13"/>
-      <c r="E236" s="13"/>
+        <v>94126</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A236" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B236" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C236" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D236" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E236" s="13">
+        <v>4200</v>
+      </c>
       <c r="F236" s="13"/>
       <c r="G236" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>98326</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A237" s="17"/>
-      <c r="B237" s="14"/>
-      <c r="C237" s="14"/>
-      <c r="D237" s="14"/>
-      <c r="E237" s="14"/>
+      <c r="A237" s="17">
+        <v>46295</v>
+      </c>
+      <c r="B237" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C237" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E237" s="14">
+        <v>4200</v>
+      </c>
       <c r="F237" s="14"/>
       <c r="G237" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>102526</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A238" s="16"/>
-      <c r="B238" s="13"/>
-      <c r="C238" s="13"/>
-      <c r="D238" s="13"/>
-      <c r="E238" s="13"/>
+      <c r="A238" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B238" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C238" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D238" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E238" s="13">
+        <v>3000</v>
+      </c>
       <c r="F238" s="13"/>
       <c r="G238" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>105526</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A239" s="17"/>
-      <c r="B239" s="14"/>
-      <c r="C239" s="14"/>
-      <c r="D239" s="14"/>
-      <c r="E239" s="14"/>
+      <c r="A239" s="17">
+        <v>46296</v>
+      </c>
+      <c r="B239" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C239" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D239" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E239" s="14">
+        <v>300</v>
+      </c>
       <c r="F239" s="14"/>
       <c r="G239" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>105826</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A240" s="16"/>
-      <c r="B240" s="13"/>
-      <c r="C240" s="13"/>
-      <c r="D240" s="13"/>
-      <c r="E240" s="13"/>
+      <c r="A240" s="16">
+        <v>46296</v>
+      </c>
+      <c r="B240" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C240" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D240" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E240" s="13">
+        <v>100</v>
+      </c>
       <c r="F240" s="13"/>
       <c r="G240" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>105926</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A241" s="17"/>
-      <c r="B241" s="14"/>
-      <c r="C241" s="14"/>
-      <c r="D241" s="14"/>
-      <c r="E241" s="14"/>
+      <c r="A241" s="17">
+        <v>46296</v>
+      </c>
+      <c r="B241" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C241" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D241" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E241" s="14">
+        <v>200</v>
+      </c>
       <c r="F241" s="14"/>
       <c r="G241" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>106126</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A242" s="16"/>
-      <c r="B242" s="13"/>
-      <c r="C242" s="13"/>
-      <c r="D242" s="13"/>
-      <c r="E242" s="13"/>
+      <c r="A242" s="16">
+        <v>46296</v>
+      </c>
+      <c r="B242" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C242" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D242" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E242" s="13">
+        <v>3000</v>
+      </c>
       <c r="F242" s="13"/>
       <c r="G242" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>109126</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" s="17"/>
-      <c r="B243" s="14"/>
-      <c r="C243" s="14"/>
-      <c r="D243" s="14"/>
-      <c r="E243" s="14"/>
+      <c r="A243" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B243" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C243" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D243" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E243" s="14">
+        <v>600</v>
+      </c>
       <c r="F243" s="14"/>
       <c r="G243" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>109726</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A244" s="16"/>
-      <c r="B244" s="13"/>
-      <c r="C244" s="13"/>
-      <c r="D244" s="13"/>
-      <c r="E244" s="13"/>
+      <c r="A244" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B244" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C244" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D244" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E244" s="13">
+        <v>300</v>
+      </c>
       <c r="F244" s="13"/>
       <c r="G244" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>110026</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" s="17"/>
-      <c r="B245" s="14"/>
-      <c r="C245" s="14"/>
-      <c r="D245" s="14"/>
-      <c r="E245" s="14"/>
+      <c r="A245" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B245" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C245" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D245" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E245" s="14">
+        <v>200</v>
+      </c>
       <c r="F245" s="14"/>
       <c r="G245" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>110226</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" s="16"/>
-      <c r="B246" s="13"/>
-      <c r="C246" s="13"/>
-      <c r="D246" s="13"/>
-      <c r="E246" s="13"/>
+      <c r="A246" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B246" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C246" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D246" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E246" s="13">
+        <v>300</v>
+      </c>
       <c r="F246" s="13"/>
       <c r="G246" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>110526</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" s="17"/>
-      <c r="B247" s="14"/>
-      <c r="C247" s="14"/>
-      <c r="D247" s="14"/>
-      <c r="E247" s="14"/>
+      <c r="A247" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B247" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C247" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D247" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E247" s="14">
+        <v>100</v>
+      </c>
       <c r="F247" s="14"/>
       <c r="G247" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>110626</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" s="16"/>
-      <c r="B248" s="13"/>
-      <c r="C248" s="13"/>
-      <c r="D248" s="13"/>
-      <c r="E248" s="13"/>
+      <c r="A248" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B248" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C248" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D248" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E248" s="13">
+        <v>1400</v>
+      </c>
       <c r="F248" s="13"/>
       <c r="G248" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>112026</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="17"/>
-      <c r="B249" s="14"/>
-      <c r="C249" s="14"/>
-      <c r="D249" s="14"/>
-      <c r="E249" s="14"/>
+      <c r="A249" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B249" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C249" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D249" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E249" s="14">
+        <v>2100</v>
+      </c>
       <c r="F249" s="14"/>
       <c r="G249" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>114126</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="16"/>
-      <c r="B250" s="13"/>
-      <c r="C250" s="13"/>
-      <c r="D250" s="13"/>
-      <c r="E250" s="13"/>
+      <c r="A250" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B250" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C250" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D250" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E250" s="13">
+        <v>1400</v>
+      </c>
       <c r="F250" s="13"/>
       <c r="G250" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" s="17"/>
-      <c r="B251" s="14"/>
-      <c r="C251" s="14"/>
-      <c r="D251" s="14"/>
-      <c r="E251" s="14"/>
+        <v>115526</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A251" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B251" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C251" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D251" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E251" s="14">
+        <v>1750</v>
+      </c>
       <c r="F251" s="14"/>
       <c r="G251" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>117276</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A252" s="16"/>
-      <c r="B252" s="13"/>
-      <c r="C252" s="13"/>
-      <c r="D252" s="13"/>
-      <c r="E252" s="13"/>
+      <c r="A252" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B252" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C252" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D252" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E252" s="13">
+        <v>2100</v>
+      </c>
       <c r="F252" s="13"/>
       <c r="G252" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>119376</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" s="17"/>
-      <c r="B253" s="14"/>
-      <c r="C253" s="14"/>
-      <c r="D253" s="14"/>
-      <c r="E253" s="14"/>
+      <c r="A253" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B253" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C253" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D253" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E253" s="14">
+        <v>12600</v>
+      </c>
       <c r="F253" s="14"/>
       <c r="G253" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>131976</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A254" s="16"/>
-      <c r="B254" s="13"/>
-      <c r="C254" s="13"/>
-      <c r="D254" s="13"/>
-      <c r="E254" s="13"/>
+      <c r="A254" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B254" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C254" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D254" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E254" s="13">
+        <v>1400</v>
+      </c>
       <c r="F254" s="13"/>
       <c r="G254" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>133376</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A255" s="17"/>
-      <c r="B255" s="14"/>
-      <c r="C255" s="14"/>
-      <c r="D255" s="14"/>
-      <c r="E255" s="14"/>
+      <c r="A255" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B255" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C255" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D255" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E255" s="14">
+        <v>1400</v>
+      </c>
       <c r="F255" s="14"/>
       <c r="G255" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
+        <v>134776</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" s="16"/>
-      <c r="B256" s="13"/>
-      <c r="C256" s="13"/>
-      <c r="D256" s="13"/>
-      <c r="E256" s="13"/>
+      <c r="A256" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B256" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C256" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D256" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E256" s="13">
+        <v>350</v>
+      </c>
       <c r="F256" s="13"/>
       <c r="G256" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A257" s="17"/>
-      <c r="B257" s="14"/>
-      <c r="C257" s="14"/>
-      <c r="D257" s="14"/>
-      <c r="E257" s="14"/>
+        <v>135126</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A257" s="17">
+        <v>46297</v>
+      </c>
+      <c r="B257" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C257" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D257" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E257" s="14">
+        <v>600</v>
+      </c>
       <c r="F257" s="14"/>
       <c r="G257" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A258" s="16"/>
+        <v>135726</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A258" s="16">
+        <v>46298</v>
+      </c>
       <c r="B258" s="13"/>
-      <c r="C258" s="13"/>
-      <c r="D258" s="13"/>
+      <c r="C258" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D258" s="13" t="s">
+        <v>19</v>
+      </c>
       <c r="E258" s="13"/>
       <c r="F258" s="13"/>
       <c r="G258" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A259" s="17"/>
-      <c r="B259" s="14"/>
-      <c r="C259" s="14"/>
-      <c r="D259" s="14"/>
-      <c r="E259" s="14"/>
+        <v>135726</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A259" s="17">
+        <v>46298</v>
+      </c>
+      <c r="B259" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C259" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D259" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E259" s="14">
+        <v>300</v>
+      </c>
       <c r="F259" s="14"/>
       <c r="G259" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A260" s="16"/>
-      <c r="B260" s="13"/>
-      <c r="C260" s="13"/>
-      <c r="D260" s="13"/>
-      <c r="E260" s="13"/>
+        <v>136026</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A260" s="16">
+        <v>46298</v>
+      </c>
+      <c r="B260" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C260" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D260" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E260" s="13">
+        <v>300</v>
+      </c>
       <c r="F260" s="13"/>
       <c r="G260" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A261" s="17"/>
-      <c r="B261" s="14"/>
-      <c r="C261" s="14"/>
-      <c r="D261" s="14"/>
-      <c r="E261" s="14"/>
+        <v>136326</v>
+      </c>
+      <c r="I260" s="21"/>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A261" s="17">
+        <v>46298</v>
+      </c>
+      <c r="B261" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C261" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D261" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E261" s="14">
+        <v>200</v>
+      </c>
       <c r="F261" s="14"/>
       <c r="G261" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A262" s="16"/>
-      <c r="B262" s="13"/>
-      <c r="C262" s="13"/>
-      <c r="D262" s="13"/>
-      <c r="E262" s="13"/>
+        <v>136526</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A262" s="16">
+        <v>46298</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C262" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D262" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E262" s="13">
+        <v>100</v>
+      </c>
       <c r="F262" s="13"/>
       <c r="G262" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A263" s="17"/>
-      <c r="B263" s="14"/>
-      <c r="C263" s="14"/>
-      <c r="D263" s="14"/>
-      <c r="E263" s="14"/>
+        <v>136626</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A263" s="17">
+        <v>46298</v>
+      </c>
+      <c r="B263" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C263" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D263" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E263" s="14">
+        <v>300</v>
+      </c>
       <c r="F263" s="14"/>
       <c r="G263" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A264" s="16"/>
-      <c r="B264" s="13"/>
-      <c r="C264" s="13"/>
-      <c r="D264" s="13"/>
-      <c r="E264" s="13"/>
+        <v>136926</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A264" s="16">
+        <v>46299</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C264" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D264" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E264" s="13">
+        <v>300</v>
+      </c>
       <c r="F264" s="13"/>
       <c r="G264" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A265" s="17"/>
-      <c r="B265" s="14"/>
-      <c r="C265" s="14"/>
-      <c r="D265" s="14"/>
-      <c r="E265" s="14"/>
+        <v>137226</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A265" s="17">
+        <v>46299</v>
+      </c>
+      <c r="B265" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C265" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D265" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E265" s="14">
+        <v>200</v>
+      </c>
       <c r="F265" s="14"/>
       <c r="G265" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A266" s="16"/>
-      <c r="B266" s="13"/>
-      <c r="C266" s="13"/>
-      <c r="D266" s="13"/>
-      <c r="E266" s="13"/>
+        <v>137426</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A266" s="16">
+        <v>46299</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C266" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D266" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E266" s="13">
+        <v>100</v>
+      </c>
       <c r="F266" s="13"/>
       <c r="G266" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A267" s="17"/>
-      <c r="B267" s="14"/>
-      <c r="C267" s="14"/>
-      <c r="D267" s="14"/>
-      <c r="E267" s="14"/>
+        <v>137526</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A267" s="17">
+        <v>46299</v>
+      </c>
+      <c r="B267" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C267" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D267" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E267" s="14">
+        <v>300</v>
+      </c>
       <c r="F267" s="14"/>
       <c r="G267" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A268" s="16"/>
-      <c r="B268" s="13"/>
-      <c r="C268" s="13"/>
-      <c r="D268" s="13"/>
-      <c r="E268" s="13"/>
+        <v>137826</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A268" s="16">
+        <v>46299</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C268" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D268" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E268" s="13">
+        <v>4200</v>
+      </c>
       <c r="F268" s="13"/>
       <c r="G268" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A269" s="17"/>
-      <c r="B269" s="14"/>
-      <c r="C269" s="14"/>
-      <c r="D269" s="14"/>
-      <c r="E269" s="14"/>
+        <v>142026</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A269" s="17">
+        <v>46299</v>
+      </c>
+      <c r="B269" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C269" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D269" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E269" s="14">
+        <v>1400</v>
+      </c>
       <c r="F269" s="14"/>
       <c r="G269" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A270" s="16"/>
-      <c r="B270" s="13"/>
-      <c r="C270" s="13"/>
-      <c r="D270" s="13"/>
-      <c r="E270" s="13"/>
+        <v>143426</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A270" s="16">
+        <v>46299</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C270" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D270" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E270" s="13">
+        <v>200</v>
+      </c>
       <c r="F270" s="13"/>
       <c r="G270" s="13">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A271" s="17"/>
-      <c r="B271" s="14"/>
-      <c r="C271" s="14"/>
-      <c r="D271" s="14"/>
-      <c r="E271" s="14"/>
+        <v>143626</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A271" s="17">
+        <v>46300</v>
+      </c>
+      <c r="B271" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C271" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D271" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E271" s="14">
+        <v>300</v>
+      </c>
       <c r="F271" s="14"/>
       <c r="G271" s="14">
         <f t="shared" si="5"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A272" s="16"/>
-      <c r="B272" s="13"/>
-      <c r="C272" s="13"/>
-      <c r="D272" s="13"/>
-      <c r="E272" s="13"/>
+        <v>143926</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A272" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C272" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D272" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E272" s="13">
+        <v>200</v>
+      </c>
       <c r="F272" s="13"/>
       <c r="G272" s="13">
         <f t="shared" ref="G272:G335" si="6">G271+E272-F272</f>
-        <v>89726</v>
+        <v>144126</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A273" s="17"/>
-      <c r="B273" s="14"/>
-      <c r="C273" s="14"/>
-      <c r="D273" s="14"/>
-      <c r="E273" s="14"/>
+      <c r="A273" s="17">
+        <v>46300</v>
+      </c>
+      <c r="B273" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C273" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D273" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E273" s="14">
+        <v>100</v>
+      </c>
       <c r="F273" s="14"/>
       <c r="G273" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>144226</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A274" s="16"/>
-      <c r="B274" s="13"/>
-      <c r="C274" s="13"/>
-      <c r="D274" s="13"/>
-      <c r="E274" s="13"/>
+      <c r="A274" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B274" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C274" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D274" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E274" s="13">
+        <v>300</v>
+      </c>
       <c r="F274" s="13"/>
       <c r="G274" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>144526</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A275" s="17"/>
-      <c r="B275" s="14"/>
-      <c r="C275" s="14"/>
-      <c r="D275" s="14"/>
-      <c r="E275" s="14"/>
+      <c r="A275" s="17">
+        <v>46300</v>
+      </c>
+      <c r="B275" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C275" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D275" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E275" s="14">
+        <v>4200</v>
+      </c>
       <c r="F275" s="14"/>
       <c r="G275" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>148726</v>
       </c>
       <c r="I275" s="21"/>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A276" s="16"/>
-      <c r="B276" s="13"/>
-      <c r="C276" s="13"/>
-      <c r="D276" s="13"/>
-      <c r="E276" s="13"/>
+      <c r="A276" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C276" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D276" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E276" s="13">
+        <v>7000</v>
+      </c>
       <c r="F276" s="13"/>
       <c r="G276" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>155726</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A277" s="17"/>
-      <c r="B277" s="14"/>
-      <c r="C277" s="14"/>
-      <c r="D277" s="14"/>
-      <c r="E277" s="14"/>
+      <c r="A277" s="17">
+        <v>46300</v>
+      </c>
+      <c r="B277" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C277" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D277" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E277" s="14">
+        <v>7000</v>
+      </c>
       <c r="F277" s="14"/>
       <c r="G277" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>162726</v>
       </c>
       <c r="I277" s="21"/>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A278" s="16"/>
-      <c r="B278" s="13"/>
-      <c r="C278" s="13"/>
-      <c r="D278" s="13"/>
-      <c r="E278" s="13"/>
+      <c r="A278" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B278" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C278" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D278" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E278" s="13">
+        <v>1400</v>
+      </c>
       <c r="F278" s="13"/>
       <c r="G278" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>164126</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A279" s="17"/>
-      <c r="B279" s="14"/>
-      <c r="C279" s="14"/>
-      <c r="D279" s="14"/>
-      <c r="E279" s="14"/>
+      <c r="A279" s="17">
+        <v>46300</v>
+      </c>
+      <c r="B279" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C279" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D279" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E279" s="14">
+        <v>1400</v>
+      </c>
       <c r="F279" s="14"/>
       <c r="G279" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>165526</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A280" s="16"/>
-      <c r="B280" s="13"/>
-      <c r="C280" s="13"/>
-      <c r="D280" s="13"/>
-      <c r="E280" s="13"/>
+      <c r="A280" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B280" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C280" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D280" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E280" s="13">
+        <v>1400</v>
+      </c>
       <c r="F280" s="13"/>
       <c r="G280" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>166926</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A281" s="17"/>
-      <c r="B281" s="14"/>
-      <c r="C281" s="14"/>
-      <c r="D281" s="14"/>
-      <c r="E281" s="14"/>
+      <c r="A281" s="17">
+        <v>46300</v>
+      </c>
+      <c r="B281" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C281" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D281" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E281" s="14">
+        <v>2100</v>
+      </c>
       <c r="F281" s="14"/>
       <c r="G281" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>169026</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A282" s="16"/>
-      <c r="B282" s="13"/>
-      <c r="C282" s="13"/>
-      <c r="D282" s="13"/>
-      <c r="E282" s="13"/>
+      <c r="A282" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B282" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C282" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D282" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E282" s="13">
+        <v>2500</v>
+      </c>
       <c r="F282" s="13"/>
       <c r="G282" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A283" s="17"/>
-      <c r="B283" s="14"/>
-      <c r="C283" s="14"/>
-      <c r="D283" s="14"/>
+        <v>171526</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A283" s="17">
+        <v>46300</v>
+      </c>
+      <c r="B283" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C283" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D283" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E283" s="14"/>
-      <c r="F283" s="14"/>
+      <c r="F283" s="14">
+        <v>60000</v>
+      </c>
       <c r="G283" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>111526</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A284" s="16"/>
-      <c r="B284" s="13"/>
-      <c r="C284" s="13"/>
-      <c r="D284" s="13"/>
+      <c r="A284" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B284" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C284" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D284" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E284" s="13"/>
-      <c r="F284" s="13"/>
+      <c r="F284" s="13">
+        <v>30000</v>
+      </c>
       <c r="G284" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>81526</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A285" s="17"/>
-      <c r="B285" s="14"/>
-      <c r="C285" s="14"/>
-      <c r="D285" s="14"/>
-      <c r="E285" s="14"/>
+      <c r="A285" s="17">
+        <v>46301</v>
+      </c>
+      <c r="B285" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C285" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D285" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E285" s="14">
+        <v>300</v>
+      </c>
       <c r="F285" s="14"/>
       <c r="G285" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>81826</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A286" s="16"/>
-      <c r="B286" s="13"/>
-      <c r="C286" s="13"/>
-      <c r="D286" s="13"/>
-      <c r="E286" s="13"/>
+      <c r="A286" s="16">
+        <v>46301</v>
+      </c>
+      <c r="B286" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C286" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D286" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E286" s="13">
+        <v>200</v>
+      </c>
       <c r="F286" s="13"/>
       <c r="G286" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>82026</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A287" s="17"/>
-      <c r="B287" s="14"/>
-      <c r="C287" s="14"/>
-      <c r="D287" s="14"/>
-      <c r="E287" s="14"/>
+      <c r="A287" s="17">
+        <v>46301</v>
+      </c>
+      <c r="B287" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C287" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D287" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E287" s="14">
+        <v>100</v>
+      </c>
       <c r="F287" s="14"/>
       <c r="G287" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>82126</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A288" s="16"/>
-      <c r="B288" s="13"/>
-      <c r="C288" s="13"/>
-      <c r="D288" s="13"/>
-      <c r="E288" s="13"/>
+      <c r="A288" s="16">
+        <v>46301</v>
+      </c>
+      <c r="B288" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C288" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D288" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E288" s="13">
+        <v>2100</v>
+      </c>
       <c r="F288" s="13"/>
       <c r="G288" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>84226</v>
       </c>
       <c r="I288" s="21"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A289" s="17"/>
-      <c r="B289" s="14"/>
-      <c r="C289" s="14"/>
-      <c r="D289" s="14"/>
-      <c r="E289" s="14"/>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A289" s="17">
+        <v>46301</v>
+      </c>
+      <c r="B289" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C289" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D289" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E289" s="14">
+        <v>200</v>
+      </c>
       <c r="F289" s="14"/>
       <c r="G289" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" s="16"/>
-      <c r="B290" s="13"/>
-      <c r="C290" s="13"/>
-      <c r="D290" s="13"/>
-      <c r="E290" s="13"/>
+        <v>84426</v>
+      </c>
+      <c r="J289" s="21"/>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A290" s="16">
+        <v>46301</v>
+      </c>
+      <c r="B290" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="C290" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D290" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E290" s="13">
+        <v>500</v>
+      </c>
       <c r="F290" s="13"/>
       <c r="G290" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A291" s="17"/>
-      <c r="B291" s="14"/>
-      <c r="C291" s="14"/>
-      <c r="D291" s="14"/>
+        <v>84926</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A291" s="17">
+        <v>46301</v>
+      </c>
+      <c r="B291" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C291" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D291" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E291" s="14"/>
-      <c r="F291" s="14"/>
+      <c r="F291" s="14">
+        <f>500+600</f>
+        <v>1100</v>
+      </c>
       <c r="G291" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A292" s="16"/>
-      <c r="B292" s="13"/>
-      <c r="C292" s="13"/>
-      <c r="D292" s="13"/>
-      <c r="E292" s="13"/>
+        <v>83826</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A292" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B292" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C292" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D292" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E292" s="13">
+        <v>300</v>
+      </c>
       <c r="F292" s="13"/>
       <c r="G292" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" s="17"/>
-      <c r="B293" s="14"/>
-      <c r="C293" s="14"/>
-      <c r="D293" s="14"/>
-      <c r="E293" s="14"/>
+        <v>84126</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A293" s="17">
+        <v>46302</v>
+      </c>
+      <c r="B293" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C293" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D293" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E293" s="14">
+        <v>500</v>
+      </c>
       <c r="F293" s="14"/>
       <c r="G293" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="16"/>
-      <c r="B294" s="13"/>
-      <c r="C294" s="13"/>
-      <c r="D294" s="13"/>
-      <c r="E294" s="13"/>
+        <v>84626</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A294" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B294" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C294" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D294" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E294" s="13">
+        <v>2100</v>
+      </c>
       <c r="F294" s="13"/>
       <c r="G294" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A295" s="17"/>
-      <c r="B295" s="14"/>
-      <c r="C295" s="14"/>
-      <c r="D295" s="14"/>
-      <c r="E295" s="14"/>
+        <v>86726</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A295" s="17">
+        <v>46302</v>
+      </c>
+      <c r="B295" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C295" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D295" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E295" s="14">
+        <v>200</v>
+      </c>
       <c r="F295" s="14"/>
       <c r="G295" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296" s="16"/>
-      <c r="B296" s="13"/>
-      <c r="C296" s="13"/>
-      <c r="D296" s="13"/>
-      <c r="E296" s="13"/>
+        <v>86926</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A296" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B296" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C296" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D296" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E296" s="13">
+        <v>4200</v>
+      </c>
       <c r="F296" s="13"/>
       <c r="G296" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" s="17"/>
-      <c r="B297" s="14"/>
-      <c r="C297" s="14"/>
-      <c r="D297" s="14"/>
-      <c r="E297" s="14"/>
+        <v>91126</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A297" s="17">
+        <v>46302</v>
+      </c>
+      <c r="B297" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C297" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D297" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E297" s="14">
+        <v>600</v>
+      </c>
       <c r="F297" s="14"/>
       <c r="G297" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" s="16"/>
-      <c r="B298" s="13"/>
-      <c r="C298" s="13"/>
-      <c r="D298" s="13"/>
-      <c r="E298" s="13"/>
+        <v>91726</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A298" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C298" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D298" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E298" s="13">
+        <v>100</v>
+      </c>
       <c r="F298" s="13"/>
       <c r="G298" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A299" s="17"/>
-      <c r="B299" s="14"/>
-      <c r="C299" s="14"/>
-      <c r="D299" s="14"/>
-      <c r="E299" s="14"/>
+        <v>91826</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A299" s="17">
+        <v>46303</v>
+      </c>
+      <c r="B299" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C299" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D299" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E299" s="14">
+        <v>300</v>
+      </c>
       <c r="F299" s="14"/>
       <c r="G299" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A300" s="16"/>
-      <c r="B300" s="13"/>
-      <c r="C300" s="13"/>
-      <c r="D300" s="13"/>
-      <c r="E300" s="13"/>
+        <v>92126</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A300" s="16">
+        <v>46303</v>
+      </c>
+      <c r="B300" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C300" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D300" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E300" s="13">
+        <v>200</v>
+      </c>
       <c r="F300" s="13"/>
       <c r="G300" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A301" s="17"/>
-      <c r="B301" s="14"/>
-      <c r="C301" s="14"/>
-      <c r="D301" s="14"/>
-      <c r="E301" s="14"/>
+        <v>92326</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A301" s="17">
+        <v>46303</v>
+      </c>
+      <c r="B301" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C301" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D301" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E301" s="14">
+        <v>100</v>
+      </c>
       <c r="F301" s="14"/>
       <c r="G301" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A302" s="16"/>
-      <c r="B302" s="13"/>
-      <c r="C302" s="13"/>
-      <c r="D302" s="13"/>
-      <c r="E302" s="13"/>
+        <v>92426</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A302" s="16">
+        <v>46303</v>
+      </c>
+      <c r="B302" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C302" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D302" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E302" s="13">
+        <v>300</v>
+      </c>
       <c r="F302" s="13"/>
       <c r="G302" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A303" s="17"/>
-      <c r="B303" s="14"/>
-      <c r="C303" s="14"/>
-      <c r="D303" s="14"/>
-      <c r="E303" s="14"/>
+        <v>92726</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A303" s="17">
+        <v>46303</v>
+      </c>
+      <c r="B303" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C303" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D303" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E303" s="14">
+        <v>4200</v>
+      </c>
       <c r="F303" s="14"/>
       <c r="G303" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A304" s="16"/>
-      <c r="B304" s="13"/>
-      <c r="C304" s="13"/>
-      <c r="D304" s="13"/>
-      <c r="E304" s="13"/>
+        <v>96926</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A304" s="16">
+        <v>46303</v>
+      </c>
+      <c r="B304" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C304" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D304" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E304" s="13">
+        <v>3000</v>
+      </c>
       <c r="F304" s="13"/>
       <c r="G304" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A305" s="17"/>
-      <c r="B305" s="14"/>
-      <c r="C305" s="14"/>
-      <c r="D305" s="14"/>
-      <c r="E305" s="14"/>
+        <v>99926</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A305" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B305" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C305" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D305" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E305" s="14">
+        <v>300</v>
+      </c>
       <c r="F305" s="14"/>
       <c r="G305" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A306" s="16"/>
-      <c r="B306" s="13"/>
-      <c r="C306" s="13"/>
-      <c r="D306" s="13"/>
-      <c r="E306" s="13"/>
+        <v>100226</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A306" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B306" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C306" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D306" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E306" s="13">
+        <v>700</v>
+      </c>
       <c r="F306" s="13"/>
       <c r="G306" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="17"/>
-      <c r="B307" s="14"/>
-      <c r="C307" s="14"/>
-      <c r="D307" s="14"/>
-      <c r="E307" s="14"/>
+        <v>100926</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A307" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B307" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C307" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D307" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E307" s="14">
+        <v>500</v>
+      </c>
       <c r="F307" s="14"/>
       <c r="G307" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A308" s="16"/>
-      <c r="B308" s="13"/>
-      <c r="C308" s="13"/>
-      <c r="D308" s="13"/>
-      <c r="E308" s="13"/>
+        <v>101426</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A308" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B308" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C308" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D308" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E308" s="13">
+        <v>100</v>
+      </c>
       <c r="F308" s="13"/>
       <c r="G308" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A309" s="17"/>
-      <c r="B309" s="14"/>
-      <c r="C309" s="14"/>
-      <c r="D309" s="14"/>
-      <c r="E309" s="14"/>
+        <v>101526</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A309" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B309" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C309" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D309" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E309" s="14">
+        <v>300</v>
+      </c>
       <c r="F309" s="14"/>
       <c r="G309" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A310" s="16"/>
-      <c r="B310" s="13"/>
-      <c r="C310" s="13"/>
-      <c r="D310" s="13"/>
-      <c r="E310" s="14"/>
+        <v>101826</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A310" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B310" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C310" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D310" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E310" s="14">
+        <v>2100</v>
+      </c>
       <c r="F310" s="13"/>
       <c r="G310" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A311" s="17"/>
-      <c r="B311" s="14"/>
-      <c r="C311" s="14"/>
-      <c r="D311" s="14"/>
-      <c r="E311" s="14"/>
+        <v>103926</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A311" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B311" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C311" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D311" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E311" s="14">
+        <v>700</v>
+      </c>
       <c r="F311" s="14"/>
       <c r="G311" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A312" s="16"/>
-      <c r="B312" s="13"/>
-      <c r="C312" s="13"/>
-      <c r="D312" s="13"/>
-      <c r="E312" s="13"/>
+        <v>104626</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A312" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B312" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C312" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D312" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E312" s="13">
+        <v>1750</v>
+      </c>
       <c r="F312" s="13"/>
       <c r="G312" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A313" s="17"/>
-      <c r="B313" s="14"/>
-      <c r="C313" s="14"/>
-      <c r="D313" s="14"/>
-      <c r="E313" s="14"/>
+        <v>106376</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A313" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B313" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C313" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D313" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E313" s="14">
+        <v>600</v>
+      </c>
       <c r="F313" s="14"/>
       <c r="G313" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A314" s="16"/>
-      <c r="B314" s="13"/>
-      <c r="C314" s="13"/>
-      <c r="D314" s="13"/>
-      <c r="E314" s="13"/>
+        <v>106976</v>
+      </c>
+      <c r="J313" s="21"/>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A314" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B314" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C314" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D314" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E314" s="13">
+        <v>2100</v>
+      </c>
       <c r="F314" s="13"/>
       <c r="G314" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="17"/>
-      <c r="B315" s="14"/>
-      <c r="C315" s="14"/>
-      <c r="D315" s="14"/>
-      <c r="E315" s="14"/>
+        <v>109076</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A315" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B315" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C315" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D315" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E315" s="14">
+        <v>2100</v>
+      </c>
       <c r="F315" s="14"/>
       <c r="G315" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="16"/>
-      <c r="B316" s="13"/>
-      <c r="C316" s="13"/>
-      <c r="D316" s="13"/>
-      <c r="E316" s="13"/>
+        <v>111176</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A316" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B316" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C316" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D316" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E316" s="13">
+        <v>350</v>
+      </c>
       <c r="F316" s="13"/>
       <c r="G316" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A317" s="17"/>
-      <c r="B317" s="14"/>
-      <c r="C317" s="14"/>
-      <c r="D317" s="14"/>
-      <c r="E317" s="14"/>
+        <v>111526</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A317" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B317" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C317" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D317" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E317" s="14">
+        <v>1400</v>
+      </c>
       <c r="F317" s="14"/>
       <c r="G317" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A318" s="16"/>
-      <c r="B318" s="13"/>
-      <c r="C318" s="13"/>
-      <c r="D318" s="13"/>
-      <c r="E318" s="13"/>
+        <v>112926</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A318" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B318" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C318" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D318" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E318" s="13">
+        <v>200</v>
+      </c>
       <c r="F318" s="13"/>
       <c r="G318" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A319" s="17"/>
-      <c r="B319" s="14"/>
-      <c r="C319" s="14"/>
-      <c r="D319" s="14"/>
+        <v>113126</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A319" s="17">
+        <v>46304</v>
+      </c>
+      <c r="B319" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C319" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D319" s="14" t="s">
+        <v>7</v>
+      </c>
       <c r="E319" s="14"/>
-      <c r="F319" s="14"/>
+      <c r="F319" s="14">
+        <v>30000</v>
+      </c>
       <c r="G319" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A320" s="16"/>
-      <c r="B320" s="13"/>
-      <c r="C320" s="13"/>
-      <c r="D320" s="13"/>
-      <c r="E320" s="13"/>
+        <v>83126</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A320" s="16">
+        <v>46305</v>
+      </c>
+      <c r="B320" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C320" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D320" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E320" s="13">
+        <v>300</v>
+      </c>
       <c r="F320" s="13"/>
       <c r="G320" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>83426</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A321" s="17"/>
-      <c r="B321" s="14"/>
-      <c r="C321" s="14"/>
-      <c r="D321" s="14"/>
-      <c r="E321" s="14"/>
+      <c r="A321" s="17">
+        <v>46305</v>
+      </c>
+      <c r="B321" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C321" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D321" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E321" s="14">
+        <v>200</v>
+      </c>
       <c r="F321" s="14"/>
       <c r="G321" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>83626</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A322" s="16"/>
-      <c r="B322" s="13"/>
-      <c r="C322" s="13"/>
-      <c r="D322" s="13"/>
-      <c r="E322" s="13"/>
+      <c r="A322" s="16">
+        <v>46305</v>
+      </c>
+      <c r="B322" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C322" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D322" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E322" s="13">
+        <v>100</v>
+      </c>
       <c r="F322" s="13"/>
       <c r="G322" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>83726</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A323" s="17"/>
-      <c r="B323" s="14"/>
-      <c r="C323" s="14"/>
-      <c r="D323" s="14"/>
-      <c r="E323" s="14"/>
+      <c r="A323" s="17">
+        <v>46305</v>
+      </c>
+      <c r="B323" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C323" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D323" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E323" s="14">
+        <v>200</v>
+      </c>
       <c r="F323" s="14"/>
       <c r="G323" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>83926</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A324" s="16"/>
-      <c r="B324" s="13"/>
-      <c r="C324" s="13"/>
-      <c r="D324" s="13"/>
-      <c r="E324" s="13"/>
+      <c r="A324" s="16">
+        <v>46305</v>
+      </c>
+      <c r="B324" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C324" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D324" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E324" s="13">
+        <v>2100</v>
+      </c>
       <c r="F324" s="13"/>
       <c r="G324" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>86026</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A325" s="17"/>
-      <c r="B325" s="14"/>
-      <c r="C325" s="14"/>
-      <c r="D325" s="14"/>
-      <c r="E325" s="14"/>
+      <c r="A325" s="17">
+        <v>46305</v>
+      </c>
+      <c r="B325" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C325" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D325" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E325" s="14">
+        <v>2800</v>
+      </c>
       <c r="F325" s="14"/>
       <c r="G325" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>88826</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A326" s="16"/>
-      <c r="B326" s="13"/>
-      <c r="C326" s="13"/>
-      <c r="D326" s="13"/>
-      <c r="E326" s="13"/>
+      <c r="A326" s="16">
+        <v>46305</v>
+      </c>
+      <c r="B326" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C326" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D326" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E326" s="13">
+        <v>1400</v>
+      </c>
       <c r="F326" s="13"/>
       <c r="G326" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>90226</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A327" s="17"/>
-      <c r="B327" s="14"/>
-      <c r="C327" s="14"/>
-      <c r="D327" s="14"/>
-      <c r="E327" s="14"/>
+      <c r="A327" s="17">
+        <v>46305</v>
+      </c>
+      <c r="B327" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C327" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D327" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E327" s="14">
+        <v>2100</v>
+      </c>
       <c r="F327" s="14"/>
       <c r="G327" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>92326</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A328" s="16"/>
-      <c r="B328" s="13"/>
-      <c r="C328" s="13"/>
-      <c r="D328" s="13"/>
-      <c r="E328" s="13"/>
+      <c r="A328" s="16">
+        <v>46305</v>
+      </c>
+      <c r="B328" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C328" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E328" s="13">
+        <v>1400</v>
+      </c>
       <c r="F328" s="13"/>
       <c r="G328" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A329" s="17"/>
-      <c r="B329" s="14"/>
-      <c r="C329" s="14"/>
-      <c r="D329" s="14"/>
-      <c r="E329" s="14"/>
+        <v>93726</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A329" s="17">
+        <v>46305</v>
+      </c>
+      <c r="B329" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C329" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D329" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E329" s="14">
+        <v>4200</v>
+      </c>
       <c r="F329" s="14"/>
       <c r="G329" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>97926</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A330" s="16"/>
-      <c r="B330" s="13"/>
-      <c r="C330" s="13"/>
-      <c r="D330" s="13"/>
-      <c r="E330" s="13"/>
+      <c r="A330" s="16">
+        <v>46305</v>
+      </c>
+      <c r="B330" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C330" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D330" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E330" s="13">
+        <v>2500</v>
+      </c>
       <c r="F330" s="13"/>
       <c r="G330" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>100426</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A331" s="17"/>
-      <c r="B331" s="14"/>
-      <c r="C331" s="14"/>
-      <c r="D331" s="14"/>
-      <c r="E331" s="14"/>
+      <c r="A331" s="17">
+        <v>46305</v>
+      </c>
+      <c r="B331" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C331" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D331" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E331" s="14">
+        <v>1400</v>
+      </c>
       <c r="F331" s="14"/>
       <c r="G331" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>101826</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A332" s="16"/>
-      <c r="B332" s="13"/>
-      <c r="C332" s="13"/>
-      <c r="D332" s="13"/>
-      <c r="E332" s="13"/>
+      <c r="A332" s="16">
+        <v>46305</v>
+      </c>
+      <c r="B332" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C332" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D332" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E332" s="13">
+        <v>1400</v>
+      </c>
       <c r="F332" s="13"/>
       <c r="G332" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>103226</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A333" s="17"/>
-      <c r="B333" s="14"/>
-      <c r="C333" s="14"/>
-      <c r="D333" s="14"/>
-      <c r="E333" s="14"/>
+      <c r="A333" s="17">
+        <v>46306</v>
+      </c>
+      <c r="B333" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C333" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D333" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E333" s="14">
+        <v>100</v>
+      </c>
       <c r="F333" s="14"/>
       <c r="G333" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>103326</v>
       </c>
       <c r="I333" s="21"/>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A334" s="16"/>
-      <c r="B334" s="13"/>
-      <c r="C334" s="13"/>
-      <c r="D334" s="13"/>
-      <c r="E334" s="13"/>
+      <c r="A334" s="16">
+        <v>46306</v>
+      </c>
+      <c r="B334" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C334" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D334" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E334" s="13">
+        <v>300</v>
+      </c>
       <c r="F334" s="13"/>
       <c r="G334" s="13">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>103626</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A335" s="17"/>
-      <c r="B335" s="14"/>
-      <c r="C335" s="14"/>
-      <c r="D335" s="14"/>
-      <c r="E335" s="14"/>
+      <c r="A335" s="17">
+        <v>46307</v>
+      </c>
+      <c r="B335" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C335" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D335" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E335" s="14">
+        <v>300</v>
+      </c>
       <c r="F335" s="14"/>
       <c r="G335" s="14">
         <f t="shared" si="6"/>
-        <v>89726</v>
+        <v>103926</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A336" s="16"/>
-      <c r="B336" s="13"/>
-      <c r="C336" s="13"/>
-      <c r="D336" s="13"/>
-      <c r="E336" s="13"/>
+      <c r="A336" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B336" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C336" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D336" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E336" s="13">
+        <v>7000</v>
+      </c>
       <c r="F336" s="13"/>
       <c r="G336" s="13">
         <f t="shared" ref="G336:G399" si="7">G335+E336-F336</f>
-        <v>89726</v>
+        <v>110926</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A337" s="17"/>
-      <c r="B337" s="14"/>
-      <c r="C337" s="14"/>
-      <c r="D337" s="14"/>
-      <c r="E337" s="14"/>
+      <c r="A337" s="17">
+        <v>46307</v>
+      </c>
+      <c r="B337" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C337" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D337" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E337" s="14">
+        <v>7000</v>
+      </c>
       <c r="F337" s="14"/>
       <c r="G337" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>117926</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A338" s="16"/>
-      <c r="B338" s="13"/>
-      <c r="C338" s="13"/>
-      <c r="D338" s="13"/>
-      <c r="E338" s="13"/>
+      <c r="A338" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B338" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C338" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D338" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E338" s="13">
+        <v>100</v>
+      </c>
       <c r="F338" s="13"/>
       <c r="G338" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>118026</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A339" s="17"/>
-      <c r="B339" s="14"/>
-      <c r="C339" s="14"/>
-      <c r="D339" s="14"/>
-      <c r="E339" s="14"/>
+      <c r="A339" s="17">
+        <v>46307</v>
+      </c>
+      <c r="B339" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C339" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D339" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E339" s="14">
+        <v>200</v>
+      </c>
       <c r="F339" s="14"/>
       <c r="G339" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>118226</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A340" s="16"/>
-      <c r="B340" s="13"/>
-      <c r="C340" s="13"/>
-      <c r="D340" s="13"/>
-      <c r="E340" s="13"/>
+      <c r="A340" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B340" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C340" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D340" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E340" s="13">
+        <v>2100</v>
+      </c>
       <c r="F340" s="13"/>
       <c r="G340" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>120326</v>
       </c>
       <c r="J340" s="21"/>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A341" s="17"/>
-      <c r="B341" s="14"/>
-      <c r="C341" s="14"/>
-      <c r="D341" s="14"/>
-      <c r="E341" s="14"/>
+      <c r="A341" s="17">
+        <v>46307</v>
+      </c>
+      <c r="B341" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C341" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D341" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E341" s="14">
+        <v>1400</v>
+      </c>
       <c r="F341" s="14"/>
       <c r="G341" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>121726</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A342" s="16"/>
-      <c r="B342" s="13"/>
-      <c r="C342" s="13"/>
-      <c r="D342" s="13"/>
-      <c r="E342" s="13"/>
+      <c r="A342" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B342" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C342" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D342" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E342" s="13">
+        <v>1400</v>
+      </c>
       <c r="F342" s="13"/>
       <c r="G342" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>123126</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A343" s="17"/>
-      <c r="B343" s="14"/>
-      <c r="C343" s="14"/>
-      <c r="D343" s="14"/>
-      <c r="E343" s="14"/>
+      <c r="A343" s="17">
+        <v>46307</v>
+      </c>
+      <c r="B343" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C343" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D343" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E343" s="14">
+        <v>1400</v>
+      </c>
       <c r="F343" s="14"/>
       <c r="G343" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124526</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A344" s="16"/>
-      <c r="B344" s="13"/>
-      <c r="C344" s="13"/>
-      <c r="D344" s="13"/>
+      <c r="A344" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B344" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C344" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D344" s="13" t="s">
+        <v>7</v>
+      </c>
       <c r="E344" s="13"/>
-      <c r="F344" s="13"/>
+      <c r="F344" s="13">
+        <v>300</v>
+      </c>
       <c r="G344" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
@@ -7657,7 +8831,11 @@
       <c r="F345" s="14"/>
       <c r="G345" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
+      </c>
+      <c r="J345" s="21">
+        <f>SUM(E320:E343)</f>
+        <v>41400</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
@@ -7669,7 +8847,7 @@
       <c r="F346" s="13"/>
       <c r="G346" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
@@ -7681,7 +8859,7 @@
       <c r="F347" s="14"/>
       <c r="G347" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
@@ -7693,7 +8871,7 @@
       <c r="F348" s="13"/>
       <c r="G348" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
@@ -7705,7 +8883,7 @@
       <c r="F349" s="14"/>
       <c r="G349" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
@@ -7717,7 +8895,7 @@
       <c r="F350" s="13"/>
       <c r="G350" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
@@ -7729,7 +8907,7 @@
       <c r="F351" s="14"/>
       <c r="G351" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
@@ -7741,7 +8919,7 @@
       <c r="F352" s="13"/>
       <c r="G352" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
@@ -7753,7 +8931,7 @@
       <c r="F353" s="14"/>
       <c r="G353" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
@@ -7765,7 +8943,7 @@
       <c r="F354" s="13"/>
       <c r="G354" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
       <c r="J354" s="21"/>
     </row>
@@ -7778,7 +8956,7 @@
       <c r="F355" s="14"/>
       <c r="G355" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
@@ -7790,7 +8968,7 @@
       <c r="F356" s="13"/>
       <c r="G356" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
@@ -7802,7 +8980,7 @@
       <c r="F357" s="14"/>
       <c r="G357" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
@@ -7814,7 +8992,7 @@
       <c r="F358" s="13"/>
       <c r="G358" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
@@ -7826,7 +9004,7 @@
       <c r="F359" s="14"/>
       <c r="G359" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
@@ -7838,7 +9016,7 @@
       <c r="F360" s="13"/>
       <c r="G360" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
@@ -7850,7 +9028,7 @@
       <c r="F361" s="14"/>
       <c r="G361" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
@@ -7862,7 +9040,7 @@
       <c r="F362" s="13"/>
       <c r="G362" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
@@ -7874,7 +9052,7 @@
       <c r="F363" s="14"/>
       <c r="G363" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
@@ -7886,7 +9064,7 @@
       <c r="F364" s="13"/>
       <c r="G364" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
@@ -7898,7 +9076,7 @@
       <c r="F365" s="14"/>
       <c r="G365" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
@@ -7910,7 +9088,7 @@
       <c r="F366" s="13"/>
       <c r="G366" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
@@ -7922,7 +9100,7 @@
       <c r="F367" s="14"/>
       <c r="G367" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
@@ -7934,7 +9112,7 @@
       <c r="F368" s="13"/>
       <c r="G368" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
@@ -7946,7 +9124,7 @@
       <c r="F369" s="14"/>
       <c r="G369" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
@@ -7958,7 +9136,7 @@
       <c r="F370" s="13"/>
       <c r="G370" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
@@ -7970,7 +9148,7 @@
       <c r="F371" s="14"/>
       <c r="G371" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
@@ -7982,7 +9160,7 @@
       <c r="F372" s="13"/>
       <c r="G372" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
@@ -7994,7 +9172,7 @@
       <c r="F373" s="14"/>
       <c r="G373" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
@@ -8006,7 +9184,7 @@
       <c r="F374" s="13"/>
       <c r="G374" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
@@ -8018,7 +9196,7 @@
       <c r="F375" s="14"/>
       <c r="G375" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
@@ -8030,7 +9208,7 @@
       <c r="F376" s="13"/>
       <c r="G376" s="13">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
@@ -8042,7 +9220,7 @@
       <c r="F377" s="14"/>
       <c r="G377" s="14">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
@@ -8054,7 +9232,7 @@
       <c r="F378" s="18"/>
       <c r="G378" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
@@ -8066,7 +9244,7 @@
       <c r="F379" s="19"/>
       <c r="G379" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
@@ -8078,7 +9256,7 @@
       <c r="F380" s="18"/>
       <c r="G380" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
@@ -8090,7 +9268,7 @@
       <c r="F381" s="19"/>
       <c r="G381" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
@@ -8102,7 +9280,7 @@
       <c r="F382" s="18"/>
       <c r="G382" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
@@ -8114,7 +9292,7 @@
       <c r="F383" s="19"/>
       <c r="G383" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
@@ -8126,7 +9304,7 @@
       <c r="F384" s="18"/>
       <c r="G384" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
@@ -8138,7 +9316,7 @@
       <c r="F385" s="19"/>
       <c r="G385" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
@@ -8150,7 +9328,7 @@
       <c r="F386" s="18"/>
       <c r="G386" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
@@ -8162,7 +9340,7 @@
       <c r="F387" s="19"/>
       <c r="G387" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
@@ -8174,7 +9352,7 @@
       <c r="F388" s="18"/>
       <c r="G388" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
@@ -8186,7 +9364,7 @@
       <c r="F389" s="19"/>
       <c r="G389" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
@@ -8198,7 +9376,7 @@
       <c r="F390" s="18"/>
       <c r="G390" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
@@ -8210,7 +9388,7 @@
       <c r="F391" s="19"/>
       <c r="G391" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
@@ -8222,7 +9400,7 @@
       <c r="F392" s="18"/>
       <c r="G392" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
@@ -8234,7 +9412,7 @@
       <c r="F393" s="19"/>
       <c r="G393" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
@@ -8246,7 +9424,7 @@
       <c r="F394" s="18"/>
       <c r="G394" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
@@ -8258,7 +9436,7 @@
       <c r="F395" s="19"/>
       <c r="G395" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
@@ -8270,7 +9448,7 @@
       <c r="F396" s="18"/>
       <c r="G396" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
@@ -8282,7 +9460,7 @@
       <c r="F397" s="19"/>
       <c r="G397" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
@@ -8294,7 +9472,7 @@
       <c r="F398" s="18"/>
       <c r="G398" s="18">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
@@ -8306,7 +9484,7 @@
       <c r="F399" s="19"/>
       <c r="G399" s="19">
         <f t="shared" si="7"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
@@ -8318,7 +9496,7 @@
       <c r="F400" s="18"/>
       <c r="G400" s="18">
         <f t="shared" ref="G400:G463" si="8">G399+E400-F400</f>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
@@ -8330,7 +9508,7 @@
       <c r="F401" s="19"/>
       <c r="G401" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -8342,7 +9520,7 @@
       <c r="F402" s="18"/>
       <c r="G402" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
       <c r="I402" s="21"/>
     </row>
@@ -8355,7 +9533,7 @@
       <c r="F403" s="19"/>
       <c r="G403" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
       <c r="I403" s="21"/>
     </row>
@@ -8368,7 +9546,7 @@
       <c r="F404" s="18"/>
       <c r="G404" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
       <c r="I404" s="21"/>
     </row>
@@ -8381,7 +9559,7 @@
       <c r="F405" s="19"/>
       <c r="G405" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
@@ -8393,7 +9571,7 @@
       <c r="F406" s="18"/>
       <c r="G406" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.3">
@@ -8405,7 +9583,7 @@
       <c r="F407" s="19"/>
       <c r="G407" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
@@ -8417,7 +9595,7 @@
       <c r="F408" s="18"/>
       <c r="G408" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
@@ -8429,7 +9607,7 @@
       <c r="F409" s="19"/>
       <c r="G409" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
@@ -8441,7 +9619,7 @@
       <c r="F410" s="18"/>
       <c r="G410" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
@@ -8453,7 +9631,7 @@
       <c r="F411" s="19"/>
       <c r="G411" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
@@ -8465,7 +9643,7 @@
       <c r="F412" s="18"/>
       <c r="G412" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
@@ -8477,7 +9655,7 @@
       <c r="F413" s="19"/>
       <c r="G413" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
@@ -8489,7 +9667,7 @@
       <c r="F414" s="18"/>
       <c r="G414" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
@@ -8501,7 +9679,7 @@
       <c r="F415" s="19"/>
       <c r="G415" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
@@ -8513,7 +9691,7 @@
       <c r="F416" s="18"/>
       <c r="G416" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
@@ -8525,7 +9703,7 @@
       <c r="F417" s="19"/>
       <c r="G417" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
@@ -8537,7 +9715,7 @@
       <c r="F418" s="18"/>
       <c r="G418" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
@@ -8549,7 +9727,7 @@
       <c r="F419" s="19"/>
       <c r="G419" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
@@ -8561,7 +9739,7 @@
       <c r="F420" s="18"/>
       <c r="G420" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
@@ -8573,7 +9751,7 @@
       <c r="F421" s="19"/>
       <c r="G421" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
@@ -8585,7 +9763,7 @@
       <c r="F422" s="18"/>
       <c r="G422" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
@@ -8597,7 +9775,7 @@
       <c r="F423" s="19"/>
       <c r="G423" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
@@ -8609,7 +9787,7 @@
       <c r="F424" s="18"/>
       <c r="G424" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
@@ -8621,7 +9799,7 @@
       <c r="F425" s="19"/>
       <c r="G425" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
@@ -8633,7 +9811,7 @@
       <c r="F426" s="18"/>
       <c r="G426" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
@@ -8645,7 +9823,7 @@
       <c r="F427" s="19"/>
       <c r="G427" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
@@ -8657,7 +9835,7 @@
       <c r="F428" s="18"/>
       <c r="G428" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
@@ -8669,7 +9847,7 @@
       <c r="F429" s="19"/>
       <c r="G429" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
@@ -8681,7 +9859,7 @@
       <c r="F430" s="18"/>
       <c r="G430" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
@@ -8693,7 +9871,7 @@
       <c r="F431" s="19"/>
       <c r="G431" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
@@ -8705,7 +9883,7 @@
       <c r="F432" s="18"/>
       <c r="G432" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
@@ -8717,7 +9895,7 @@
       <c r="F433" s="19"/>
       <c r="G433" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
@@ -8729,7 +9907,7 @@
       <c r="F434" s="18"/>
       <c r="G434" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
@@ -8741,7 +9919,7 @@
       <c r="F435" s="19"/>
       <c r="G435" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
@@ -8753,7 +9931,7 @@
       <c r="F436" s="18"/>
       <c r="G436" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
@@ -8765,7 +9943,7 @@
       <c r="F437" s="19"/>
       <c r="G437" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
@@ -8777,7 +9955,7 @@
       <c r="F438" s="18"/>
       <c r="G438" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
@@ -8789,7 +9967,7 @@
       <c r="F439" s="19"/>
       <c r="G439" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
@@ -8801,7 +9979,7 @@
       <c r="F440" s="18"/>
       <c r="G440" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
@@ -8813,7 +9991,7 @@
       <c r="F441" s="19"/>
       <c r="G441" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
@@ -8825,7 +10003,7 @@
       <c r="F442" s="18"/>
       <c r="G442" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
@@ -8837,7 +10015,7 @@
       <c r="F443" s="19"/>
       <c r="G443" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
@@ -8849,7 +10027,7 @@
       <c r="F444" s="18"/>
       <c r="G444" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
@@ -8861,7 +10039,7 @@
       <c r="F445" s="19"/>
       <c r="G445" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
@@ -8873,7 +10051,7 @@
       <c r="F446" s="18"/>
       <c r="G446" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
@@ -8885,7 +10063,7 @@
       <c r="F447" s="19"/>
       <c r="G447" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
@@ -8897,7 +10075,7 @@
       <c r="F448" s="18"/>
       <c r="G448" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
@@ -8909,7 +10087,7 @@
       <c r="F449" s="19"/>
       <c r="G449" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
@@ -8921,7 +10099,7 @@
       <c r="F450" s="18"/>
       <c r="G450" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
@@ -8933,7 +10111,7 @@
       <c r="F451" s="19"/>
       <c r="G451" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
@@ -8945,7 +10123,7 @@
       <c r="F452" s="18"/>
       <c r="G452" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
@@ -8957,7 +10135,7 @@
       <c r="F453" s="19"/>
       <c r="G453" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
@@ -8969,7 +10147,7 @@
       <c r="F454" s="18"/>
       <c r="G454" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
@@ -8981,7 +10159,7 @@
       <c r="F455" s="19"/>
       <c r="G455" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
@@ -8993,7 +10171,7 @@
       <c r="F456" s="18"/>
       <c r="G456" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
@@ -9005,7 +10183,7 @@
       <c r="F457" s="19"/>
       <c r="G457" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
@@ -9017,7 +10195,7 @@
       <c r="F458" s="18"/>
       <c r="G458" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
@@ -9029,7 +10207,7 @@
       <c r="F459" s="19"/>
       <c r="G459" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
@@ -9041,7 +10219,7 @@
       <c r="F460" s="18"/>
       <c r="G460" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
@@ -9053,7 +10231,7 @@
       <c r="F461" s="19"/>
       <c r="G461" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
@@ -9065,7 +10243,7 @@
       <c r="F462" s="18"/>
       <c r="G462" s="18">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
@@ -9077,7 +10255,7 @@
       <c r="F463" s="19"/>
       <c r="G463" s="19">
         <f t="shared" si="8"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
@@ -9089,7 +10267,7 @@
       <c r="F464" s="18"/>
       <c r="G464" s="18">
         <f t="shared" ref="G464:G527" si="9">G463+E464-F464</f>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
@@ -9101,7 +10279,7 @@
       <c r="F465" s="19"/>
       <c r="G465" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
@@ -9113,7 +10291,7 @@
       <c r="F466" s="18"/>
       <c r="G466" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
@@ -9125,7 +10303,7 @@
       <c r="F467" s="19"/>
       <c r="G467" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
@@ -9137,7 +10315,7 @@
       <c r="F468" s="18"/>
       <c r="G468" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
@@ -9149,7 +10327,7 @@
       <c r="F469" s="19"/>
       <c r="G469" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.3">
@@ -9161,7 +10339,7 @@
       <c r="F470" s="18"/>
       <c r="G470" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
@@ -9173,7 +10351,7 @@
       <c r="F471" s="19"/>
       <c r="G471" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
@@ -9185,7 +10363,7 @@
       <c r="F472" s="18"/>
       <c r="G472" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
@@ -9197,7 +10375,7 @@
       <c r="F473" s="19"/>
       <c r="G473" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
       <c r="J473" s="21"/>
     </row>
@@ -9210,7 +10388,7 @@
       <c r="F474" s="18"/>
       <c r="G474" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
@@ -9222,7 +10400,7 @@
       <c r="F475" s="19"/>
       <c r="G475" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
@@ -9234,7 +10412,7 @@
       <c r="F476" s="18"/>
       <c r="G476" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
@@ -9246,7 +10424,7 @@
       <c r="F477" s="19"/>
       <c r="G477" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
@@ -9258,7 +10436,7 @@
       <c r="F478" s="18"/>
       <c r="G478" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
@@ -9270,7 +10448,7 @@
       <c r="F479" s="19"/>
       <c r="G479" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
@@ -9282,7 +10460,7 @@
       <c r="F480" s="18"/>
       <c r="G480" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
@@ -9294,7 +10472,7 @@
       <c r="F481" s="19"/>
       <c r="G481" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
@@ -9306,7 +10484,7 @@
       <c r="F482" s="18"/>
       <c r="G482" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
@@ -9318,7 +10496,7 @@
       <c r="F483" s="19"/>
       <c r="G483" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
@@ -9330,7 +10508,7 @@
       <c r="F484" s="18"/>
       <c r="G484" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
@@ -9342,7 +10520,7 @@
       <c r="F485" s="19"/>
       <c r="G485" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
@@ -9354,7 +10532,7 @@
       <c r="F486" s="18"/>
       <c r="G486" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
@@ -9366,7 +10544,7 @@
       <c r="F487" s="19"/>
       <c r="G487" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.3">
@@ -9378,7 +10556,7 @@
       <c r="F488" s="18"/>
       <c r="G488" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
@@ -9390,7 +10568,7 @@
       <c r="F489" s="19"/>
       <c r="G489" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
       <c r="J489" s="21"/>
     </row>
@@ -9403,7 +10581,7 @@
       <c r="F490" s="18"/>
       <c r="G490" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.3">
@@ -9415,7 +10593,7 @@
       <c r="F491" s="19"/>
       <c r="G491" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.3">
@@ -9427,7 +10605,7 @@
       <c r="F492" s="18"/>
       <c r="G492" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.3">
@@ -9439,7 +10617,7 @@
       <c r="F493" s="19"/>
       <c r="G493" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.3">
@@ -9451,7 +10629,7 @@
       <c r="F494" s="18"/>
       <c r="G494" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.3">
@@ -9463,7 +10641,7 @@
       <c r="F495" s="19"/>
       <c r="G495" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.3">
@@ -9475,7 +10653,7 @@
       <c r="F496" s="18"/>
       <c r="G496" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
@@ -9487,7 +10665,7 @@
       <c r="F497" s="19"/>
       <c r="G497" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
@@ -9499,7 +10677,7 @@
       <c r="F498" s="18"/>
       <c r="G498" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
@@ -9511,7 +10689,7 @@
       <c r="F499" s="19"/>
       <c r="G499" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
@@ -9523,7 +10701,7 @@
       <c r="F500" s="18"/>
       <c r="G500" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
@@ -9535,7 +10713,7 @@
       <c r="F501" s="19"/>
       <c r="G501" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
@@ -9547,7 +10725,7 @@
       <c r="F502" s="18"/>
       <c r="G502" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
@@ -9559,7 +10737,7 @@
       <c r="F503" s="19"/>
       <c r="G503" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
@@ -9571,7 +10749,7 @@
       <c r="F504" s="18"/>
       <c r="G504" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
@@ -9583,7 +10761,7 @@
       <c r="F505" s="19"/>
       <c r="G505" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
@@ -9595,7 +10773,7 @@
       <c r="F506" s="18"/>
       <c r="G506" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
@@ -9607,7 +10785,7 @@
       <c r="F507" s="19"/>
       <c r="G507" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
@@ -9619,7 +10797,7 @@
       <c r="F508" s="18"/>
       <c r="G508" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
@@ -9631,7 +10809,7 @@
       <c r="F509" s="19"/>
       <c r="G509" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
@@ -9643,7 +10821,7 @@
       <c r="F510" s="18"/>
       <c r="G510" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
@@ -9655,7 +10833,7 @@
       <c r="F511" s="19"/>
       <c r="G511" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
@@ -9667,7 +10845,7 @@
       <c r="F512" s="18"/>
       <c r="G512" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
@@ -9679,7 +10857,7 @@
       <c r="F513" s="19"/>
       <c r="G513" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
@@ -9691,7 +10869,7 @@
       <c r="F514" s="18"/>
       <c r="G514" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
@@ -9703,7 +10881,7 @@
       <c r="F515" s="19"/>
       <c r="G515" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
@@ -9715,7 +10893,7 @@
       <c r="F516" s="18"/>
       <c r="G516" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
@@ -9727,7 +10905,7 @@
       <c r="F517" s="19"/>
       <c r="G517" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
@@ -9739,7 +10917,7 @@
       <c r="F518" s="18"/>
       <c r="G518" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
@@ -9751,7 +10929,7 @@
       <c r="F519" s="19"/>
       <c r="G519" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
@@ -9763,7 +10941,7 @@
       <c r="F520" s="18"/>
       <c r="G520" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
@@ -9775,7 +10953,7 @@
       <c r="F521" s="19"/>
       <c r="G521" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
@@ -9787,7 +10965,7 @@
       <c r="F522" s="18"/>
       <c r="G522" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
@@ -9799,7 +10977,7 @@
       <c r="F523" s="19"/>
       <c r="G523" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
@@ -9811,7 +10989,7 @@
       <c r="F524" s="18"/>
       <c r="G524" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
@@ -9823,7 +11001,7 @@
       <c r="F525" s="19"/>
       <c r="G525" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
@@ -9835,7 +11013,7 @@
       <c r="F526" s="18"/>
       <c r="G526" s="18">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
@@ -9847,7 +11025,7 @@
       <c r="F527" s="19"/>
       <c r="G527" s="19">
         <f t="shared" si="9"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
@@ -9859,7 +11037,7 @@
       <c r="F528" s="18"/>
       <c r="G528" s="18">
         <f t="shared" ref="G528:G591" si="10">G527+E528-F528</f>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.3">
@@ -9871,7 +11049,7 @@
       <c r="F529" s="19"/>
       <c r="G529" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.3">
@@ -9883,7 +11061,7 @@
       <c r="F530" s="18"/>
       <c r="G530" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.3">
@@ -9895,7 +11073,7 @@
       <c r="F531" s="19"/>
       <c r="G531" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.3">
@@ -9907,7 +11085,7 @@
       <c r="F532" s="18"/>
       <c r="G532" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
       <c r="K532" s="21"/>
     </row>
@@ -9920,7 +11098,7 @@
       <c r="F533" s="19"/>
       <c r="G533" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.3">
@@ -9932,7 +11110,7 @@
       <c r="F534" s="18"/>
       <c r="G534" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.3">
@@ -9944,7 +11122,7 @@
       <c r="F535" s="19"/>
       <c r="G535" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.3">
@@ -9956,7 +11134,7 @@
       <c r="F536" s="18"/>
       <c r="G536" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.3">
@@ -9968,7 +11146,7 @@
       <c r="F537" s="19"/>
       <c r="G537" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.3">
@@ -9980,7 +11158,7 @@
       <c r="F538" s="18"/>
       <c r="G538" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.3">
@@ -9992,7 +11170,7 @@
       <c r="F539" s="19"/>
       <c r="G539" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.3">
@@ -10004,7 +11182,7 @@
       <c r="F540" s="18"/>
       <c r="G540" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.3">
@@ -10016,7 +11194,7 @@
       <c r="F541" s="19"/>
       <c r="G541" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.3">
@@ -10028,7 +11206,7 @@
       <c r="F542" s="18"/>
       <c r="G542" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.3">
@@ -10040,7 +11218,7 @@
       <c r="F543" s="19"/>
       <c r="G543" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.3">
@@ -10052,7 +11230,7 @@
       <c r="F544" s="18"/>
       <c r="G544" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
@@ -10064,7 +11242,7 @@
       <c r="F545" s="19"/>
       <c r="G545" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
@@ -10076,7 +11254,7 @@
       <c r="F546" s="18"/>
       <c r="G546" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -10088,7 +11266,7 @@
       <c r="F547" s="19"/>
       <c r="G547" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.3">
@@ -10100,7 +11278,7 @@
       <c r="F548" s="18"/>
       <c r="G548" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
@@ -10112,7 +11290,7 @@
       <c r="F549" s="19"/>
       <c r="G549" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.3">
@@ -10124,7 +11302,7 @@
       <c r="F550" s="18"/>
       <c r="G550" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.3">
@@ -10136,7 +11314,7 @@
       <c r="F551" s="19"/>
       <c r="G551" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
@@ -10148,7 +11326,7 @@
       <c r="F552" s="18"/>
       <c r="G552" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.3">
@@ -10160,7 +11338,7 @@
       <c r="F553" s="19"/>
       <c r="G553" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.3">
@@ -10172,7 +11350,7 @@
       <c r="F554" s="18"/>
       <c r="G554" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.3">
@@ -10184,7 +11362,7 @@
       <c r="F555" s="19"/>
       <c r="G555" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.3">
@@ -10196,7 +11374,7 @@
       <c r="F556" s="18"/>
       <c r="G556" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
@@ -10208,7 +11386,7 @@
       <c r="F557" s="19"/>
       <c r="G557" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
@@ -10220,7 +11398,7 @@
       <c r="F558" s="18"/>
       <c r="G558" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
@@ -10232,7 +11410,7 @@
       <c r="F559" s="19"/>
       <c r="G559" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.3">
@@ -10244,7 +11422,7 @@
       <c r="F560" s="18"/>
       <c r="G560" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
@@ -10256,7 +11434,7 @@
       <c r="F561" s="19"/>
       <c r="G561" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.3">
@@ -10268,7 +11446,7 @@
       <c r="F562" s="18"/>
       <c r="G562" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.3">
@@ -10280,7 +11458,7 @@
       <c r="F563" s="19"/>
       <c r="G563" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
@@ -10292,7 +11470,7 @@
       <c r="F564" s="18"/>
       <c r="G564" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.3">
@@ -10304,7 +11482,7 @@
       <c r="F565" s="19"/>
       <c r="G565" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.3">
@@ -10316,7 +11494,7 @@
       <c r="F566" s="18"/>
       <c r="G566" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
@@ -10328,7 +11506,7 @@
       <c r="F567" s="19"/>
       <c r="G567" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.3">
@@ -10340,7 +11518,7 @@
       <c r="F568" s="18"/>
       <c r="G568" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
@@ -10352,7 +11530,7 @@
       <c r="F569" s="19"/>
       <c r="G569" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
@@ -10364,7 +11542,7 @@
       <c r="F570" s="18"/>
       <c r="G570" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.3">
@@ -10376,7 +11554,7 @@
       <c r="F571" s="19"/>
       <c r="G571" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
@@ -10388,7 +11566,7 @@
       <c r="F572" s="18"/>
       <c r="G572" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
@@ -10400,7 +11578,7 @@
       <c r="F573" s="19"/>
       <c r="G573" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.3">
@@ -10412,7 +11590,7 @@
       <c r="F574" s="18"/>
       <c r="G574" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
@@ -10424,7 +11602,7 @@
       <c r="F575" s="19"/>
       <c r="G575" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
@@ -10436,7 +11614,7 @@
       <c r="F576" s="18"/>
       <c r="G576" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
@@ -10448,7 +11626,7 @@
       <c r="F577" s="19"/>
       <c r="G577" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.3">
@@ -10460,7 +11638,7 @@
       <c r="F578" s="18"/>
       <c r="G578" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
@@ -10472,7 +11650,7 @@
       <c r="F579" s="19"/>
       <c r="G579" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
@@ -10484,7 +11662,7 @@
       <c r="F580" s="18"/>
       <c r="G580" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
@@ -10496,7 +11674,7 @@
       <c r="F581" s="19"/>
       <c r="G581" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
@@ -10508,7 +11686,7 @@
       <c r="F582" s="18"/>
       <c r="G582" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
@@ -10520,7 +11698,7 @@
       <c r="F583" s="19"/>
       <c r="G583" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
@@ -10532,7 +11710,7 @@
       <c r="F584" s="18"/>
       <c r="G584" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
@@ -10544,7 +11722,7 @@
       <c r="F585" s="19"/>
       <c r="G585" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
@@ -10556,7 +11734,7 @@
       <c r="F586" s="18"/>
       <c r="G586" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
@@ -10568,7 +11746,7 @@
       <c r="F587" s="19"/>
       <c r="G587" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
@@ -10580,7 +11758,7 @@
       <c r="F588" s="18"/>
       <c r="G588" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
@@ -10592,7 +11770,7 @@
       <c r="F589" s="19"/>
       <c r="G589" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
@@ -10604,7 +11782,7 @@
       <c r="F590" s="18"/>
       <c r="G590" s="18">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
@@ -10616,7 +11794,7 @@
       <c r="F591" s="19"/>
       <c r="G591" s="19">
         <f t="shared" si="10"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
@@ -10628,7 +11806,7 @@
       <c r="F592" s="18"/>
       <c r="G592" s="18">
         <f t="shared" ref="G592:G655" si="11">G591+E592-F592</f>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
@@ -10640,7 +11818,7 @@
       <c r="F593" s="19"/>
       <c r="G593" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
@@ -10652,7 +11830,7 @@
       <c r="F594" s="18"/>
       <c r="G594" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
@@ -10664,7 +11842,7 @@
       <c r="F595" s="19"/>
       <c r="G595" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
@@ -10676,7 +11854,7 @@
       <c r="F596" s="18"/>
       <c r="G596" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
@@ -10688,7 +11866,7 @@
       <c r="F597" s="19"/>
       <c r="G597" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.3">
@@ -10700,7 +11878,7 @@
       <c r="F598" s="18"/>
       <c r="G598" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
@@ -10712,7 +11890,7 @@
       <c r="F599" s="19"/>
       <c r="G599" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.3">
@@ -10724,7 +11902,7 @@
       <c r="F600" s="18"/>
       <c r="G600" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
@@ -10736,7 +11914,7 @@
       <c r="F601" s="19"/>
       <c r="G601" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
@@ -10748,7 +11926,7 @@
       <c r="F602" s="18"/>
       <c r="G602" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
@@ -10760,7 +11938,7 @@
       <c r="F603" s="19"/>
       <c r="G603" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
@@ -10772,7 +11950,7 @@
       <c r="F604" s="18"/>
       <c r="G604" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
@@ -10784,7 +11962,7 @@
       <c r="F605" s="19"/>
       <c r="G605" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
@@ -10796,7 +11974,7 @@
       <c r="F606" s="18"/>
       <c r="G606" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.3">
@@ -10808,7 +11986,7 @@
       <c r="F607" s="19"/>
       <c r="G607" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
@@ -10820,7 +11998,7 @@
       <c r="F608" s="18"/>
       <c r="G608" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
@@ -10832,7 +12010,7 @@
       <c r="F609" s="19"/>
       <c r="G609" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
@@ -10844,7 +12022,7 @@
       <c r="F610" s="18"/>
       <c r="G610" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.3">
@@ -10856,7 +12034,7 @@
       <c r="F611" s="19"/>
       <c r="G611" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
@@ -10868,7 +12046,7 @@
       <c r="F612" s="18"/>
       <c r="G612" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
@@ -10880,7 +12058,7 @@
       <c r="F613" s="19"/>
       <c r="G613" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">
@@ -10892,7 +12070,7 @@
       <c r="F614" s="18"/>
       <c r="G614" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
@@ -10904,7 +12082,7 @@
       <c r="F615" s="19"/>
       <c r="G615" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.3">
@@ -10916,7 +12094,7 @@
       <c r="F616" s="18"/>
       <c r="G616" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.3">
@@ -10928,7 +12106,7 @@
       <c r="F617" s="19"/>
       <c r="G617" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.3">
@@ -10940,7 +12118,7 @@
       <c r="F618" s="18"/>
       <c r="G618" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.3">
@@ -10952,7 +12130,7 @@
       <c r="F619" s="19"/>
       <c r="G619" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.3">
@@ -10964,7 +12142,7 @@
       <c r="F620" s="18"/>
       <c r="G620" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.3">
@@ -10976,7 +12154,7 @@
       <c r="F621" s="19"/>
       <c r="G621" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.3">
@@ -10988,7 +12166,7 @@
       <c r="F622" s="18"/>
       <c r="G622" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.3">
@@ -11000,7 +12178,7 @@
       <c r="F623" s="19"/>
       <c r="G623" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
@@ -11012,7 +12190,7 @@
       <c r="F624" s="18"/>
       <c r="G624" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
@@ -11024,7 +12202,7 @@
       <c r="F625" s="19"/>
       <c r="G625" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.3">
@@ -11036,7 +12214,7 @@
       <c r="F626" s="18"/>
       <c r="G626" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.3">
@@ -11048,7 +12226,7 @@
       <c r="F627" s="19"/>
       <c r="G627" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
@@ -11060,7 +12238,7 @@
       <c r="F628" s="18"/>
       <c r="G628" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.3">
@@ -11072,7 +12250,7 @@
       <c r="F629" s="19"/>
       <c r="G629" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.3">
@@ -11084,7 +12262,7 @@
       <c r="F630" s="18"/>
       <c r="G630" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.3">
@@ -11096,7 +12274,7 @@
       <c r="F631" s="19"/>
       <c r="G631" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.3">
@@ -11108,7 +12286,7 @@
       <c r="F632" s="18"/>
       <c r="G632" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.3">
@@ -11120,7 +12298,7 @@
       <c r="F633" s="19"/>
       <c r="G633" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.3">
@@ -11132,7 +12310,7 @@
       <c r="F634" s="18"/>
       <c r="G634" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.3">
@@ -11144,7 +12322,7 @@
       <c r="F635" s="19"/>
       <c r="G635" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
@@ -11156,7 +12334,7 @@
       <c r="F636" s="18"/>
       <c r="G636" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.3">
@@ -11168,7 +12346,7 @@
       <c r="F637" s="19"/>
       <c r="G637" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.3">
@@ -11180,7 +12358,7 @@
       <c r="F638" s="18"/>
       <c r="G638" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
@@ -11192,7 +12370,7 @@
       <c r="F639" s="19"/>
       <c r="G639" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.3">
@@ -11204,7 +12382,7 @@
       <c r="F640" s="18"/>
       <c r="G640" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.3">
@@ -11216,7 +12394,7 @@
       <c r="F641" s="19"/>
       <c r="G641" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.3">
@@ -11228,7 +12406,7 @@
       <c r="F642" s="18"/>
       <c r="G642" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.3">
@@ -11240,7 +12418,7 @@
       <c r="F643" s="19"/>
       <c r="G643" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.3">
@@ -11252,7 +12430,7 @@
       <c r="F644" s="18"/>
       <c r="G644" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.3">
@@ -11264,7 +12442,7 @@
       <c r="F645" s="19"/>
       <c r="G645" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.3">
@@ -11276,7 +12454,7 @@
       <c r="F646" s="18"/>
       <c r="G646" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.3">
@@ -11288,7 +12466,7 @@
       <c r="F647" s="19"/>
       <c r="G647" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.3">
@@ -11300,7 +12478,7 @@
       <c r="F648" s="18"/>
       <c r="G648" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.3">
@@ -11312,7 +12490,7 @@
       <c r="F649" s="19"/>
       <c r="G649" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.3">
@@ -11324,7 +12502,7 @@
       <c r="F650" s="18"/>
       <c r="G650" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.3">
@@ -11336,7 +12514,7 @@
       <c r="F651" s="19"/>
       <c r="G651" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.3">
@@ -11348,7 +12526,7 @@
       <c r="F652" s="18"/>
       <c r="G652" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.3">
@@ -11360,7 +12538,7 @@
       <c r="F653" s="19"/>
       <c r="G653" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.3">
@@ -11372,7 +12550,7 @@
       <c r="F654" s="18"/>
       <c r="G654" s="18">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.3">
@@ -11384,7 +12562,7 @@
       <c r="F655" s="19"/>
       <c r="G655" s="19">
         <f t="shared" si="11"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.3">
@@ -11396,7 +12574,7 @@
       <c r="F656" s="18"/>
       <c r="G656" s="18">
         <f t="shared" ref="G656:G719" si="12">G655+E656-F656</f>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.3">
@@ -11408,7 +12586,7 @@
       <c r="F657" s="19"/>
       <c r="G657" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.3">
@@ -11420,7 +12598,7 @@
       <c r="F658" s="18"/>
       <c r="G658" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.3">
@@ -11432,7 +12610,7 @@
       <c r="F659" s="19"/>
       <c r="G659" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.3">
@@ -11444,7 +12622,7 @@
       <c r="F660" s="18"/>
       <c r="G660" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.3">
@@ -11456,7 +12634,7 @@
       <c r="F661" s="19"/>
       <c r="G661" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.3">
@@ -11468,7 +12646,7 @@
       <c r="F662" s="18"/>
       <c r="G662" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.3">
@@ -11480,7 +12658,7 @@
       <c r="F663" s="19"/>
       <c r="G663" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.3">
@@ -11492,7 +12670,7 @@
       <c r="F664" s="18"/>
       <c r="G664" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.3">
@@ -11504,7 +12682,7 @@
       <c r="F665" s="19"/>
       <c r="G665" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.3">
@@ -11516,7 +12694,7 @@
       <c r="F666" s="18"/>
       <c r="G666" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.3">
@@ -11528,7 +12706,7 @@
       <c r="F667" s="19"/>
       <c r="G667" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.3">
@@ -11540,7 +12718,7 @@
       <c r="F668" s="18"/>
       <c r="G668" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.3">
@@ -11552,7 +12730,7 @@
       <c r="F669" s="19"/>
       <c r="G669" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.3">
@@ -11564,7 +12742,7 @@
       <c r="F670" s="18"/>
       <c r="G670" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.3">
@@ -11576,7 +12754,7 @@
       <c r="F671" s="19"/>
       <c r="G671" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.3">
@@ -11588,7 +12766,7 @@
       <c r="F672" s="18"/>
       <c r="G672" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.3">
@@ -11600,7 +12778,7 @@
       <c r="F673" s="19"/>
       <c r="G673" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.3">
@@ -11612,7 +12790,7 @@
       <c r="F674" s="18"/>
       <c r="G674" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.3">
@@ -11624,7 +12802,7 @@
       <c r="F675" s="19"/>
       <c r="G675" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.3">
@@ -11636,7 +12814,7 @@
       <c r="F676" s="18"/>
       <c r="G676" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.3">
@@ -11648,7 +12826,7 @@
       <c r="F677" s="19"/>
       <c r="G677" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.3">
@@ -11660,7 +12838,7 @@
       <c r="F678" s="18"/>
       <c r="G678" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.3">
@@ -11672,7 +12850,7 @@
       <c r="F679" s="19"/>
       <c r="G679" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.3">
@@ -11684,7 +12862,7 @@
       <c r="F680" s="18"/>
       <c r="G680" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.3">
@@ -11696,7 +12874,7 @@
       <c r="F681" s="19"/>
       <c r="G681" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.3">
@@ -11708,7 +12886,7 @@
       <c r="F682" s="18"/>
       <c r="G682" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.3">
@@ -11720,7 +12898,7 @@
       <c r="F683" s="19"/>
       <c r="G683" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.3">
@@ -11732,7 +12910,7 @@
       <c r="F684" s="18"/>
       <c r="G684" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.3">
@@ -11744,7 +12922,7 @@
       <c r="F685" s="19"/>
       <c r="G685" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.3">
@@ -11756,7 +12934,7 @@
       <c r="F686" s="18"/>
       <c r="G686" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.3">
@@ -11768,7 +12946,7 @@
       <c r="F687" s="19"/>
       <c r="G687" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.3">
@@ -11780,7 +12958,7 @@
       <c r="F688" s="18"/>
       <c r="G688" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.3">
@@ -11792,7 +12970,7 @@
       <c r="F689" s="19"/>
       <c r="G689" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.3">
@@ -11804,7 +12982,7 @@
       <c r="F690" s="18"/>
       <c r="G690" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.3">
@@ -11816,7 +12994,7 @@
       <c r="F691" s="19"/>
       <c r="G691" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.3">
@@ -11828,7 +13006,7 @@
       <c r="F692" s="18"/>
       <c r="G692" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.3">
@@ -11840,7 +13018,7 @@
       <c r="F693" s="19"/>
       <c r="G693" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.3">
@@ -11852,7 +13030,7 @@
       <c r="F694" s="18"/>
       <c r="G694" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.3">
@@ -11864,7 +13042,7 @@
       <c r="F695" s="19"/>
       <c r="G695" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.3">
@@ -11876,7 +13054,7 @@
       <c r="F696" s="18"/>
       <c r="G696" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.3">
@@ -11888,7 +13066,7 @@
       <c r="F697" s="19"/>
       <c r="G697" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.3">
@@ -11900,7 +13078,7 @@
       <c r="F698" s="18"/>
       <c r="G698" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.3">
@@ -11912,7 +13090,7 @@
       <c r="F699" s="19"/>
       <c r="G699" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.3">
@@ -11924,7 +13102,7 @@
       <c r="F700" s="18"/>
       <c r="G700" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.3">
@@ -11936,7 +13114,7 @@
       <c r="F701" s="19"/>
       <c r="G701" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.3">
@@ -11948,7 +13126,7 @@
       <c r="F702" s="18"/>
       <c r="G702" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.3">
@@ -11960,7 +13138,7 @@
       <c r="F703" s="19"/>
       <c r="G703" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.3">
@@ -11972,7 +13150,7 @@
       <c r="F704" s="18"/>
       <c r="G704" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.3">
@@ -11984,7 +13162,7 @@
       <c r="F705" s="19"/>
       <c r="G705" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.3">
@@ -11996,7 +13174,7 @@
       <c r="F706" s="18"/>
       <c r="G706" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.3">
@@ -12008,7 +13186,7 @@
       <c r="F707" s="19"/>
       <c r="G707" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.3">
@@ -12020,7 +13198,7 @@
       <c r="F708" s="18"/>
       <c r="G708" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.3">
@@ -12032,7 +13210,7 @@
       <c r="F709" s="19"/>
       <c r="G709" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.3">
@@ -12044,7 +13222,7 @@
       <c r="F710" s="18"/>
       <c r="G710" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.3">
@@ -12056,7 +13234,7 @@
       <c r="F711" s="19"/>
       <c r="G711" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.3">
@@ -12068,7 +13246,7 @@
       <c r="F712" s="18"/>
       <c r="G712" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.3">
@@ -12080,7 +13258,7 @@
       <c r="F713" s="19"/>
       <c r="G713" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.3">
@@ -12092,7 +13270,7 @@
       <c r="F714" s="18"/>
       <c r="G714" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.3">
@@ -12104,7 +13282,7 @@
       <c r="F715" s="19"/>
       <c r="G715" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.3">
@@ -12116,7 +13294,7 @@
       <c r="F716" s="18"/>
       <c r="G716" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.3">
@@ -12128,7 +13306,7 @@
       <c r="F717" s="19"/>
       <c r="G717" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.3">
@@ -12140,7 +13318,7 @@
       <c r="F718" s="18"/>
       <c r="G718" s="18">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.3">
@@ -12152,7 +13330,7 @@
       <c r="F719" s="19"/>
       <c r="G719" s="19">
         <f t="shared" si="12"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
@@ -12164,7 +13342,7 @@
       <c r="F720" s="18"/>
       <c r="G720" s="18">
         <f t="shared" ref="G720:G735" si="13">G719+E720-F720</f>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.3">
@@ -12176,7 +13354,7 @@
       <c r="F721" s="19"/>
       <c r="G721" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,7 +13366,7 @@
       <c r="F722" s="18"/>
       <c r="G722" s="18">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.3">
@@ -12200,7 +13378,7 @@
       <c r="F723" s="19"/>
       <c r="G723" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.3">
@@ -12212,7 +13390,7 @@
       <c r="F724" s="18"/>
       <c r="G724" s="18">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.3">
@@ -12224,7 +13402,7 @@
       <c r="F725" s="19"/>
       <c r="G725" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.3">
@@ -12236,7 +13414,7 @@
       <c r="F726" s="18"/>
       <c r="G726" s="18">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.3">
@@ -12248,7 +13426,7 @@
       <c r="F727" s="19"/>
       <c r="G727" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.3">
@@ -12260,7 +13438,7 @@
       <c r="F728" s="18"/>
       <c r="G728" s="18">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.3">
@@ -12272,7 +13450,7 @@
       <c r="F729" s="19"/>
       <c r="G729" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.3">
@@ -12284,7 +13462,7 @@
       <c r="F730" s="18"/>
       <c r="G730" s="18">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.3">
@@ -12296,7 +13474,7 @@
       <c r="F731" s="19"/>
       <c r="G731" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.3">
@@ -12308,7 +13486,7 @@
       <c r="F732" s="18"/>
       <c r="G732" s="18">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.3">
@@ -12320,7 +13498,7 @@
       <c r="F733" s="19"/>
       <c r="G733" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.3">
@@ -12332,7 +13510,7 @@
       <c r="F734" s="18"/>
       <c r="G734" s="18">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.3">
@@ -12344,7 +13522,7 @@
       <c r="F735" s="19"/>
       <c r="G735" s="19">
         <f t="shared" si="13"/>
-        <v>89726</v>
+        <v>124226</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.3">
